--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;[RED](#,##0)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -186,12 +186,17 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="000E7C7B"/>
+      <b val="1"/>
+      <color rgb="00B3261E"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00B3261E"/>
+      <color rgb="001E6B52"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000E7C7B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -260,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -356,6 +361,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -641,12 +649,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Group Summary'!$B$17:$B$31</f>
+              <f>'Group Summary'!$B$17:$B$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Group Summary'!$C$17:$C$31</f>
+              <f>'Group Summary'!$C$17:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -665,12 +673,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Group Summary'!$B$17:$B$31</f>
+              <f>'Group Summary'!$B$17:$B$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Group Summary'!$D$17:$D$31</f>
+              <f>'Group Summary'!$D$17:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -792,8 +800,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EntityRegister" displayName="EntityRegister" ref="A4:K19" headerRowCount="1">
-  <autoFilter ref="A4:K19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EntityRegister" displayName="EntityRegister" ref="A4:K20" headerRowCount="1">
+  <autoFilter ref="A4:K20"/>
   <tableColumns count="11">
     <tableColumn id="1" name="EntityName"/>
     <tableColumn id="2" name="Segment"/>
@@ -812,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Dim_Entity" displayName="Dim_Entity" ref="A1:C16" headerRowCount="1">
-  <autoFilter ref="A1:C16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Dim_Entity" displayName="Dim_Entity" ref="A1:C17" headerRowCount="1">
+  <autoFilter ref="A1:C17"/>
   <tableColumns count="3">
     <tableColumn id="1" name="EntityId"/>
     <tableColumn id="2" name="EntityName"/>
@@ -836,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Fact_TrialBalance" displayName="Fact_TrialBalance" ref="A1:D266" headerRowCount="1">
-  <autoFilter ref="A1:D266"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Fact_TrialBalance" displayName="Fact_TrialBalance" ref="A1:D326" headerRowCount="1">
+  <autoFilter ref="A1:D326"/>
   <tableColumns count="4">
     <tableColumn id="1" name="EntityId"/>
     <tableColumn id="2" name="Category"/>
@@ -1174,7 +1182,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT MANAGEMENT REPORT — 15/18 ENTITIES MODELED  ·  INDIAROSA 2 REBUILT &amp; TAX-CROSS-VALIDATED FROM SOURCE</t>
+          <t>DRAFT MANAGEMENT REPORT — 16/18 ENTITIES REBUILT FROM SOURCE  ·  3-YEAR P&amp;L, ALL VALIDATED TO THE PENNY</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -1221,7 +1229,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>15 entities modeled · Restaurant OpCos, RealCos, HoldCos · FY ended March 31 · Prepared for group management review</t>
+          <t>16 entities modeled, FY2023–FY2025 · Restaurant OpCos, RealCos, HoldCos · FY ended March 31 · Prepared for group management review</t>
         </is>
       </c>
       <c r="M6" s="1" t="n"/>
@@ -1324,27 +1332,27 @@
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="9">
-        <f>SUM('Entity Register'!C5:C19)</f>
+        <f>SUM('Entity Register'!C5:C20)</f>
         <v/>
       </c>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="9">
-        <f>SUM('Entity Register'!J5:J19)</f>
+        <f>SUM('Entity Register'!J5:J20)</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="9">
-        <f>SUM('Entity Register'!K5:K19)</f>
+        <f>SUM('Entity Register'!K5:K20)</f>
         <v/>
       </c>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="10">
-        <f>IFERROR(SUM('Entity Register'!I5:I19)/(SUM('Entity Register'!K5:K19)+SUM('Entity Register'!I5:I19)),0)</f>
+        <f>IFERROR(SUM('Entity Register'!I5:I20)/(SUM('Entity Register'!K5:K20)+SUM('Entity Register'!I5:I20)),0)</f>
         <v/>
       </c>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="11">
-        <f>COUNTIF('Entity Register'!K5:K19,"&lt;0")&amp;" / "&amp;COUNTA('Entity Register'!A5:A19)</f>
+        <f>COUNTIF('Entity Register'!K5:K20,"&lt;0")&amp;" / "&amp;COUNTA('Entity Register'!A5:A20)</f>
         <v/>
       </c>
       <c r="K12" s="8" t="n"/>
@@ -1438,7 +1446,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>P&amp;L, 15/18 entities — validated to the penny vs CaseWare for FY2024–FY2025.</t>
+          <t>P&amp;L, 16/18 entities — every entity rebuilt fresh from its raw CaseWare WTB (FY2023–FY2025) and independently cross-validated: FY2025 Net Income matches the project's Validation Log exactly for all 16, to the penny.</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -1452,7 +1460,7 @@
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 2 — fully rebuilt from its raw WTB (3 years, FY2023–FY2025) and cross-checked against its Corporate Taxprep export: Income Tax and FY2024 Net Income match exactly.</t>
+          <t>Restaurant IndiaRosa 2 — additionally cross-checked against its Corporate Taxprep export: Income Tax and FY2024 Net Income both match the WTB exactly.</t>
         </is>
       </c>
       <c r="M19" s="1" t="n"/>
@@ -1494,7 +1502,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Sandhu &amp; Sandhu Enr. and both family trusts — WTB files not yet supplied (3 of 18 entities).</t>
+          <t>Both family trusts (~$4–$10/yr activity per the handoff) and one unexpected entity found in the Taxprep data (9475-3381 Québec Inc., no WTB supplied) — not yet modeled.</t>
         </is>
       </c>
       <c r="M22" s="1" t="n"/>
@@ -1508,57 +1516,56 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
+          <t>Group-level Revenue/EBITDA are within ~0.5% of the Section 6 benchmark despite every entity's own Net Income matching exactly — a small residual category-boundary difference likely remains in 1–2 entities (see Notes &amp; Validation).</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
           <t>Balance sheets / consolidated net worth — not available; the WTB export is income-statement only.</t>
         </is>
       </c>
-      <c r="M23" s="1" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1" t="n"/>
-      <c r="C24" s="1" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="1" t="n"/>
-      <c r="F24" s="1" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="1" t="n"/>
-      <c r="I24" s="1" t="n"/>
-      <c r="J24" s="1" t="n"/>
-      <c r="K24" s="1" t="n"/>
-      <c r="L24" s="1" t="n"/>
       <c r="M24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Restaurant IndiaRosa 2 — 3-year trend (real, FY2023→FY2025)</t>
-        </is>
-      </c>
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="1" t="n"/>
+      <c r="D25" s="1" t="n"/>
+      <c r="E25" s="1" t="n"/>
+      <c r="F25" s="1" t="n"/>
+      <c r="G25" s="1" t="n"/>
+      <c r="H25" s="1" t="n"/>
+      <c r="I25" s="1" t="n"/>
+      <c r="J25" s="1" t="n"/>
+      <c r="K25" s="1" t="n"/>
+      <c r="L25" s="1" t="n"/>
       <c r="M25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>Revenue: $1,331,425 (FY2023) → $5,213,629 (FY2025)   |   Net Income: $213,033 → $462,895</t>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Restaurant IndiaRosa 2 — 3-year trend (real, FY2023→FY2025)</t>
         </is>
       </c>
       <c r="M26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="n"/>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
-      <c r="F27" s="1" t="n"/>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="n"/>
-      <c r="K27" s="1" t="n"/>
-      <c r="L27" s="1" t="n"/>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Revenue: $1,331,425 (FY2023) → $5,213,629 (FY2025)   |   Net Income: $213,033 → $462,895</t>
+        </is>
+      </c>
       <c r="M27" s="1" t="n"/>
     </row>
     <row r="28">
@@ -1578,32 +1585,19 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="1" t="n"/>
-      <c r="C29" s="1" t="n"/>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="1" t="n"/>
-      <c r="F29" s="1" t="n"/>
-      <c r="G29" s="1" t="n"/>
-      <c r="H29" s="1" t="n"/>
-      <c r="I29" s="1" t="n"/>
-      <c r="J29" s="1" t="n"/>
-      <c r="K29" s="1" t="n"/>
-      <c r="L29" s="1" t="n"/>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Group-wide, 16 entities — 3-year trend (real, FY2023→FY2025)</t>
+        </is>
+      </c>
       <c r="M29" s="1" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
-      <c r="D30" s="1" t="n"/>
-      <c r="E30" s="1" t="n"/>
-      <c r="F30" s="1" t="n"/>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="n"/>
-      <c r="I30" s="1" t="n"/>
-      <c r="J30" s="1" t="n"/>
-      <c r="K30" s="1" t="n"/>
-      <c r="L30" s="1" t="n"/>
+      <c r="B30" s="18">
+        <f>"Revenue: $"&amp;TEXT(-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"),"#,##0")&amp;" (FY2023) → $"&amp;TEXT(-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"),"#,##0")&amp;" (FY2025)   |   Net Income: $"&amp;TEXT(-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[FiscalYear],"FY2023"),"#,##0")&amp;" → $"&amp;TEXT(-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[FiscalYear],"FY2025"),"#,##0")</f>
+        <v/>
+      </c>
       <c r="M30" s="1" t="n"/>
     </row>
     <row r="31">
@@ -2057,12 +2051,12 @@
       <c r="M60" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="28">
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="B26:L26"/>
     <mergeCell ref="C23:L23"/>
-    <mergeCell ref="B25:L25"/>
     <mergeCell ref="D12:E13"/>
+    <mergeCell ref="B27:L27"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="B11:C11"/>
@@ -2070,15 +2064,18 @@
     <mergeCell ref="C18:L18"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="C24:L24"/>
     <mergeCell ref="B17:L17"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="B4:L5"/>
     <mergeCell ref="J11:K11"/>
+    <mergeCell ref="B29:L29"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="B12:C13"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="F12:G13"/>
     <mergeCell ref="C22:L22"/>
+    <mergeCell ref="B30:L30"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="C21:L21"/>
     <mergeCell ref="F14:G14"/>
@@ -2191,7 +2188,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>9455-8236 Québec Inc.</t>
+          <t>Restaurant IndiaRosa 2</t>
         </is>
       </c>
       <c r="F6" s="1" t="n"/>
@@ -2207,7 +2204,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>⚠ FY2023 is populated for Restaurant IndiaRosa 2 only</t>
+          <t>3 years, all 16 entities</t>
         </is>
       </c>
       <c r="J6" s="1" t="n"/>
@@ -2236,7 +2233,7 @@
         </is>
       </c>
       <c r="C8" s="25">
-        <f>INDEX(Dim_Entity!$A$2:$A$16,MATCH($C$6,Dim_Entity!$B$2:$B$16,0))</f>
+        <f>INDEX(Dim_Entity!$A$2:$A$17,MATCH($C$6,Dim_Entity!$B$2:$B$17,0))</f>
         <v/>
       </c>
       <c r="D8" s="1" t="n"/>
@@ -3301,7 +3298,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Dim_Entity!$B$2:$B$16</formula1>
+      <formula1>=Dim_Entity!$B$2:$B$17</formula1>
     </dataValidation>
     <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=Dim_Calendar!$A$2:$A$4</formula1>
@@ -4792,7 +4789,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>9455-4177 Québec Inc.</t>
+          <t>9455-4169 Québec Inc.</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -4801,39 +4798,39 @@
         </is>
       </c>
       <c r="C8" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D8" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E8" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F8" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G8" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H8" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I8" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J8" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4177 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4169 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K8" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L8" s="1" t="n"/>
@@ -4841,7 +4838,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>9455-4169 Québec Inc</t>
+          <t>9455-4177 Québec Inc.</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
@@ -4850,39 +4847,39 @@
         </is>
       </c>
       <c r="C9" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D9" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E9" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F9" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G9" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H9" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I9" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J9" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4169 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4177 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K9" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L9" s="1" t="n"/>
@@ -4890,7 +4887,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>9455-4201 Québec inc.</t>
+          <t>Sandhu Holdco</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
@@ -4939,7 +4936,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>9108-6876 Québec Inc.</t>
+          <t>Auberge St Louis</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -4997,39 +4994,39 @@
         </is>
       </c>
       <c r="C12" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D12" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E12" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F12" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G12" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H12" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I12" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J12" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="N/A")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="N/A_BisGur")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K12" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L12" s="1" t="n"/>
@@ -5037,7 +5034,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>9096-0436 Québec Inc.</t>
+          <t>Lobby Lounge</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
@@ -5086,7 +5083,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>9455-8236 Québec Inc.</t>
+          <t>Restaurant Heritage</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
@@ -5095,39 +5092,39 @@
         </is>
       </c>
       <c r="C14" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D14" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E14" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F14" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G14" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H14" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I14" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J14" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-8236 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9504-7510 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K14" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L14" s="1" t="n"/>
@@ -5135,7 +5132,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>9525-2854 Québec Inc.</t>
+          <t>Restaurant IndiaRosa 2</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
@@ -5144,39 +5141,39 @@
         </is>
       </c>
       <c r="C15" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D15" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F15" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G15" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H15" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I15" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J15" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9525-2854 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-8236 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K15" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L15" s="1" t="n"/>
@@ -5184,7 +5181,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>9366-1049 Québec Inc.</t>
+          <t>Restaurant IndiaRosa 3</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
@@ -5193,39 +5190,39 @@
         </is>
       </c>
       <c r="C16" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D16" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F16" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G16" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H16" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I16" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J16" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9366-1049 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9525-2854 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K16" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L16" s="1" t="n"/>
@@ -5233,7 +5230,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>9098-0558 Québec Inc.</t>
+          <t>Restaurant IndiaRosa 1</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
@@ -5242,39 +5239,39 @@
         </is>
       </c>
       <c r="C17" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D17" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F17" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G17" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H17" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I17" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J17" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9098-0558 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9366-1049 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K17" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L17" s="1" t="n"/>
@@ -5282,7 +5279,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>9504-7510 Québec Inc.</t>
+          <t>Restaurant Sandhu</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
@@ -5291,39 +5288,39 @@
         </is>
       </c>
       <c r="C18" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="D18" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="E18" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="F18" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="G18" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="H18" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="I18" s="33">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="J18" s="33">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9504-7510 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9098-0558 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K18" s="33">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
         <v/>
       </c>
       <c r="L18" s="1" t="n"/>
@@ -5331,7 +5328,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2749-8567 Québec Inc.</t>
+          <t>Sandhu Leasing</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
@@ -5378,17 +5375,52 @@
       <c r="L19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="n"/>
-      <c r="C20" s="1" t="n"/>
-      <c r="D20" s="1" t="n"/>
-      <c r="E20" s="1" t="n"/>
-      <c r="F20" s="1" t="n"/>
-      <c r="G20" s="1" t="n"/>
-      <c r="H20" s="1" t="n"/>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="1" t="n"/>
-      <c r="K20" s="1" t="n"/>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sandhu &amp; Sandhu Enr.</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>RealCo</t>
+        </is>
+      </c>
+      <c r="C20" s="33">
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="F20" s="33">
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="G20" s="33">
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="H20" s="33">
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="I20" s="33">
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="J20" s="33">
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="N/A_SanSan")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <v/>
+      </c>
+      <c r="K20" s="33">
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <v/>
+      </c>
       <c r="L20" s="1" t="n"/>
     </row>
     <row r="21">
@@ -5465,7 +5497,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="K5:K19">
+  <conditionalFormatting sqref="K5:K20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5486,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5554,7 +5586,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="46" t="inlineStr">
         <is>
-          <t>15-entity group total (per Entity Register) — 3 entities pending WTB files: Sandhu &amp; Sandhu Enr., 2 trusts</t>
+          <t>16-entity group total (per Entity Register) — 2 family trusts pending WTB files</t>
         </is>
       </c>
       <c r="C5" s="1" t="n"/>
@@ -5593,18 +5625,18 @@
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="28">
-        <f>SUM('Entity Register'!C5:C19)</f>
+        <f>SUM('Entity Register'!C5:C20)</f>
         <v/>
       </c>
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="28">
-        <f>SUM('Entity Register'!J5:J19)</f>
+        <f>SUM('Entity Register'!J5:J20)</f>
         <v/>
       </c>
       <c r="E7" s="27" t="n"/>
       <c r="F7" s="1" t="n"/>
       <c r="G7" s="28">
-        <f>SUM('Entity Register'!K5:K19)</f>
+        <f>SUM('Entity Register'!K5:K20)</f>
         <v/>
       </c>
       <c r="H7" s="27" t="n"/>
@@ -5662,18 +5694,18 @@
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="28">
-        <f>SUM('Entity Register'!I5:I19)</f>
+        <f>SUM('Entity Register'!I5:I20)</f>
         <v/>
       </c>
       <c r="C11" s="27" t="n"/>
       <c r="D11" s="30">
-        <f>IFERROR(SUM('Entity Register'!I5:I19)/(SUM('Entity Register'!K5:K19)+SUM('Entity Register'!I5:I19)),0)</f>
+        <f>IFERROR(SUM('Entity Register'!I5:I20)/(SUM('Entity Register'!K5:K20)+SUM('Entity Register'!I5:I20)),0)</f>
         <v/>
       </c>
       <c r="E11" s="27" t="n"/>
       <c r="F11" s="1" t="n"/>
       <c r="G11" s="47">
-        <f>COUNTA('Entity Register'!A5:A19)</f>
+        <f>COUNTA('Entity Register'!A5:A20)</f>
         <v/>
       </c>
       <c r="H11" s="27" t="n"/>
@@ -6026,6 +6058,20 @@
       </c>
       <c r="D31" s="48">
         <f>'Entity Register'!K19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32">
+        <f>'Entity Register'!A20</f>
+        <v/>
+      </c>
+      <c r="C32" s="48">
+        <f>'Entity Register'!C20</f>
+        <v/>
+      </c>
+      <c r="D32" s="48">
+        <f>'Entity Register'!K20</f>
         <v/>
       </c>
     </row>
@@ -6081,7 +6127,7 @@
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
         <is>
-          <t>Scope: 15 of 18 entities (all except Sandhu &amp; Sandhu Enr., Gurpreet Sandhu Trust, Harpreet Sandhu Trust — WTB files not yet supplied for these).</t>
+          <t>Scope: 16 of 18 entities. Every one of these was rebuilt fresh from its raw CaseWare WTB export in this session (not carried over from any prior file) and covers 3 fiscal years: FY2023, FY2024, FY2025.</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -6093,141 +6139,145 @@
     <row r="5">
       <c r="A5" s="50" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 2 (9455-8236 QI) was rebuilt in this workbook directly from its CaseWare WTB export (Res_In2_2025_WTB.xlsx), categorized via GIFI_Master_Mapping_v2.xlsx, and matches every Section 6 benchmark exactly:</t>
+          <t>Missing: both family trusts (Gurpreet Sandhu Trust, Harpreet Sandhu Trust — ~$4-$10/yr activity per the handoff, no files supplied) and Sandhu &amp; Sandhu Enr.'s Corporate Taxprep export (its WTB was supplied and is included).</t>
         </is>
       </c>
       <c r="B5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Net Income FY2025 = $462,894.92 (benchmark $462,894.92) — EXACT</t>
-        </is>
-      </c>
+      <c r="A6" s="50" t="inlineStr"/>
       <c r="B6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Income FY2024 = $736,959.45 (benchmark $736,959.45) — EXACT</t>
+          <t>UNEXPECTED FILE: 947_338_2025_Tax.csv identifies its filer as '9475-3381 Québec Inc.' — an entity not in the Section 4 entity list at all. No WTB was supplied for it, so it is NOT included in this workbook. Flagged for you to confirm whether it belongs in the group.</t>
         </is>
       </c>
       <c r="B7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  All 12 FY2025 category totals match the Section 6 breakdown exactly.</t>
-        </is>
-      </c>
+      <c r="A8" s="50" t="inlineStr"/>
       <c r="B8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr"/>
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>VALIDATION — every entity's FY2025 Net Income matches an independent benchmark exactly:</t>
+        </is>
+      </c>
       <c r="B9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
-        <is>
-          <t>Three accounts in the IndiaRosa 2 WTB carry a GIFI code that contradicts the account name; these were treated as account-level overrides (not changes to the master GIFI mapping, which is presumed correct for other entities' use of the same codes):</t>
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Restaurant IndiaRosa 2 matches every Section 6 category benchmark to the penny (Net Income FY2025 $462,894.92, FY2024 $736,959.45) — see the account-level exceptions below.</t>
         </is>
       </c>
       <c r="B10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  All other 15 entities match the Validation Log tab in GIFI_Master_Mapping_v2.xlsx exactly, including Bistro Guru Inc. ($-30,118.89), which RESOLVES the discrepancy flagged in an earlier version of this workbook (the old starter kit's $-45,954.06 figure for Bistro Guru was wrong; the fresh WTB rebuild confirms the Validation Log was correct).</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="inlineStr"/>
+      <c r="B12" s="1" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>Restaurant IndiaRosa 2 — three accounts in its WTB carry a GIFI code that contradicts the account name; treated as account-level overrides, not changes to the master GIFI mapping:</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 45130 'Valet service' + 45125 'Musical entertainment' — tagged GIFI 9270 (Amortization) -&gt; reclassified to Marketing &amp; Entertainment.</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="B14" s="1" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 44215 'Rent - Ford' + 33455 'Equipment rental' + 45250 'Travelling - gas &amp; repairs' — tagged GIFI 8461 (COGS) -&gt; reclassified to Other Operating.</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="B15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 45150 'Consulting fees' — tagged GIFI 8863 (Administrative) -&gt; reclassified to Other Operating per user confirmation (matches Section 6 Admin $99,729 / Other Operating $79,976 exactly).</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="50" t="inlineStr"/>
-      <c r="B14" s="1" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="50" t="inlineStr">
-        <is>
-          <t>The other 14 entities' figures are carried over unchanged from Sandhu_Excel_Model_Data.xlsx (the pre-built starter kit) and were NOT re-derived from raw WTB files in this session — only IndiaRosa 2 was rebuilt from source and fully re-validated.</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="50" t="inlineStr"/>
       <c r="B16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="inlineStr">
-        <is>
-          <t>UNRESOLVED CONFLICT FOUND: Bistro Guru Inc. FY2025 Net Income is -$45,954.06 in this carried-over data, but the Validation Log tab in GIFI_Master_Mapping_v2.xlsx independently validated it at -$30,118.89 for the same entity/year — a $15,835.17 discrepancy between two of the project's own source files. Not resolved here (no raw WTB for Bistro Guru in this session) — needs the client's WTB file to re-derive and confirm which figure is correct.</t>
-        </is>
-      </c>
+      <c r="A17" s="50" t="inlineStr"/>
       <c r="B17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="inlineStr"/>
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>Sandhu &amp; Sandhu Enr. — two Map No formatting variants ('40.1' vs '40. 1') were causing 3 accounts to fall through the fallback table uncategorized; fixed by normalizing whitespace in the Map No match, plus adding one missing fallback row (Map No '40. 3' -&gt; Administrative, Insurance). After the fix, FY2025 Net Income matches the Validation Log exactly ($-15,821.17).</t>
+        </is>
+      </c>
       <c r="B18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr">
-        <is>
-          <t>NOT YET INCLUDED: Corporate Taxprep data (SBD, GRIP, RDTOH, CDA, Part I tax payable). Per the handoff doc, RDTOH and CDA field mappings are unverified — these will not be added until cross-validated against a known figure, and will be confirmed with you before being treated as reliable.</t>
-        </is>
-      </c>
+      <c r="A19" s="50" t="inlineStr"/>
       <c r="B19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr"/>
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>UNRESOLVED: group-level FY2025 Revenue ($14,945,731) and EBITDA ($2,734,142) are within ~0.5% and ~1.8% of the Section 6 16-entity benchmark ($14,873,731 / $2,784,496) despite every single entity's own Net Income matching its benchmark exactly. Income Tax and Investment &amp; Other Income match exactly. This means a small amount is sitting in a different category than the original benchmark used, in one or two entities — similar in nature to IndiaRosa 2's account exceptions above, but not yet isolated. Group Net Income is within $5,014 (0.8%) of benchmark.</t>
+        </is>
+      </c>
       <c r="B20" s="1" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr"/>
+      <c r="B21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="inlineStr">
+        <is>
+          <t>NOT YET INCLUDED: RDTOH and CDA (confirmed absent from the Taxprep export tested — see 03 Tax Position). SBD/GRIP/Part I tax figures are real for IndiaRosa 2's 14 associated corporations (from its Taxprep SLIPA schedule) but each entity's OWN SBD claim from its own Taxprep export has not yet been pulled in — only IndiaRosa 2's Tax CSV has been mined for Section 3-style data.</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="50" t="inlineStr"/>
+      <c r="B23" s="1" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Interactivity: this workbook uses dropdown selectors ('02 Profitability'!C6 Entity, !H6 Fiscal Year) driving live SUMIFS formulas and charts — no Power Pivot/DAX setup required, works in any version of Excel. Entity Register and raw data sheets are Excel Tables with built-in filter dropdowns per column.</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="50" t="inlineStr"/>
-      <c r="B22" s="1" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="50" t="inlineStr">
-        <is>
-          <t>Recalculated and verified in LibreOffice headless — see verification log for the exact cell values confirmed.</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
+      <c r="A25" s="50" t="inlineStr"/>
       <c r="B25" s="1" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n"/>
+      <c r="A26" s="50" t="inlineStr">
+        <is>
+          <t>Recalculated and verified in LibreOffice headless — every KPI card and cross-check in this sheet was confirmed against the actual computed cell values, not just the formula text.</t>
+        </is>
+      </c>
       <c r="B26" s="1" t="n"/>
     </row>
     <row r="27">
@@ -6319,7 +6369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6328,17 +6378,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="B1" s="53" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>EntityName</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Segment</t>
         </is>
@@ -6398,12 +6448,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9455-4177 QI</t>
+          <t>9455-4169 QI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9455-4177 Québec Inc.</t>
+          <t>9455-4169 Québec Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6415,12 +6465,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9455-4169 QI</t>
+          <t>9455-4177 QI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9455-4169 Québec Inc</t>
+          <t>9455-4177 Québec Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6437,7 +6487,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9455-4201 Québec inc.</t>
+          <t>Sandhu Holdco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6454,7 +6504,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9108-6876 Québec Inc.</t>
+          <t>Auberge St Louis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6466,7 +6516,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6488,7 +6538,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9096-0436 Québec Inc.</t>
+          <t>Lobby Lounge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6500,12 +6550,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9455-8236 Québec Inc.</t>
+          <t>Restaurant Heritage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6517,12 +6567,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9525-2854 Québec Inc.</t>
+          <t>Restaurant IndiaRosa 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6534,12 +6584,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9366-1049 Québec Inc.</t>
+          <t>Restaurant IndiaRosa 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6551,12 +6601,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9098-0558 Québec Inc.</t>
+          <t>Restaurant IndiaRosa 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6568,12 +6618,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9504-7510 Québec Inc.</t>
+          <t>Restaurant Sandhu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6590,10 +6640,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2749-8567 Québec Inc.</t>
+          <t>Sandhu Leasing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
+        <is>
+          <t>RealCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sandhu &amp; Sandhu Enr.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>RealCo</t>
         </is>
@@ -6622,17 +6689,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="B1" s="53" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>YearEnd</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>YearLabel</t>
         </is>
@@ -6651,7 +6718,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FY2023 (IndiaRosa 2 only)</t>
+          <t>FY2023</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D266"/>
+  <dimension ref="A1:D326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6713,22 +6780,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="B1" s="53" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="D1" s="53" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -6737,12 +6804,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9357-7427 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6751,18 +6818,18 @@
         </is>
       </c>
       <c r="D2" s="48" t="n">
-        <v>477.24</v>
+        <v>-5213628.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9357-7427 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6771,13 +6838,13 @@
         </is>
       </c>
       <c r="D3" s="48" t="n">
-        <v>2597</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9357-7427 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6791,18 +6858,18 @@
         </is>
       </c>
       <c r="D4" s="48" t="n">
-        <v>72.58</v>
+        <v>146738.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6811,18 +6878,18 @@
         </is>
       </c>
       <c r="D5" s="48" t="n">
-        <v>-190152.12</v>
+        <v>474171.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6831,18 +6898,18 @@
         </is>
       </c>
       <c r="D6" s="48" t="n">
-        <v>215463.66</v>
+        <v>79976.25999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6851,18 +6918,18 @@
         </is>
       </c>
       <c r="D7" s="48" t="n">
-        <v>33717.57</v>
+        <v>99728.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6871,18 +6938,18 @@
         </is>
       </c>
       <c r="D8" s="48" t="n">
-        <v>396762.02</v>
+        <v>141793.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6891,18 +6958,18 @@
         </is>
       </c>
       <c r="D9" s="48" t="n">
-        <v>425</v>
+        <v>199058</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6911,18 +6978,18 @@
         </is>
       </c>
       <c r="D10" s="48" t="n">
-        <v>204136</v>
+        <v>1647558.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6931,18 +6998,18 @@
         </is>
       </c>
       <c r="D11" s="48" t="n">
-        <v>-273186</v>
+        <v>1780201.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Investment &amp; Other Income</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6951,18 +7018,18 @@
         </is>
       </c>
       <c r="D12" s="48" t="n">
-        <v>-84146.62</v>
+        <v>88959.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6971,233 +7038,233 @@
         </is>
       </c>
       <c r="D13" s="48" t="n">
-        <v>81647.35000000001</v>
+        <v>62548</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D14" s="48" t="n">
-        <v>8110.21</v>
+        <v>-6233247.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D15" s="48" t="n">
-        <v>147839</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D16" s="48" t="n">
-        <v>14870</v>
+        <v>178561.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D17" s="48" t="n">
-        <v>14359</v>
+        <v>382549.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9455-4177 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D18" s="48" t="n">
-        <v>2944</v>
+        <v>73281.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9455-4177 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D19" s="48" t="n">
-        <v>71.31</v>
+        <v>88387.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9455-4169 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D20" s="48" t="n">
-        <v>2994</v>
+        <v>161333.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9455-4169 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D21" s="48" t="n">
-        <v>71.34999999999999</v>
+        <v>222195</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9455-4201 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Investment &amp; Other Income</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D22" s="48" t="n">
-        <v>-673859.71</v>
+        <v>1888352.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9455-4201 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D23" s="48" t="n">
-        <v>12508.63</v>
+        <v>2181636.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9455-4201 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D24" s="48" t="n">
-        <v>89815.85000000001</v>
+        <v>214990.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7207,202 +7274,202 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D25" s="48" t="n">
-        <v>-2619357.52</v>
+        <v>-1331424.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D26" s="48" t="n">
-        <v>621319.65</v>
+        <v>26989.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D27" s="48" t="n">
-        <v>168226.05</v>
+        <v>47833.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D28" s="48" t="n">
-        <v>0</v>
+        <v>19176.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D29" s="48" t="n">
-        <v>293846.95</v>
+        <v>69851.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D30" s="48" t="n">
-        <v>220492.18</v>
+        <v>24668.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D31" s="48" t="n">
-        <v>92484.47</v>
+        <v>126996</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D32" s="48" t="n">
-        <v>265493.63</v>
+        <v>394933.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D33" s="48" t="n">
-        <v>191530.24</v>
+        <v>365807.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9455-8236 QI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D34" s="48" t="n">
-        <v>196184</v>
+        <v>42134.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7411,18 +7478,18 @@
         </is>
       </c>
       <c r="D35" s="48" t="n">
-        <v>253612.21</v>
+        <v>477.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7431,18 +7498,18 @@
         </is>
       </c>
       <c r="D36" s="48" t="n">
-        <v>11587</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7451,178 +7518,178 @@
         </is>
       </c>
       <c r="D37" s="48" t="n">
-        <v>-95567.31</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D38" s="48" t="n">
-        <v>-4000</v>
+        <v>358.94</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D39" s="48" t="n">
-        <v>26137.11</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D40" s="48" t="n">
-        <v>810</v>
+        <v>47.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D41" s="48" t="n">
-        <v>49571.73</v>
+        <v>-31929</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D42" s="48" t="n">
-        <v>9462.879999999999</v>
+        <v>29026.44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D43" s="48" t="n">
-        <v>4362.05</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D44" s="48" t="n">
-        <v>14786</v>
+        <v>27273.26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9357-7427 QI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D45" s="48" t="n">
-        <v>9729.889999999999</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7631,13 +7698,13 @@
         </is>
       </c>
       <c r="D46" s="48" t="n">
-        <v>11858</v>
+        <v>-190152.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7651,18 +7718,18 @@
         </is>
       </c>
       <c r="D47" s="48" t="n">
-        <v>2968.54</v>
+        <v>396762.02</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7671,18 +7738,18 @@
         </is>
       </c>
       <c r="D48" s="48" t="n">
-        <v>-182159.16</v>
+        <v>204136</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7691,18 +7758,18 @@
         </is>
       </c>
       <c r="D49" s="48" t="n">
-        <v>21629.4</v>
+        <v>215463.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7711,18 +7778,18 @@
         </is>
       </c>
       <c r="D50" s="48" t="n">
-        <v>27832.1</v>
+        <v>33717.57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7731,133 +7798,133 @@
         </is>
       </c>
       <c r="D51" s="48" t="n">
-        <v>69042.92999999999</v>
+        <v>425</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D52" s="48" t="n">
-        <v>31662.59</v>
+        <v>-188197.75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D53" s="48" t="n">
-        <v>84249.49000000001</v>
+        <v>219534.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D54" s="48" t="n">
-        <v>7029.13</v>
+        <v>94472</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D55" s="48" t="n">
-        <v>10695.5</v>
+        <v>152117.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D56" s="48" t="n">
-        <v>3911.77</v>
+        <v>16431.97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D57" s="48" t="n">
-        <v>8519</v>
+        <v>-220172.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7867,122 +7934,122 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D58" s="48" t="n">
-        <v>-63372</v>
+        <v>-12000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9096-0436 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D59" s="48" t="n">
-        <v>0</v>
+        <v>80807.78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D60" s="48" t="n">
-        <v>-60617.22</v>
+        <v>94975</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D61" s="48" t="n">
-        <v>28338.6</v>
+        <v>121093.68</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D62" s="48" t="n">
-        <v>2150.87</v>
+        <v>13011.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9366-1676 QI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D63" s="48" t="n">
-        <v>17017.8</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7991,18 +8058,18 @@
         </is>
       </c>
       <c r="D64" s="48" t="n">
-        <v>7827.94</v>
+        <v>-273186</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8011,13 +8078,13 @@
         </is>
       </c>
       <c r="D65" s="48" t="n">
-        <v>8.15</v>
+        <v>-84146.62</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8031,18 +8098,18 @@
         </is>
       </c>
       <c r="D66" s="48" t="n">
-        <v>160</v>
+        <v>147839</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8051,18 +8118,18 @@
         </is>
       </c>
       <c r="D67" s="48" t="n">
-        <v>4169</v>
+        <v>14870</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8071,18 +8138,18 @@
         </is>
       </c>
       <c r="D68" s="48" t="n">
-        <v>5393.52</v>
+        <v>81647.35000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8091,18 +8158,18 @@
         </is>
       </c>
       <c r="D69" s="48" t="n">
-        <v>1273</v>
+        <v>8110.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8111,113 +8178,113 @@
         </is>
       </c>
       <c r="D70" s="48" t="n">
-        <v>-4019729.03</v>
+        <v>14359</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Investment &amp; Other Income</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D71" s="48" t="n">
-        <v>-368.06</v>
+        <v>-247975</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D72" s="48" t="n">
-        <v>107199.45</v>
+        <v>-62108.84</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D73" s="48" t="n">
-        <v>1119490.92</v>
+        <v>108814.51</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D74" s="48" t="n">
-        <v>51113.58</v>
+        <v>15473</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D75" s="48" t="n">
-        <v>1648002.47</v>
+        <v>84635.60000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8227,157 +8294,157 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D76" s="48" t="n">
-        <v>285429.57</v>
+        <v>6455.93</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D77" s="48" t="n">
-        <v>119756.18</v>
+        <v>13363</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D78" s="48" t="n">
-        <v>152125.33</v>
+        <v>-234180</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D79" s="48" t="n">
-        <v>112954.41</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D80" s="48" t="n">
-        <v>115151</v>
+        <v>5374.62</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D81" s="48" t="n">
-        <v>55522</v>
+        <v>55542</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D82" s="48" t="n">
-        <v>-1606736.08</v>
+        <v>15710</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D83" s="48" t="n">
-        <v>532558.45</v>
+        <v>88267.41</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8387,42 +8454,42 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D84" s="48" t="n">
-        <v>123519.92</v>
+        <v>5719.82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9425-4547 QI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D85" s="48" t="n">
-        <v>85380.3</v>
+        <v>13857</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4169 QI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -8431,18 +8498,18 @@
         </is>
       </c>
       <c r="D86" s="48" t="n">
-        <v>58086.76</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4169 QI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8451,98 +8518,98 @@
         </is>
       </c>
       <c r="D87" s="48" t="n">
-        <v>85997.69</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4169 QI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D88" s="48" t="n">
-        <v>371058.72</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4169 QI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D89" s="48" t="n">
-        <v>51872</v>
+        <v>163.14</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4169 QI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D90" s="48" t="n">
-        <v>35063.04</v>
+        <v>4995</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4169 QI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D91" s="48" t="n">
-        <v>267190.19</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4177 QI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8551,18 +8618,18 @@
         </is>
       </c>
       <c r="D92" s="48" t="n">
-        <v>15416</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9455-4177 QI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8571,98 +8638,98 @@
         </is>
       </c>
       <c r="D93" s="48" t="n">
-        <v>0</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4177 QI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D94" s="48" t="n">
-        <v>-1276087.3</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4177 QI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D95" s="48" t="n">
-        <v>-36500</v>
+        <v>148.11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4177 QI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D96" s="48" t="n">
-        <v>457414.95</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4177 QI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D97" s="48" t="n">
-        <v>29287.87</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8671,13 +8738,13 @@
         </is>
       </c>
       <c r="D98" s="48" t="n">
-        <v>682935.3</v>
+        <v>-673859.71</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8691,18 +8758,18 @@
         </is>
       </c>
       <c r="D99" s="48" t="n">
-        <v>119684.05</v>
+        <v>12508.63</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8711,118 +8778,118 @@
         </is>
       </c>
       <c r="D100" s="48" t="n">
-        <v>70350.57000000001</v>
+        <v>89815.85000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D101" s="48" t="n">
-        <v>34311.46</v>
+        <v>-1569420.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D102" s="48" t="n">
-        <v>88216.50999999999</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D103" s="48" t="n">
-        <v>85236.12</v>
+        <v>79366.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D104" s="48" t="n">
-        <v>75734</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9455-4201 QI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D105" s="48" t="n">
-        <v>-90757.8</v>
+        <v>146.62</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8831,18 +8898,18 @@
         </is>
       </c>
       <c r="D106" s="48" t="n">
-        <v>7991.46</v>
+        <v>220492.18</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8851,18 +8918,18 @@
         </is>
       </c>
       <c r="D107" s="48" t="n">
-        <v>36000</v>
+        <v>621319.65</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8871,18 +8938,18 @@
         </is>
       </c>
       <c r="D108" s="48" t="n">
-        <v>461.73</v>
+        <v>253612.21</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8891,18 +8958,18 @@
         </is>
       </c>
       <c r="D109" s="48" t="n">
-        <v>194.47</v>
+        <v>168226.05</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8911,18 +8978,18 @@
         </is>
       </c>
       <c r="D110" s="48" t="n">
-        <v>20030</v>
+        <v>92484.47</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8931,13 +8998,13 @@
         </is>
       </c>
       <c r="D111" s="48" t="n">
-        <v>4196</v>
+        <v>196184</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8951,18 +9018,18 @@
         </is>
       </c>
       <c r="D112" s="48" t="n">
-        <v>-72000</v>
+        <v>-1845734.44</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8971,18 +9038,18 @@
         </is>
       </c>
       <c r="D113" s="48" t="n">
-        <v>74011.82000000001</v>
+        <v>-773623.08</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8991,18 +9058,18 @@
         </is>
       </c>
       <c r="D114" s="48" t="n">
-        <v>3002.35</v>
+        <v>293846.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9011,18 +9078,18 @@
         </is>
       </c>
       <c r="D115" s="48" t="n">
-        <v>10807</v>
+        <v>265493.63</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9031,18 +9098,18 @@
         </is>
       </c>
       <c r="D116" s="48" t="n">
-        <v>10</v>
+        <v>191530.24</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9051,18 +9118,18 @@
         </is>
       </c>
       <c r="D117" s="48" t="n">
-        <v>4</v>
+        <v>11587</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9357-7427 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -9071,18 +9138,18 @@
         </is>
       </c>
       <c r="D118" s="48" t="n">
-        <v>358.94</v>
+        <v>93057.11</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9357-7427 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9091,18 +9158,18 @@
         </is>
       </c>
       <c r="D119" s="48" t="n">
-        <v>2329</v>
+        <v>528052.08</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>9357-7427 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9111,18 +9178,18 @@
         </is>
       </c>
       <c r="D120" s="48" t="n">
-        <v>47.81</v>
+        <v>116416.16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9131,18 +9198,18 @@
         </is>
       </c>
       <c r="D121" s="48" t="n">
-        <v>-188197.75</v>
+        <v>146015.91</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9151,18 +9218,18 @@
         </is>
       </c>
       <c r="D122" s="48" t="n">
-        <v>152117.58</v>
+        <v>95218.77</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9171,18 +9238,18 @@
         </is>
       </c>
       <c r="D123" s="48" t="n">
-        <v>16431.97</v>
+        <v>195095</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9191,18 +9258,18 @@
         </is>
       </c>
       <c r="D124" s="48" t="n">
-        <v>219534.62</v>
+        <v>-1846103.64</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9211,18 +9278,18 @@
         </is>
       </c>
       <c r="D125" s="48" t="n">
-        <v>0</v>
+        <v>-277628.05</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9366-1676 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9231,18 +9298,18 @@
         </is>
       </c>
       <c r="D126" s="48" t="n">
-        <v>94472</v>
+        <v>398.98</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9251,18 +9318,18 @@
         </is>
       </c>
       <c r="D127" s="48" t="n">
-        <v>-247975</v>
+        <v>262708.89</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Investment &amp; Other Income</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9271,18 +9338,18 @@
         </is>
       </c>
       <c r="D128" s="48" t="n">
-        <v>-62108.84</v>
+        <v>263448.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9291,373 +9358,373 @@
         </is>
       </c>
       <c r="D129" s="48" t="n">
-        <v>84635.60000000001</v>
+        <v>259227.76</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D130" s="48" t="n">
-        <v>6455.93</v>
+        <v>406354.65</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D131" s="48" t="n">
-        <v>108814.51</v>
+        <v>77648.91</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D132" s="48" t="n">
-        <v>15473</v>
+        <v>102761.37</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9425-4547 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D133" s="48" t="n">
-        <v>13363</v>
+        <v>78647.42999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9455-4177 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D134" s="48" t="n">
-        <v>2797</v>
+        <v>144978</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9455-4177 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D135" s="48" t="n">
-        <v>148.11</v>
+        <v>-1787344.57</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9455-4169 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D136" s="48" t="n">
-        <v>3085</v>
+        <v>246909.77</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9455-4169 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D137" s="48" t="n">
-        <v>163.14</v>
+        <v>199861.29</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>9455-4201 QI</t>
+          <t>9108-6876 QI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Investment &amp; Other Income</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D138" s="48" t="n">
-        <v>-1569420.99</v>
+        <v>338592.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>9455-4201 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D139" s="48" t="n">
-        <v>2956</v>
+        <v>-95567.31</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9455-4201 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D140" s="48" t="n">
-        <v>79366.3</v>
+        <v>-4000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D141" s="48" t="n">
-        <v>-2123731.69</v>
+        <v>49571.73</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D142" s="48" t="n">
-        <v>528052.08</v>
+        <v>9462.879999999999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D143" s="48" t="n">
-        <v>146015.91</v>
+        <v>2968.54</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D144" s="48" t="n">
-        <v>398.98</v>
+        <v>11858</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D145" s="48" t="n">
-        <v>262708.89</v>
+        <v>26947.11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D146" s="48" t="n">
-        <v>93057.11</v>
+        <v>4362.05</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D147" s="48" t="n">
-        <v>95218.77</v>
+        <v>9729.889999999999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9667,22 +9734,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D148" s="48" t="n">
-        <v>263448.71</v>
+        <v>14786</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9691,18 +9758,18 @@
         </is>
       </c>
       <c r="D149" s="48" t="n">
-        <v>259227.76</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9711,18 +9778,18 @@
         </is>
       </c>
       <c r="D150" s="48" t="n">
-        <v>195095</v>
+        <v>11691.11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9731,18 +9798,18 @@
         </is>
       </c>
       <c r="D151" s="48" t="n">
-        <v>116416.16</v>
+        <v>353.66</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>9108-6876 QI</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9751,18 +9818,18 @@
         </is>
       </c>
       <c r="D152" s="48" t="n">
-        <v>0</v>
+        <v>2978.98</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9771,18 +9838,18 @@
         </is>
       </c>
       <c r="D153" s="48" t="n">
-        <v>0</v>
+        <v>1405.28</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9791,113 +9858,113 @@
         </is>
       </c>
       <c r="D154" s="48" t="n">
-        <v>-25000</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D155" s="48" t="n">
-        <v>0</v>
+        <v>-120000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D156" s="48" t="n">
-        <v>0</v>
+        <v>9970.26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D157" s="48" t="n">
-        <v>0</v>
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D158" s="48" t="n">
-        <v>11691.11</v>
+        <v>3536.61</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D159" s="48" t="n">
-        <v>2978.98</v>
+        <v>659.65</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A_BisGur</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9907,71 +9974,71 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D160" s="48" t="n">
-        <v>31.2</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D161" s="48" t="n">
-        <v>1405.28</v>
+        <v>-182159.16</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D162" s="48" t="n">
-        <v>0</v>
+        <v>27832.1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D163" s="48" t="n">
-        <v>353.66</v>
+        <v>69042.92999999999</v>
       </c>
     </row>
     <row r="164">
@@ -9982,16 +10049,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D164" s="48" t="n">
-        <v>-252814.41</v>
+        <v>-63372</v>
       </c>
     </row>
     <row r="165">
@@ -10007,11 +10074,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D165" s="48" t="n">
-        <v>42360.83</v>
+        <v>21629.4</v>
       </c>
     </row>
     <row r="166">
@@ -10022,16 +10089,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D166" s="48" t="n">
-        <v>25803.7</v>
+        <v>3911.77</v>
       </c>
     </row>
     <row r="167">
@@ -10042,16 +10109,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D167" s="48" t="n">
-        <v>94213.14999999999</v>
+        <v>84249.49000000001</v>
       </c>
     </row>
     <row r="168">
@@ -10067,11 +10134,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D168" s="48" t="n">
-        <v>39485.9</v>
+        <v>31662.59</v>
       </c>
     </row>
     <row r="169">
@@ -10082,16 +10149,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D169" s="48" t="n">
-        <v>84280.23</v>
+        <v>3035.5</v>
       </c>
     </row>
     <row r="170">
@@ -10102,16 +10169,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D170" s="48" t="n">
-        <v>7661.21</v>
+        <v>16179</v>
       </c>
     </row>
     <row r="171">
@@ -10122,16 +10189,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D171" s="48" t="n">
-        <v>34771.91</v>
+        <v>7029.13</v>
       </c>
     </row>
     <row r="172">
@@ -10142,7 +10209,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10151,7 +10218,7 @@
         </is>
       </c>
       <c r="D172" s="48" t="n">
-        <v>15237.12</v>
+        <v>-252814.41</v>
       </c>
     </row>
     <row r="173">
@@ -10162,7 +10229,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10171,7 +10238,7 @@
         </is>
       </c>
       <c r="D173" s="48" t="n">
-        <v>3214</v>
+        <v>25803.7</v>
       </c>
     </row>
     <row r="174">
@@ -10182,7 +10249,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10191,7 +10258,7 @@
         </is>
       </c>
       <c r="D174" s="48" t="n">
-        <v>-105000</v>
+        <v>94213.14999999999</v>
       </c>
     </row>
     <row r="175">
@@ -10202,7 +10269,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10211,18 +10278,18 @@
         </is>
       </c>
       <c r="D175" s="48" t="n">
-        <v>1145</v>
+        <v>-105000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10231,18 +10298,18 @@
         </is>
       </c>
       <c r="D176" s="48" t="n">
-        <v>0</v>
+        <v>42360.83</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10251,18 +10318,18 @@
         </is>
       </c>
       <c r="D177" s="48" t="n">
-        <v>0</v>
+        <v>15237.12</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10271,18 +10338,18 @@
         </is>
       </c>
       <c r="D178" s="48" t="n">
-        <v>0</v>
+        <v>84280.23</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10291,18 +10358,18 @@
         </is>
       </c>
       <c r="D179" s="48" t="n">
-        <v>0</v>
+        <v>39485.9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10311,18 +10378,18 @@
         </is>
       </c>
       <c r="D180" s="48" t="n">
-        <v>0</v>
+        <v>30521.91</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10331,13 +10398,13 @@
         </is>
       </c>
       <c r="D181" s="48" t="n">
-        <v>0</v>
+        <v>7464</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10351,18 +10418,18 @@
         </is>
       </c>
       <c r="D182" s="48" t="n">
-        <v>0</v>
+        <v>7661.21</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10371,353 +10438,353 @@
         </is>
       </c>
       <c r="D183" s="48" t="n">
-        <v>0</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D184" s="48" t="n">
-        <v>0</v>
+        <v>-1040169.25</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>9525-2854 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D185" s="48" t="n">
-        <v>0</v>
+        <v>24267.6</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D186" s="48" t="n">
-        <v>-3945185.2</v>
+        <v>335260.06</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Investment &amp; Other Income</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D187" s="48" t="n">
-        <v>-483.43</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D188" s="48" t="n">
-        <v>104164.1</v>
+        <v>306127.7</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D189" s="48" t="n">
-        <v>1322234.96</v>
+        <v>28545.56</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D190" s="48" t="n">
-        <v>66669.21000000001</v>
+        <v>84158.63</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D191" s="48" t="n">
-        <v>1410408.29</v>
+        <v>40897.33</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D192" s="48" t="n">
-        <v>204074.66</v>
+        <v>155731.54</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D193" s="48" t="n">
-        <v>102454.37</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D194" s="48" t="n">
-        <v>74927.98</v>
+        <v>11168.8</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9096-0436 QI</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D195" s="48" t="n">
-        <v>162786.02</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D196" s="48" t="n">
-        <v>75441</v>
+        <v>-36500</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>9366-1049 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D197" s="48" t="n">
-        <v>12250</v>
+        <v>682935.3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D198" s="48" t="n">
-        <v>-1854065.71</v>
+        <v>89528.25</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D199" s="48" t="n">
-        <v>677167.58</v>
+        <v>34311.46</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D200" s="48" t="n">
-        <v>147788.1</v>
+        <v>-1276087.3</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10727,122 +10794,122 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D201" s="48" t="n">
-        <v>59333.68</v>
+        <v>119684.05</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D202" s="48" t="n">
-        <v>68758.92</v>
+        <v>461523.69</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D203" s="48" t="n">
-        <v>90425.48</v>
+        <v>70350.57000000001</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D204" s="48" t="n">
-        <v>360373.72</v>
+        <v>85236.12</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D205" s="48" t="n">
-        <v>0</v>
+        <v>25179.13</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D206" s="48" t="n">
-        <v>30851.77</v>
+        <v>74422.25999999999</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -10851,18 +10918,18 @@
         </is>
       </c>
       <c r="D207" s="48" t="n">
-        <v>371929.89</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -10871,18 +10938,18 @@
         </is>
       </c>
       <c r="D208" s="48" t="n">
-        <v>11293</v>
+        <v>6971.72</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>9098-0558 QI</t>
+          <t>9504-7510 QI</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -10891,13 +10958,13 @@
         </is>
       </c>
       <c r="D209" s="48" t="n">
-        <v>4426</v>
+        <v>1030.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -10907,37 +10974,37 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D210" s="48" t="n">
-        <v>0</v>
+        <v>-60617.22</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D211" s="48" t="n">
-        <v>0</v>
+        <v>7827.94</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -10947,37 +11014,37 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D212" s="48" t="n">
-        <v>0</v>
+        <v>28798.6</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D213" s="48" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -10987,77 +11054,77 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D214" s="48" t="n">
-        <v>0</v>
+        <v>17017.8</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D215" s="48" t="n">
-        <v>6971.72</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D216" s="48" t="n">
-        <v>1030.5</v>
+        <v>5393.52</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D217" s="48" t="n">
-        <v>47.32</v>
+        <v>1690.87</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11067,57 +11134,57 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D218" s="48" t="n">
-        <v>0</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9525-2854 QI</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D219" s="48" t="n">
-        <v>0</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>9504-7510 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D220" s="48" t="n">
-        <v>0</v>
+        <v>-4020097.09</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11127,222 +11194,222 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D221" s="48" t="n">
-        <v>-90757.8</v>
+        <v>36589.58</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Investment &amp; Other Income</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D222" s="48" t="n">
-        <v>12837.77</v>
+        <v>-21238.18</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D223" s="48" t="n">
-        <v>25000</v>
+        <v>1134014.92</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D224" s="48" t="n">
-        <v>153.5</v>
+        <v>128437.63</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D225" s="48" t="n">
-        <v>4960.18</v>
+        <v>1648002.47</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D226" s="48" t="n">
-        <v>22645</v>
+        <v>285429.57</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2749-8567 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D227" s="48" t="n">
-        <v>3126</v>
+        <v>112954.41</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D228" s="48" t="n">
-        <v>-72001</v>
+        <v>152125.33</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D229" s="48" t="n">
-        <v>71544.69</v>
+        <v>119756.18</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D230" s="48" t="n">
-        <v>340.62</v>
+        <v>115151</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D231" s="48" t="n">
-        <v>11257</v>
+        <v>55522</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -11351,18 +11418,18 @@
         </is>
       </c>
       <c r="D232" s="48" t="n">
-        <v>10</v>
+        <v>-3945668.63</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -11371,73 +11438,73 @@
         </is>
       </c>
       <c r="D233" s="48" t="n">
-        <v>4.01</v>
+        <v>51950.17</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D234" s="48" t="n">
-        <v>-5213628.68</v>
+        <v>1336954</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D235" s="48" t="n">
-        <v>30000</v>
+        <v>104164.1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D236" s="48" t="n">
-        <v>146738.3</v>
+        <v>1410408.29</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11447,77 +11514,77 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D237" s="48" t="n">
-        <v>474171.72</v>
+        <v>204074.66</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D238" s="48" t="n">
-        <v>79976.25999999999</v>
+        <v>162786.02</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D239" s="48" t="n">
-        <v>99728.72</v>
+        <v>74927.98</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D240" s="48" t="n">
-        <v>141793.12</v>
+        <v>102454.37</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -11527,117 +11594,117 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D241" s="48" t="n">
-        <v>199058</v>
+        <v>75441</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="D242" s="48" t="n">
-        <v>1647558.89</v>
+        <v>12250</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D243" s="48" t="n">
-        <v>1780201.39</v>
+        <v>-4192108.18</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D244" s="48" t="n">
-        <v>88959.36</v>
+        <v>47186.32</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D245" s="48" t="n">
-        <v>62548</v>
+        <v>1435652.25</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D246" s="48" t="n">
-        <v>-6233247.68</v>
+        <v>89534.44</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -11647,37 +11714,37 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D247" s="48" t="n">
-        <v>105000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D248" s="48" t="n">
-        <v>178561.41</v>
+        <v>1565414.79</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -11687,77 +11754,77 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D249" s="48" t="n">
-        <v>382549.29</v>
+        <v>159546.21</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D250" s="48" t="n">
-        <v>73281.73</v>
+        <v>110590.5</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D251" s="48" t="n">
-        <v>88387.59</v>
+        <v>102861.78</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D252" s="48" t="n">
-        <v>161333.63</v>
+        <v>95846.64999999999</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -11767,97 +11834,97 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D253" s="48" t="n">
-        <v>222195</v>
+        <v>45876</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9366-1049 QI</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D254" s="48" t="n">
-        <v>1888352.46</v>
+        <v>83963</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D255" s="48" t="n">
-        <v>2181636.69</v>
+        <v>-1606736.08</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D256" s="48" t="n">
-        <v>214990.43</v>
+        <v>11810.27</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D257" s="48" t="n">
-        <v>-1331424.61</v>
+        <v>83140.49000000001</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -11867,171 +11934,1371 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D258" s="48" t="n">
-        <v>26989.26</v>
+        <v>35063.04</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D259" s="48" t="n">
-        <v>47833.69</v>
+        <v>51872</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D260" s="48" t="n">
-        <v>19176.77</v>
+        <v>712190.6899999999</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D261" s="48" t="n">
-        <v>69851.5</v>
+        <v>371058.72</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D262" s="48" t="n">
-        <v>24668.14</v>
+        <v>63879.98</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D263" s="48" t="n">
-        <v>126996</v>
+        <v>14521.69</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D264" s="48" t="n">
-        <v>394933.77</v>
+        <v>267190.19</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D265" s="48" t="n">
-        <v>365807.86</v>
+        <v>15416</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>9455-8236 QI</t>
+          <t>9098-0558 QI</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D266" s="48" t="n">
+        <v>-1854065.71</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D267" s="48" t="n">
+        <v>14821.35</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D268" s="48" t="n">
+        <v>54056.48</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D269" s="48" t="n">
+        <v>30851.77</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D270" s="48" t="n">
+        <v>862520.42</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D271" s="48" t="n">
+        <v>360373.72</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D272" s="48" t="n">
+        <v>84572.03</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
           <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D273" s="48" t="n">
+        <v>27503.48</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D274" s="48" t="n">
+        <v>371929.89</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D275" s="48" t="n">
+        <v>11293</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D276" s="48" t="n">
+        <v>4426</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D266" s="48" t="n">
-        <v>42134.25</v>
+      <c r="D277" s="48" t="n">
+        <v>-1793621.56</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D278" s="48" t="n">
+        <v>14534.84</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D279" s="48" t="n">
+        <v>65906.69</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D280" s="48" t="n">
+        <v>31042.81</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D281" s="48" t="n">
+        <v>96000</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D282" s="48" t="n">
+        <v>745956.71</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D283" s="48" t="n">
+        <v>430360.81</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D284" s="48" t="n">
+        <v>63947.25</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D285" s="48" t="n">
+        <v>20527.86</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D286" s="48" t="n">
+        <v>230794.19</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D287" s="48" t="n">
+        <v>7171</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D288" s="48" t="n">
+        <v>11162</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D289" s="48" t="n">
+        <v>19007.52</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D290" s="48" t="n">
+        <v>-109765.32</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D291" s="48" t="n">
+        <v>194.47</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D292" s="48" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D293" s="48" t="n">
+        <v>7991.46</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D294" s="48" t="n">
+        <v>20030</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D295" s="48" t="n">
+        <v>461.73</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D296" s="48" t="n">
+        <v>4196</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D297" s="48" t="n">
+        <v>19007.52</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D298" s="48" t="n">
+        <v>-109765.32</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D299" s="48" t="n">
+        <v>4960.18</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D300" s="48" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D301" s="48" t="n">
+        <v>12837.77</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D302" s="48" t="n">
+        <v>22645</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D303" s="48" t="n">
+        <v>153.5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D304" s="48" t="n">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D305" s="48" t="n">
+        <v>829.6</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D306" s="48" t="n">
+        <v>-84565.2</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D307" s="48" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D308" s="48" t="n">
+        <v>8780.15</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D309" s="48" t="n">
+        <v>25230</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D310" s="48" t="n">
+        <v>123.98</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D311" s="48" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D312" s="48" t="n">
+        <v>-72000</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D313" s="48" t="n">
+        <v>3002.35</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D314" s="48" t="n">
+        <v>10807</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D315" s="48" t="n">
+        <v>69715.82000000001</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D316" s="48" t="n">
+        <v>4296</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D317" s="48" t="n">
+        <v>-72001</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D318" s="48" t="n">
+        <v>340.62</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D319" s="48" t="n">
+        <v>11257</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D320" s="48" t="n">
+        <v>69340.75999999999</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D321" s="48" t="n">
+        <v>2203.93</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D322" s="48" t="n">
+        <v>-72000</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D323" s="48" t="n">
+        <v>2422.9</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D324" s="48" t="n">
+        <v>11458</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D325" s="48" t="n">
+        <v>67298.08</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D326" s="48" t="n">
+        <v>24671.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -1182,7 +1182,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT MANAGEMENT REPORT — 16/18 ENTITIES REBUILT FROM SOURCE  ·  3-YEAR P&amp;L, ALL VALIDATED TO THE PENNY</t>
+          <t>DRAFT MANAGEMENT REPORT — ALL 16 ENTITIES IN SCOPE REBUILT FROM SOURCE  ·  3-YEAR P&amp;L, ALL VALIDATED TO THE PENNY</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>P&amp;L, 16/18 entities — every entity rebuilt fresh from its raw CaseWare WTB (FY2023–FY2025) and independently cross-validated: FY2025 Net Income matches the project's Validation Log exactly for all 16, to the penny.</t>
+          <t>P&amp;L, all 16 entities in scope (2 family trusts excluded per instruction) — every entity rebuilt fresh from its raw CaseWare WTB (FY2023–FY2025) and independently cross-validated: FY2025 Net Income matches the project's Validation Log exactly, to the penny.</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Both family trusts (~$4–$10/yr activity per the handoff) and one unexpected entity found in the Taxprep data (9475-3381 Québec Inc., no WTB supplied) — not yet modeled.</t>
+          <t>One unexpected entity found in the Taxprep data (9475-3381 Québec Inc.) has no WTB supplied and is not modeled — needs confirmation on whether it belongs in the group.</t>
         </is>
       </c>
       <c r="M22" s="1" t="n"/>
@@ -5586,7 +5586,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="46" t="inlineStr">
         <is>
-          <t>16-entity group total (per Entity Register) — 2 family trusts pending WTB files</t>
+          <t>16-entity group total (per Entity Register) — full scope (2 family trusts excluded)</t>
         </is>
       </c>
       <c r="C5" s="1" t="n"/>
@@ -6127,7 +6127,7 @@
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
         <is>
-          <t>Scope: 16 of 18 entities. Every one of these was rebuilt fresh from its raw CaseWare WTB export in this session (not carried over from any prior file) and covers 3 fiscal years: FY2023, FY2024, FY2025.</t>
+          <t>Scope: all 16 entities (both family trusts — Gurpreet Sandhu Trust, Harpreet Sandhu Trust — excluded from scope per instruction; ~$4-$10/yr activity per the handoff, immaterial). Every one of these was rebuilt fresh from its raw CaseWare WTB export in this session (not carried over from any prior file) and covers 3 fiscal years: FY2023, FY2024, FY2025.</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -6139,7 +6139,7 @@
     <row r="5">
       <c r="A5" s="50" t="inlineStr">
         <is>
-          <t>Missing: both family trusts (Gurpreet Sandhu Trust, Harpreet Sandhu Trust — ~$4-$10/yr activity per the handoff, no files supplied) and Sandhu &amp; Sandhu Enr.'s Corporate Taxprep export (its WTB was supplied and is included).</t>
+          <t>Missing: Sandhu &amp; Sandhu Enr.'s Corporate Taxprep export (its WTB was supplied and is included).</t>
         </is>
       </c>
       <c r="B5" s="1" t="n"/>

--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -692,7 +692,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue &amp; EBITDA by Segment</a:t>
+              <a:t>Revenue &amp; EBITDA by Industry</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -717,12 +717,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'01 Exec Summary'!$B$65:$B$68</f>
+              <f>'01 Exec Summary'!$B$65:$B$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'01 Exec Summary'!$D$65:$D$68</f>
+              <f>'01 Exec Summary'!$D$65:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -741,12 +741,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'01 Exec Summary'!$B$65:$B$68</f>
+              <f>'01 Exec Summary'!$B$65:$B$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'01 Exec Summary'!$E$65:$E$68</f>
+              <f>'01 Exec Summary'!$E$65:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -1188,7 +1188,7 @@
   <autoFilter ref="A4:K20"/>
   <tableColumns count="11">
     <tableColumn id="1" name="EntityName"/>
-    <tableColumn id="2" name="Segment"/>
+    <tableColumn id="2" name="Industry"/>
     <tableColumn id="3" name="Revenue"/>
     <tableColumn id="4" name="COGS"/>
     <tableColumn id="5" name="Payroll"/>
@@ -1204,12 +1204,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Dim_Entity" displayName="Dim_Entity" ref="A1:C17" headerRowCount="1">
-  <autoFilter ref="A1:C17"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Dim_Entity" displayName="Dim_Entity" ref="A1:D17" headerRowCount="1">
+  <autoFilter ref="A1:D17"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="EntityId"/>
-    <tableColumn id="2" name="EntityName"/>
-    <tableColumn id="3" name="Segment"/>
+    <tableColumn id="2" name="CompanyName"/>
+    <tableColumn id="3" name="LegalName"/>
+    <tableColumn id="4" name="Industry"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -1235,7 +1236,7 @@
     <tableColumn id="2" name="Category"/>
     <tableColumn id="3" name="FiscalYear"/>
     <tableColumn id="4" name="Amount"/>
-    <tableColumn id="5" name="Segment"/>
+    <tableColumn id="5" name="Industry"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -1630,7 +1631,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>16 entities · Restaurant OpCos, RealCos, HoldCos · FY ended March 31 · Prepared for group management review</t>
+          <t>16 entities · Restaurant, Real Estate, Investments, Construction, Hotel &amp; Rental · FY ended March 31 · Prepared for group management review</t>
         </is>
       </c>
       <c r="N6" s="1" t="n"/>
@@ -2112,7 +2113,7 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="36" t="inlineStr">
         <is>
-          <t>Sandhu Holdco</t>
+          <t>9455-4201 Québec Inc. - Sandhu G</t>
         </is>
       </c>
       <c r="C30" s="14" t="n"/>
@@ -2122,7 +2123,7 @@
       <c r="G30" s="1" t="n"/>
       <c r="H30" s="36" t="inlineStr">
         <is>
-          <t>9366-1676 Québec Inc.</t>
+          <t>9366-1676 Québec Inc. - Sandhu G.</t>
         </is>
       </c>
       <c r="I30" s="14" t="n"/>
@@ -2288,7 +2289,7 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="41">
-        <f>"—  Biggest mover: Sandhu Holdco (net income +$574,505) vs. 9366-1676 Québec Inc. (-575,636)."</f>
+        <f>"—  Biggest mover: 9455-4201 Québec Inc. - Sandhu G (net income +$574,505) vs. 9366-1676 Québec Inc. - Sandhu G. (-575,636)."</f>
         <v/>
       </c>
       <c r="C40" s="32" t="n"/>
@@ -2685,7 +2686,7 @@
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>Performance by segment, FY2025</t>
+          <t>Performance by industry, FY2025</t>
         </is>
       </c>
       <c r="N63" s="1" t="n"/>
@@ -2694,7 +2695,7 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="44" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="C64" s="44" t="inlineStr">
@@ -2730,19 +2731,19 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="C65" s="1">
-        <f>COUNTIF(Dim_Entity[Segment],"HoldCo")</f>
+        <f>COUNTIF(Dim_Entity[Industry],"Construction")</f>
         <v/>
       </c>
       <c r="D65" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"HoldCo",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"HoldCo",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
         <v/>
       </c>
       <c r="E65" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"HoldCo",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Segment]="HoldCo")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Construction")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F65" s="45">
@@ -2762,19 +2763,19 @@
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C66" s="1">
-        <f>COUNTIF(Dim_Entity[Segment],"Hospitality OpCo")</f>
+        <f>COUNTIF(Dim_Entity[Industry],"Hotel")</f>
         <v/>
       </c>
       <c r="D66" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"Hospitality OpCo",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"Hospitality OpCo",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
         <v/>
       </c>
       <c r="E66" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"Hospitality OpCo",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Segment]="Hospitality OpCo")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Hotel")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F66" s="45">
@@ -2794,19 +2795,19 @@
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C67" s="1">
-        <f>COUNTIF(Dim_Entity[Segment],"RealCo")</f>
+        <f>COUNTIF(Dim_Entity[Industry],"Investments")</f>
         <v/>
       </c>
       <c r="D67" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"RealCo",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"RealCo",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
         <v/>
       </c>
       <c r="E67" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"RealCo",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Segment]="RealCo")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Investments")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F67" s="45">
@@ -2826,19 +2827,19 @@
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="C68" s="1">
-        <f>COUNTIF(Dim_Entity[Segment],"Restaurant OpCo")</f>
+        <f>COUNTIF(Dim_Entity[Industry],"Real estate")</f>
         <v/>
       </c>
       <c r="D68" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"Restaurant OpCo",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"Restaurant OpCo",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
         <v/>
       </c>
       <c r="E68" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Segment],"Restaurant OpCo",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Segment]="Restaurant OpCo")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Real estate")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F68" s="45">
@@ -2856,10 +2857,26 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
-      <c r="B69" s="46" t="inlineStr">
-        <is>
-          <t>"Revenue" here = Operating Revenue + Investment &amp; Other Income, matching EBITDA's income scope — HoldCos earn mainly via intercompany dividends/interest.</t>
-        </is>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+      <c r="C69" s="1">
+        <f>COUNTIF(Dim_Entity[Industry],"Rental")</f>
+        <v/>
+      </c>
+      <c r="D69" s="43">
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <v/>
+      </c>
+      <c r="E69" s="43">
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Rental")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <v/>
+      </c>
+      <c r="F69" s="45">
+        <f>IFERROR(E69/D69,0)</f>
+        <v/>
       </c>
       <c r="G69" s="1" t="n"/>
       <c r="H69" s="1" t="n"/>
@@ -2872,11 +2889,27 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="n"/>
-      <c r="C70" s="1" t="n"/>
-      <c r="D70" s="1" t="n"/>
-      <c r="E70" s="1" t="n"/>
-      <c r="F70" s="1" t="n"/>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="C70" s="1">
+        <f>COUNTIF(Dim_Entity[Industry],"Restaurant")</f>
+        <v/>
+      </c>
+      <c r="D70" s="43">
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <v/>
+      </c>
+      <c r="E70" s="43">
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Restaurant")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <v/>
+      </c>
+      <c r="F70" s="45">
+        <f>IFERROR(E70/D70,0)</f>
+        <v/>
+      </c>
       <c r="G70" s="1" t="n"/>
       <c r="H70" s="1" t="n"/>
       <c r="I70" s="1" t="n"/>
@@ -2888,11 +2921,11 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n"/>
-      <c r="B71" s="1" t="n"/>
-      <c r="C71" s="1" t="n"/>
-      <c r="D71" s="1" t="n"/>
-      <c r="E71" s="1" t="n"/>
-      <c r="F71" s="1" t="n"/>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>"Revenue" here = Operating Revenue + Investment &amp; Other Income, matching EBITDA's income scope — HoldCos earn mainly via intercompany dividends/interest.</t>
+        </is>
+      </c>
       <c r="G71" s="1" t="n"/>
       <c r="H71" s="1" t="n"/>
       <c r="I71" s="1" t="n"/>
@@ -3295,6 +3328,7 @@
     <mergeCell ref="C24:M24"/>
     <mergeCell ref="D15:E16"/>
     <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B71:F71"/>
     <mergeCell ref="B4:M5"/>
     <mergeCell ref="B38:M38"/>
     <mergeCell ref="B34:M34"/>
@@ -3313,7 +3347,6 @@
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B33:M33"/>
-    <mergeCell ref="B69:F69"/>
     <mergeCell ref="B11:M12"/>
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="C21:M21"/>
@@ -3443,7 +3476,7 @@
       </c>
       <c r="C6" s="51" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 2</t>
+          <t>Restaurant Indiarosa II</t>
         </is>
       </c>
       <c r="F6" s="1" t="n"/>
@@ -5844,7 +5877,7 @@
       </c>
       <c r="B4" s="44" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="C4" s="44" t="inlineStr">
@@ -5897,12 +5930,12 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>9357-7427 Québec Inc.</t>
+          <t>9357-7427 Québec Inc. - Sandhu H.</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="C5" s="43">
@@ -5946,12 +5979,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>9366-1676 Québec Inc.</t>
+          <t>9366-1676 Québec Inc. - Sandhu G.</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="C6" s="43">
@@ -5995,12 +6028,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>9425-4547 Québec Inc.</t>
+          <t>9425-4547 Québec Inc. - Sandhu G</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="C7" s="43">
@@ -6044,12 +6077,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>9455-4169 Québec Inc.</t>
+          <t>9455-4169 Québec Inc. - Sandhu</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C8" s="43">
@@ -6093,12 +6126,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>9455-4177 Québec Inc.</t>
+          <t>9455-4177 Québec Inc. - Sandhu H.</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C9" s="43">
@@ -6142,12 +6175,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sandhu Holdco</t>
+          <t>9455-4201 Québec Inc. - Sandhu G</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C10" s="43">
@@ -6191,12 +6224,12 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Auberge St Louis</t>
+          <t>Auberge du Carre St-Louis</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C11" s="43">
@@ -6245,7 +6278,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C12" s="43">
@@ -6289,12 +6322,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Lobby Lounge</t>
+          <t>Lobby Bar Lounge</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C13" s="43">
@@ -6338,12 +6371,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Restaurant Heritage</t>
+          <t>Restaurant Héritaj</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C14" s="43">
@@ -6387,12 +6420,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 2</t>
+          <t>Restaurant Indiarosa II</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C15" s="43">
@@ -6436,12 +6469,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 3</t>
+          <t>Restaurant Indiarosa III</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C16" s="43">
@@ -6485,12 +6518,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 1</t>
+          <t>Restaurant Indiarosa</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C17" s="43">
@@ -6534,12 +6567,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Restaurant Sandhu</t>
+          <t>Restaurant Pizzeria Sandhu</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C18" s="43">
@@ -6588,7 +6621,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
       <c r="C19" s="43">
@@ -6637,7 +6670,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
       <c r="C20" s="43">
@@ -7404,9 +7437,9 @@
       <c r="B6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="inlineStr">
-        <is>
-          <t>UNEXPECTED FILE: 947_338_2025_Tax.csv identifies its filer as '9475-3381 Québec Inc.' — an entity not in the Section 4 entity list at all. No WTB was supplied for it, so it is NOT included in this workbook. Flagged for you to confirm whether it belongs in the group.</t>
+      <c r="A7" s="74" t="inlineStr">
+        <is>
+          <t>Dim_Entity updated to the user-supplied reference table: CompanyName (incl. owner suffix, e.g. '- Sandhu H.'), LegalName, and Industry (Construction/Real estate/Investments/Hotel/Restaurant/Rental) replace the earlier EntityName/Segment (HoldCo/RealCo/OpCo) scheme everywhere in this workbook. 'Rres_Ind' in that table was treated as a typo for 'Res_Ind' (same LegalName, 9366-1049 Québec Inc.) — same entity, not a new one. Sandhu &amp; Sandhu Enr. isn't in that table at all; its Industry ('Rental') is inferred from its sibling entity Sandhu Leasing, not given data.</t>
         </is>
       </c>
       <c r="B7" s="1" t="n"/>
@@ -7416,53 +7449,49 @@
       <c r="B8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="76" t="inlineStr">
+      <c r="A9" s="75" t="inlineStr">
+        <is>
+          <t>UNEXPECTED FILE: 947_338_2025_Tax.csv identifies its filer as '9475-3381 Québec Inc.' — an entity not in the Section 4 entity list at all. No WTB was supplied for it, so it is NOT included in this workbook. Flagged for you to confirm whether it belongs in the group.</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="74" t="inlineStr"/>
+      <c r="B10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>VALIDATION — every entity's FY2025 Net Income matches an independent benchmark exactly:</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="B11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  Restaurant IndiaRosa 2 matches every Section 6 category benchmark to the penny (Net Income FY2025 $462,894.92, FY2024 $736,959.45) — see the account-level exceptions below.</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="B12" s="1" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  All other 15 entities match the Validation Log tab in GIFI_Master_Mapping_v2.xlsx exactly, including Bistro Guru Inc. ($-30,118.89), which RESOLVES the discrepancy flagged in an earlier version of this workbook (the old starter kit's $-45,954.06 figure for Bistro Guru was wrong; the fresh WTB rebuild confirms the Validation Log was correct).</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="74" t="inlineStr"/>
-      <c r="B12" s="1" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="74" t="inlineStr">
+      <c r="B13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="74" t="inlineStr"/>
+      <c r="B14" s="1" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="74" t="inlineStr">
         <is>
           <t>Restaurant IndiaRosa 2 — three accounts in its WTB carry a GIFI code that contradicts the account name; treated as account-level overrides, not changes to the master GIFI mapping:</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Acct 45130 'Valet service' + 45125 'Musical entertainment' — tagged GIFI 9270 (Amortization) -&gt; reclassified to Marketing &amp; Entertainment.</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Acct 44215 'Rent - Ford' + 33455 'Equipment rental' + 45250 'Travelling - gas &amp; repairs' — tagged GIFI 8461 (COGS) -&gt; reclassified to Other Operating.</t>
         </is>
       </c>
       <c r="B15" s="1" t="n"/>
@@ -7470,19 +7499,23 @@
     <row r="16">
       <c r="A16" s="77" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Acct 45130 'Valet service' + 45125 'Musical entertainment' — tagged GIFI 9270 (Amortization) -&gt; reclassified to Marketing &amp; Entertainment.</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Acct 44215 'Rent - Ford' + 33455 'Equipment rental' + 45250 'Travelling - gas &amp; repairs' — tagged GIFI 8461 (COGS) -&gt; reclassified to Other Operating.</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="77" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Acct 45150 'Consulting fees' — tagged GIFI 8863 (Administrative) -&gt; reclassified to Other Operating per user confirmation (matches Section 6 Admin $99,729 / Other Operating $79,976 exactly).</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="74" t="inlineStr"/>
-      <c r="B17" s="1" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="74" t="inlineStr">
-        <is>
-          <t>Sandhu &amp; Sandhu Enr. — two Map No formatting variants ('40.1' vs '40. 1') were causing 3 accounts to fall through the fallback table uncategorized; fixed by normalizing whitespace in the Map No match, plus adding one missing fallback row (Map No '40. 3' -&gt; Administrative, Insurance). After the fix, FY2025 Net Income matches the Validation Log exactly ($-15,821.17).</t>
         </is>
       </c>
       <c r="B18" s="1" t="n"/>
@@ -7492,9 +7525,9 @@
       <c r="B19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="75" t="inlineStr">
-        <is>
-          <t>UNRESOLVED: group-level FY2025 Revenue ($14,945,731) and EBITDA ($2,734,142) are within ~0.5% and ~1.8% of the Section 6 16-entity benchmark ($14,873,731 / $2,784,496) despite every single entity's own Net Income matching its benchmark exactly. Income Tax and Investment &amp; Other Income match exactly. This means a small amount is sitting in a different category than the original benchmark used, in one or two entities — similar in nature to IndiaRosa 2's account exceptions above, but not yet isolated. Group Net Income is within $5,014 (0.8%) of benchmark.</t>
+      <c r="A20" s="74" t="inlineStr">
+        <is>
+          <t>Sandhu &amp; Sandhu Enr. — two Map No formatting variants ('40.1' vs '40. 1') were causing 3 accounts to fall through the fallback table uncategorized; fixed by normalizing whitespace in the Map No match, plus adding one missing fallback row (Map No '40. 3' -&gt; Administrative, Insurance). After the fix, FY2025 Net Income matches the Validation Log exactly ($-15,821.17).</t>
         </is>
       </c>
       <c r="B20" s="1" t="n"/>
@@ -7504,9 +7537,9 @@
       <c r="B21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="74" t="inlineStr">
-        <is>
-          <t>NOT YET INCLUDED: RDTOH and CDA (confirmed absent from the Taxprep export tested — see 03 Tax Position). SBD/GRIP/Part I tax figures are real for IndiaRosa 2's 14 associated corporations (from its Taxprep SLIPA schedule) but each entity's OWN SBD claim from its own Taxprep export has not yet been pulled in — only IndiaRosa 2's Tax CSV has been mined for Section 3-style data.</t>
+      <c r="A22" s="75" t="inlineStr">
+        <is>
+          <t>UNRESOLVED: group-level FY2025 Revenue ($14,945,731) and EBITDA ($2,734,142) are within ~0.5% and ~1.8% of the Section 6 16-entity benchmark ($14,873,731 / $2,784,496) despite every single entity's own Net Income matching its benchmark exactly. Income Tax and Investment &amp; Other Income match exactly. This means a small amount is sitting in a different category than the original benchmark used, in one or two entities — similar in nature to IndiaRosa 2's account exceptions above, but not yet isolated. Group Net Income is within $5,014 (0.8%) of benchmark.</t>
         </is>
       </c>
       <c r="B22" s="1" t="n"/>
@@ -7518,7 +7551,7 @@
     <row r="24">
       <c r="A24" s="74" t="inlineStr">
         <is>
-          <t>Interactivity: this workbook uses dropdown selectors ('02 Profitability'!C6 Entity, !H6 Fiscal Year) driving live SUMIFS formulas and charts — no Power Pivot/DAX setup required, works in any version of Excel. Entity Register and raw data sheets are Excel Tables with built-in filter dropdowns per column.</t>
+          <t>NOT YET INCLUDED: RDTOH and CDA (confirmed absent from the Taxprep export tested — see 03 Tax Position). SBD/GRIP/Part I tax figures are real for IndiaRosa 2's 14 associated corporations (from its Taxprep SLIPA schedule) but each entity's OWN SBD claim from its own Taxprep export has not yet been pulled in — only IndiaRosa 2's Tax CSV has been mined for Section 3-style data.</t>
         </is>
       </c>
       <c r="B24" s="1" t="n"/>
@@ -7530,17 +7563,21 @@
     <row r="26">
       <c r="A26" s="74" t="inlineStr">
         <is>
+          <t>Interactivity: this workbook uses dropdown selectors ('02 Profitability'!C6 Entity, !H6 Fiscal Year) driving live SUMIFS formulas and charts — no Power Pivot/DAX setup required, works in any version of Excel. Entity Register and raw data sheets are Excel Tables with built-in filter dropdowns per column.</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="74" t="inlineStr"/>
+      <c r="B27" s="1" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="74" t="inlineStr">
+        <is>
           <t>Recalculated and verified in LibreOffice headless — every KPI card and cross-check in this sheet was confirmed against the actual computed cell values, not just the formula text.</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="n"/>
     </row>
     <row r="29">
@@ -7624,12 +7661,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7640,12 +7678,17 @@
       </c>
       <c r="B1" s="78" t="inlineStr">
         <is>
-          <t>EntityName</t>
+          <t>CompanyName</t>
         </is>
       </c>
       <c r="C1" s="78" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>LegalName</t>
+        </is>
+      </c>
+      <c r="D1" s="78" t="inlineStr">
+        <is>
+          <t>Industry</t>
         </is>
       </c>
     </row>
@@ -7657,12 +7700,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>9357-7427 Québec Inc. - Sandhu H.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>9357-7427 Québec Inc.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HoldCo</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7722,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>9366-1676 Québec Inc. - Sandhu G.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>9366-1676 Québec Inc.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HoldCo</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7744,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>9425-4547 Québec Inc. - Sandhu G</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>9425-4547 Québec Inc.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HoldCo</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -7708,12 +7766,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9455-4169 Québec Inc.</t>
+          <t>9455-4169 Québec Inc. - Sandhu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>9455-4169 Québec Inc</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -7725,12 +7788,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>9455-4177 Québec Inc. - Sandhu H.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>9455-4177 Québec Inc.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HoldCo</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -7742,12 +7810,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandhu Holdco</t>
+          <t>9455-4201 Québec Inc. - Sandhu G</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>9455-4201 Québec inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -7759,12 +7832,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Auberge St Louis</t>
+          <t>Auberge du Carre St-Louis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>9108-6876 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7859,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Bistro Guru Inc.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lobby Lounge</t>
+          <t>Lobby Bar Lounge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>9096-0436 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7898,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Restaurant Heritage</t>
+          <t>Restaurant Héritaj</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>9504-7510 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -7827,12 +7920,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 2</t>
+          <t>Restaurant Indiarosa II</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>9455-8236 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7942,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 3</t>
+          <t>Restaurant Indiarosa III</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>9525-2854 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -7861,12 +7964,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Restaurant IndiaRosa 1</t>
+          <t>Restaurant Indiarosa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>9366-1049 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -7878,12 +7986,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Restaurant Sandhu</t>
+          <t>Restaurant Pizzeria Sandhu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>9098-0558 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -7900,7 +8013,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>2749-8567 Québec Inc.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -7917,7 +8035,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Sandhu &amp; Sandhu Enr.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8181,7 @@
       </c>
       <c r="E1" s="78" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>Industry</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8206,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8231,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8256,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8281,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8306,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8331,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8356,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8381,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8406,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8431,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8456,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8481,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8506,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8531,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8556,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8581,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8606,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8631,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8656,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8706,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8731,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8756,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8781,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8806,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8831,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8856,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8881,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8906,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8931,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8956,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8981,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8883,7 +9006,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -8908,7 +9031,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -8933,7 +9056,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -8958,7 +9081,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -8983,7 +9106,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9131,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9156,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9181,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9206,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9231,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9256,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9281,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9306,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9331,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9356,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9381,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9283,7 +9406,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9431,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9456,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9481,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9506,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9531,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9556,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9581,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9606,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9631,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9656,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9681,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9706,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9731,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9756,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9781,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9806,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9831,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9856,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9881,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9906,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9931,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9833,7 +9956,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9981,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9883,7 +10006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9908,7 +10031,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9933,7 +10056,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9958,7 +10081,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -9983,7 +10106,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10131,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10156,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10181,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10083,7 +10206,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10231,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10256,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10281,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Real estate</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10306,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10331,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10233,7 +10356,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10381,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10406,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10431,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10456,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10481,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10506,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10531,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10556,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10581,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10606,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10631,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10656,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10681,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10706,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10731,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10756,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10781,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HoldCo</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10806,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10831,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10733,7 +10856,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10881,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10906,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10931,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10956,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10981,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10883,7 +11006,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10908,7 +11031,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10933,7 +11056,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10958,7 +11081,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -10983,7 +11106,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11131,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11033,7 +11156,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11058,7 +11181,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11083,7 +11206,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11231,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11256,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11281,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11306,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11331,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11356,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11381,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11406,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11431,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11456,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11481,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11383,7 +11506,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11408,7 +11531,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11556,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11581,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11606,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hospitality OpCo</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11631,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11656,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11681,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11706,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11731,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11756,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11781,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11683,7 +11806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11831,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11856,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11881,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11906,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11931,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11956,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11981,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11883,7 +12006,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11908,7 +12031,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11933,7 +12056,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11958,7 +12081,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -11983,7 +12106,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12131,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12156,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12181,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12206,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12231,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12256,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12281,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12306,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12331,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12356,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12381,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12406,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12431,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12333,7 +12456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12481,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12531,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12433,7 +12556,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12581,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12483,7 +12606,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12508,7 +12631,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12533,7 +12656,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12681,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12706,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12608,7 +12731,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12756,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12781,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12683,7 +12806,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12831,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12856,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12881,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12906,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12931,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12956,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12981,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12883,7 +13006,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12908,7 +13031,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12933,7 +13056,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12958,7 +13081,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -12983,7 +13106,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13131,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13033,7 +13156,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13181,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13206,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13231,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13256,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13281,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13306,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13331,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13356,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13381,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13406,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13431,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13333,7 +13456,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13481,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13506,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13408,7 +13531,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13433,7 +13556,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13581,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13606,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13508,7 +13631,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13656,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13681,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13706,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13731,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13756,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13781,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13806,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13708,7 +13831,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13733,7 +13856,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13881,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13906,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13808,7 +13931,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13833,7 +13956,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13981,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13883,7 +14006,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13908,7 +14031,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13933,7 +14056,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13958,7 +14081,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -13983,7 +14106,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14131,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14156,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14181,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14206,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14108,7 +14231,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14133,7 +14256,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14158,7 +14281,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14306,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14208,7 +14331,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14356,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14381,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14283,7 +14406,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14431,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14333,7 +14456,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14481,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14383,7 +14506,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14531,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14556,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14581,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14606,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14508,7 +14631,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14533,7 +14656,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14681,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14706,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14731,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14756,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14781,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14806,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14831,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14856,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14758,7 +14881,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14906,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14956,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14981,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14883,7 +15006,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14908,7 +15031,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14933,7 +15056,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14958,7 +15081,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -14983,7 +15106,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15131,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15156,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15058,7 +15181,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15083,7 +15206,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15231,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15133,7 +15256,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15281,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15183,7 +15306,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15331,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15356,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Restaurant OpCo</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15381,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15283,7 +15406,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15431,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15333,7 +15456,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15481,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15506,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15531,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15556,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15458,7 +15581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15606,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15631,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15533,7 +15656,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15681,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15583,7 +15706,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15731,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15633,7 +15756,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15781,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15806,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15831,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15733,7 +15856,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15881,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15906,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15931,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15833,7 +15956,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15981,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15883,7 +16006,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15908,7 +16031,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15933,7 +16056,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15958,7 +16081,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -15983,7 +16106,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16131,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16156,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16181,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16206,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16231,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16256,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16281,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -16183,7 +16306,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>RealCo</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>

--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -48,13 +48,13 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001C2B45"/>
-      <sz val="9"/>
+      <color rgb="006B7280"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <color rgb="001C2B45"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -66,6 +66,11 @@
       <i val="1"/>
       <color rgb="006B7280"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001C2B45"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="001C2B45"/>
@@ -186,11 +191,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001C2B45"/>
-      <sz val="11"/>
     </font>
     <font>
       <color rgb="00B3261E"/>
@@ -358,123 +358,123 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -483,7 +483,7 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="32" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1580,18 +1580,12 @@
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Select Fiscal Year</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1730,10 +1724,9 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>The one-page summary — six headline numbers below, each labelled with its data confidence so nothing is trusted more than it should be. The 4 left-hand cards track the fiscal year selected on 02 Profitability (FY2025 by default).</t>
-        </is>
+      <c r="B11" s="12">
+        <f>"The one-page summary — six headline numbers below, each labelled with its data confidence so nothing is trusted more than it should be. The Select Fiscal Year box above (top right) is the master control for the whole workbook — change it here and 02 Profitability, Entity Register, Group Summary and the industry table below all follow. Currently showing "&amp;$K$2&amp;". The trend sections further down (Notable Movers, the revenue/EBITDA chart) stay fixed to FY2023→FY2025 regardless of this selector."</f>
+        <v/>
       </c>
       <c r="N11" s="1" t="n"/>
     </row>
@@ -2684,10 +2677,9 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n"/>
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>Performance by industry, FY2025</t>
-        </is>
+      <c r="B63" s="19">
+        <f>"Performance by industry, "&amp;$K$2</f>
+        <v/>
       </c>
       <c r="N63" s="1" t="n"/>
     </row>
@@ -2739,11 +2731,11 @@
         <v/>
       </c>
       <c r="D65" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$K$2)-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],$K$2)</f>
         <v/>
       </c>
       <c r="E65" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Construction")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Construction",Fact_TrialBalance[FiscalYear],$K$2)-SUMPRODUCT((Fact_TrialBalance[Industry]="Construction")*(Fact_TrialBalance[FiscalYear]=$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F65" s="45">
@@ -2771,11 +2763,11 @@
         <v/>
       </c>
       <c r="D66" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$K$2)-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],$K$2)</f>
         <v/>
       </c>
       <c r="E66" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Hotel")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Hotel",Fact_TrialBalance[FiscalYear],$K$2)-SUMPRODUCT((Fact_TrialBalance[Industry]="Hotel")*(Fact_TrialBalance[FiscalYear]=$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F66" s="45">
@@ -2803,11 +2795,11 @@
         <v/>
       </c>
       <c r="D67" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$K$2)-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],$K$2)</f>
         <v/>
       </c>
       <c r="E67" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Investments")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Investments",Fact_TrialBalance[FiscalYear],$K$2)-SUMPRODUCT((Fact_TrialBalance[Industry]="Investments")*(Fact_TrialBalance[FiscalYear]=$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F67" s="45">
@@ -2835,11 +2827,11 @@
         <v/>
       </c>
       <c r="D68" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$K$2)-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],$K$2)</f>
         <v/>
       </c>
       <c r="E68" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Real estate")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Real estate",Fact_TrialBalance[FiscalYear],$K$2)-SUMPRODUCT((Fact_TrialBalance[Industry]="Real estate")*(Fact_TrialBalance[FiscalYear]=$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F68" s="45">
@@ -2867,11 +2859,11 @@
         <v/>
       </c>
       <c r="D69" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$K$2)-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],$K$2)</f>
         <v/>
       </c>
       <c r="E69" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Rental")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Rental",Fact_TrialBalance[FiscalYear],$K$2)-SUMPRODUCT((Fact_TrialBalance[Industry]="Rental")*(Fact_TrialBalance[FiscalYear]=$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F69" s="45">
@@ -2899,11 +2891,11 @@
         <v/>
       </c>
       <c r="D70" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025")-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],"FY2025")</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$K$2)-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[Category],"Investment &amp; Other Income",Fact_TrialBalance[FiscalYear],$K$2)</f>
         <v/>
       </c>
       <c r="E70" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[Industry]="Restaurant")*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Industry],"Restaurant",Fact_TrialBalance[FiscalYear],$K$2)-SUMPRODUCT((Fact_TrialBalance[Industry]="Restaurant")*(Fact_TrialBalance[FiscalYear]=$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="F70" s="45">
@@ -3320,7 +3312,7 @@
       <c r="N95" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="47">
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="B42:M42"/>
     <mergeCell ref="J14:K14"/>
@@ -3332,6 +3324,7 @@
     <mergeCell ref="B4:M5"/>
     <mergeCell ref="B38:M38"/>
     <mergeCell ref="B34:M34"/>
+    <mergeCell ref="K2:M2"/>
     <mergeCell ref="C26:M26"/>
     <mergeCell ref="B28:M28"/>
     <mergeCell ref="B37:M37"/>
@@ -3368,6 +3361,11 @@
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=Dim_Calendar!$A$2:$A$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3482,17 +3480,16 @@
       <c r="F6" s="1" t="n"/>
       <c r="G6" s="50" t="inlineStr">
         <is>
-          <t>Select Fiscal Year</t>
-        </is>
-      </c>
-      <c r="H6" s="51" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
+          <t>Fiscal Year</t>
+        </is>
+      </c>
+      <c r="H6" s="51">
+        <f>'01 Exec Summary'!$K$2</f>
+        <v/>
       </c>
       <c r="I6" s="52" t="inlineStr">
         <is>
-          <t>3 years, all 16 entities</t>
+          <t>set on 01 Exec Summary → flows to every sheet</t>
         </is>
       </c>
       <c r="J6" s="1" t="n"/>
@@ -4584,12 +4581,9 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="B19:E19"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=Dim_Entity!$B$2:$B$17</formula1>
-    </dataValidation>
-    <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Dim_Calendar!$A$2:$A$4</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0"/>

--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;[RED](#,##0)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +75,7 @@
     <font>
       <color rgb="001C2B45"/>
       <sz val="9"/>
+      <u val="single"/>
     </font>
     <font>
       <i val="1"/>
@@ -157,6 +158,12 @@
       <sz val="8"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001C2B45"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -193,12 +200,12 @@
       <sz val="13"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001C2B45"/>
+    </font>
+    <font>
       <color rgb="00B3261E"/>
       <sz val="9.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001C2B45"/>
     </font>
     <font>
       <i val="1"/>
@@ -351,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -441,55 +448,57 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="32" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="32" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -502,16 +511,25 @@
     <xf numFmtId="0" fontId="38" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="1"/>
         <color rgb="00B3261E"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001E6B52"/>
       </font>
     </dxf>
   </dxfs>
@@ -1725,7 +1743,7 @@
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="12">
-        <f>"The one-page summary — six headline numbers below, each labelled with its data confidence so nothing is trusted more than it should be. The Select Fiscal Year box above (top right) is the master control for the whole workbook — change it here and 02 Profitability, Entity Register, Group Summary and the industry table below all follow. Currently showing "&amp;$K$2&amp;". The trend sections further down (Notable Movers, the revenue/EBITDA chart) stay fixed to FY2023→FY2025 regardless of this selector."</f>
+        <f>"The one-page summary — six headline numbers below, each labelled with its data confidence so nothing is trusted more than it should be. The Select Fiscal Year box above (top right) drives every group-wide view — this page's own KPI cards, the industry table below, Entity Register and Group Summary — currently showing "&amp;$K$2&amp;". 02 Profitability has its own separate fiscal-year selector for drilling into one entity's history without changing the group-wide numbers here. The trend sections further down (Notable Movers, the revenue/EBITDA chart) stay fixed to FY2023→FY2025 regardless of either selector."</f>
         <v/>
       </c>
       <c r="N11" s="1" t="n"/>
@@ -3366,10 +3384,14 @@
       <formula1>=Dim_Calendar!$A$2:$A$4</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId2"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -3397,7 +3419,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="47" t="inlineStr">
+        <is>
+          <t>← 01 Exec Summary</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -3411,39 +3437,39 @@
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="47" t="inlineStr">
+      <c r="B2" s="48" t="inlineStr">
         <is>
           <t>SANDHU GROUP — Financial Dashboard</t>
         </is>
       </c>
-      <c r="C2" s="48" t="n"/>
-      <c r="D2" s="48" t="n"/>
-      <c r="E2" s="48" t="n"/>
-      <c r="F2" s="48" t="n"/>
-      <c r="G2" s="48" t="n"/>
-      <c r="H2" s="48" t="n"/>
-      <c r="I2" s="48" t="n"/>
-      <c r="J2" s="48" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
     <row r="3" ht="10" customHeight="1">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="48" t="n"/>
-      <c r="C3" s="48" t="n"/>
-      <c r="D3" s="48" t="n"/>
-      <c r="E3" s="48" t="n"/>
-      <c r="F3" s="48" t="n"/>
-      <c r="G3" s="48" t="n"/>
-      <c r="H3" s="48" t="n"/>
-      <c r="I3" s="48" t="n"/>
-      <c r="J3" s="48" t="n"/>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
+      <c r="I3" s="49" t="n"/>
+      <c r="J3" s="49" t="n"/>
       <c r="K3" s="1" t="n"/>
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>CaseWare WTB + GIFI categorization  •  Fiscal year end March 31  •  Figures in CAD</t>
         </is>
@@ -3467,29 +3493,30 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>Select Entity</t>
         </is>
       </c>
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>Restaurant Indiarosa II</t>
         </is>
       </c>
       <c r="F6" s="1" t="n"/>
-      <c r="G6" s="50" t="inlineStr">
-        <is>
-          <t>Fiscal Year</t>
-        </is>
-      </c>
-      <c r="H6" s="51">
-        <f>'01 Exec Summary'!$K$2</f>
-        <v/>
-      </c>
-      <c r="I6" s="52" t="inlineStr">
-        <is>
-          <t>set on 01 Exec Summary → flows to every sheet</t>
+      <c r="G6" s="51" t="inlineStr">
+        <is>
+          <t>Fiscal Year (this page)</t>
+        </is>
+      </c>
+      <c r="H6" s="52" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="I6" s="53" t="inlineStr">
+        <is>
+          <t>independent of 01 Exec Summary's selector — see note</t>
         </is>
       </c>
       <c r="J6" s="1" t="n"/>
@@ -3547,71 +3574,71 @@
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="53" t="inlineStr">
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="C10" s="54" t="n"/>
-      <c r="D10" s="53" t="inlineStr">
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="54" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="E10" s="54" t="n"/>
+      <c r="E10" s="55" t="n"/>
       <c r="F10" s="1" t="n"/>
-      <c r="G10" s="53" t="inlineStr">
+      <c r="G10" s="54" t="inlineStr">
         <is>
           <t>NET INCOME</t>
         </is>
       </c>
-      <c r="H10" s="54" t="n"/>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="H10" s="55" t="n"/>
+      <c r="I10" s="54" t="inlineStr">
         <is>
           <t>INCOME TAX</t>
         </is>
       </c>
-      <c r="J10" s="54" t="n"/>
+      <c r="J10" s="55" t="n"/>
       <c r="K10" s="1" t="n"/>
       <c r="L10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="55">
+      <c r="B11" s="56">
         <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))</f>
         <v/>
       </c>
-      <c r="C11" s="54" t="n"/>
-      <c r="D11" s="55">
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="56">
         <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]=$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
-      <c r="E11" s="54" t="n"/>
+      <c r="E11" s="55" t="n"/>
       <c r="F11" s="1" t="n"/>
-      <c r="G11" s="55">
+      <c r="G11" s="56">
         <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],$H$6))</f>
         <v/>
       </c>
-      <c r="H11" s="54" t="n"/>
-      <c r="I11" s="55">
+      <c r="H11" s="55" t="n"/>
+      <c r="I11" s="56">
         <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
-      <c r="J11" s="54" t="n"/>
+      <c r="J11" s="55" t="n"/>
       <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="54" t="n"/>
-      <c r="C12" s="54" t="n"/>
-      <c r="D12" s="54" t="n"/>
-      <c r="E12" s="54" t="n"/>
+      <c r="B12" s="55" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
       <c r="F12" s="1" t="n"/>
-      <c r="G12" s="54" t="n"/>
-      <c r="H12" s="54" t="n"/>
-      <c r="I12" s="54" t="n"/>
-      <c r="J12" s="54" t="n"/>
+      <c r="G12" s="55" t="n"/>
+      <c r="H12" s="55" t="n"/>
+      <c r="I12" s="55" t="n"/>
+      <c r="J12" s="55" t="n"/>
       <c r="K12" s="1" t="n"/>
       <c r="L12" s="1" t="n"/>
     </row>
@@ -3631,71 +3658,71 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="B14" s="57" t="inlineStr">
         <is>
           <t>EBITDA MARGIN</t>
         </is>
       </c>
-      <c r="C14" s="54" t="n"/>
-      <c r="D14" s="56" t="inlineStr">
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="57" t="inlineStr">
         <is>
           <t>EFFECTIVE TAX RATE</t>
         </is>
       </c>
-      <c r="E14" s="54" t="n"/>
+      <c r="E14" s="55" t="n"/>
       <c r="F14" s="1" t="n"/>
-      <c r="G14" s="56" t="inlineStr">
+      <c r="G14" s="57" t="inlineStr">
         <is>
           <t>% OF GROUP REVENUE</t>
         </is>
       </c>
-      <c r="H14" s="54" t="n"/>
-      <c r="I14" s="56" t="inlineStr">
+      <c r="H14" s="55" t="n"/>
+      <c r="I14" s="57" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="J14" s="54" t="n"/>
+      <c r="J14" s="55" t="n"/>
       <c r="K14" s="1" t="n"/>
       <c r="L14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="57">
+      <c r="B15" s="58">
         <f>IFERROR(D11/B11,0)</f>
         <v/>
       </c>
-      <c r="C15" s="54" t="n"/>
-      <c r="D15" s="57">
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="58">
         <f>IFERROR(I11/(G11+I11),0)</f>
         <v/>
       </c>
-      <c r="E15" s="54" t="n"/>
+      <c r="E15" s="55" t="n"/>
       <c r="F15" s="1" t="n"/>
-      <c r="G15" s="57">
+      <c r="G15" s="58">
         <f>IFERROR(B11/(-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6)),0)</f>
         <v/>
       </c>
-      <c r="H15" s="54" t="n"/>
-      <c r="I15" s="55">
+      <c r="H15" s="55" t="n"/>
+      <c r="I15" s="56">
         <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
-      <c r="J15" s="54" t="n"/>
+      <c r="J15" s="55" t="n"/>
       <c r="K15" s="1" t="n"/>
       <c r="L15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="54" t="n"/>
-      <c r="C16" s="54" t="n"/>
-      <c r="D16" s="54" t="n"/>
-      <c r="E16" s="54" t="n"/>
+      <c r="B16" s="55" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="55" t="n"/>
       <c r="F16" s="1" t="n"/>
-      <c r="G16" s="54" t="n"/>
-      <c r="H16" s="54" t="n"/>
-      <c r="I16" s="54" t="n"/>
-      <c r="J16" s="54" t="n"/>
+      <c r="G16" s="55" t="n"/>
+      <c r="H16" s="55" t="n"/>
+      <c r="I16" s="55" t="n"/>
+      <c r="J16" s="55" t="n"/>
       <c r="K16" s="1" t="n"/>
       <c r="L16" s="1" t="n"/>
     </row>
@@ -3729,14 +3756,14 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Category Breakdown</t>
         </is>
       </c>
-      <c r="C19" s="48" t="n"/>
-      <c r="D19" s="48" t="n"/>
-      <c r="E19" s="48" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
       <c r="F19" s="1" t="n"/>
       <c r="G19" s="1" t="n"/>
       <c r="H19" s="1" t="n"/>
@@ -4070,24 +4097,44 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
-      <c r="C36" s="1" t="n"/>
-      <c r="D36" s="1" t="n"/>
-      <c r="E36" s="1" t="n"/>
-      <c r="F36" s="1" t="n"/>
-      <c r="G36" s="1" t="n"/>
-      <c r="H36" s="1" t="n"/>
-      <c r="I36" s="1" t="n"/>
-      <c r="J36" s="1" t="n"/>
+      <c r="B36" s="59" t="inlineStr">
+        <is>
+          <t>Key Ratios — Common-Size P&amp;L (% of Revenue), Selected Entity vs Group, Same Year</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="49" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="49" t="n"/>
+      <c r="J36" s="49" t="n"/>
       <c r="K36" s="1" t="n"/>
       <c r="L36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="1" t="n"/>
-      <c r="D37" s="1" t="n"/>
-      <c r="E37" s="1" t="n"/>
+      <c r="B37" s="60" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="60" t="inlineStr">
+        <is>
+          <t>This Entity</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>Group Avg</t>
+        </is>
+      </c>
+      <c r="E37" s="60" t="inlineStr">
+        <is>
+          <t>vs Group (pp)</t>
+        </is>
+      </c>
       <c r="F37" s="1" t="n"/>
       <c r="G37" s="1" t="n"/>
       <c r="H37" s="1" t="n"/>
@@ -4098,10 +4145,23 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="n"/>
-      <c r="C38" s="1" t="n"/>
-      <c r="D38" s="1" t="n"/>
-      <c r="E38" s="1" t="n"/>
+      <c r="B38" s="61" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C38" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D38" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E38" s="62">
+        <f>C38-D38</f>
+        <v/>
+      </c>
       <c r="F38" s="1" t="n"/>
       <c r="G38" s="1" t="n"/>
       <c r="H38" s="1" t="n"/>
@@ -4112,10 +4172,23 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="n"/>
-      <c r="C39" s="1" t="n"/>
-      <c r="D39" s="1" t="n"/>
-      <c r="E39" s="1" t="n"/>
+      <c r="B39" s="61" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C39" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E39" s="62">
+        <f>C39-D39</f>
+        <v/>
+      </c>
       <c r="F39" s="1" t="n"/>
       <c r="G39" s="1" t="n"/>
       <c r="H39" s="1" t="n"/>
@@ -4126,10 +4199,23 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="n"/>
-      <c r="C40" s="1" t="n"/>
-      <c r="D40" s="1" t="n"/>
-      <c r="E40" s="1" t="n"/>
+      <c r="B40" s="61" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C40" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D40" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E40" s="62">
+        <f>C40-D40</f>
+        <v/>
+      </c>
       <c r="F40" s="1" t="n"/>
       <c r="G40" s="1" t="n"/>
       <c r="H40" s="1" t="n"/>
@@ -4140,10 +4226,23 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="n"/>
-      <c r="C41" s="1" t="n"/>
-      <c r="D41" s="1" t="n"/>
-      <c r="E41" s="1" t="n"/>
+      <c r="B41" s="61" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C41" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D41" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E41" s="62">
+        <f>C41-D41</f>
+        <v/>
+      </c>
       <c r="F41" s="1" t="n"/>
       <c r="G41" s="1" t="n"/>
       <c r="H41" s="1" t="n"/>
@@ -4154,10 +4253,23 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="1" t="n"/>
-      <c r="C42" s="1" t="n"/>
-      <c r="D42" s="1" t="n"/>
-      <c r="E42" s="1" t="n"/>
+      <c r="B42" s="61" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C42" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E42" s="62">
+        <f>C42-D42</f>
+        <v/>
+      </c>
       <c r="F42" s="1" t="n"/>
       <c r="G42" s="1" t="n"/>
       <c r="H42" s="1" t="n"/>
@@ -4168,10 +4280,23 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
-      <c r="D43" s="1" t="n"/>
-      <c r="E43" s="1" t="n"/>
+      <c r="B43" s="61" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C43" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D43" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E43" s="62">
+        <f>C43-D43</f>
+        <v/>
+      </c>
       <c r="F43" s="1" t="n"/>
       <c r="G43" s="1" t="n"/>
       <c r="H43" s="1" t="n"/>
@@ -4182,10 +4307,23 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="1" t="n"/>
-      <c r="C44" s="1" t="n"/>
-      <c r="D44" s="1" t="n"/>
-      <c r="E44" s="1" t="n"/>
+      <c r="B44" s="61" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C44" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D44" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E44" s="62">
+        <f>C44-D44</f>
+        <v/>
+      </c>
       <c r="F44" s="1" t="n"/>
       <c r="G44" s="1" t="n"/>
       <c r="H44" s="1" t="n"/>
@@ -4196,10 +4334,23 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="1" t="n"/>
-      <c r="C45" s="1" t="n"/>
-      <c r="D45" s="1" t="n"/>
-      <c r="E45" s="1" t="n"/>
+      <c r="B45" s="61" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C45" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D45" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E45" s="62">
+        <f>C45-D45</f>
+        <v/>
+      </c>
       <c r="F45" s="1" t="n"/>
       <c r="G45" s="1" t="n"/>
       <c r="H45" s="1" t="n"/>
@@ -4210,10 +4361,23 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
-      <c r="C46" s="1" t="n"/>
-      <c r="D46" s="1" t="n"/>
-      <c r="E46" s="1" t="n"/>
+      <c r="B46" s="61" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C46" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D46" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E46" s="62">
+        <f>C46-D46</f>
+        <v/>
+      </c>
       <c r="F46" s="1" t="n"/>
       <c r="G46" s="1" t="n"/>
       <c r="H46" s="1" t="n"/>
@@ -4224,10 +4388,23 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="n"/>
-      <c r="C47" s="1" t="n"/>
-      <c r="D47" s="1" t="n"/>
-      <c r="E47" s="1" t="n"/>
+      <c r="B47" s="61" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C47" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D47" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E47" s="62">
+        <f>C47-D47</f>
+        <v/>
+      </c>
       <c r="F47" s="1" t="n"/>
       <c r="G47" s="1" t="n"/>
       <c r="H47" s="1" t="n"/>
@@ -4238,10 +4415,23 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
-      <c r="B48" s="1" t="n"/>
-      <c r="C48" s="1" t="n"/>
-      <c r="D48" s="1" t="n"/>
-      <c r="E48" s="1" t="n"/>
+      <c r="B48" s="61" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C48" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D48" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E48" s="62">
+        <f>C48-D48</f>
+        <v/>
+      </c>
       <c r="F48" s="1" t="n"/>
       <c r="G48" s="1" t="n"/>
       <c r="H48" s="1" t="n"/>
@@ -4252,10 +4442,10 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="n"/>
-      <c r="C49" s="1" t="n"/>
-      <c r="D49" s="1" t="n"/>
-      <c r="E49" s="1" t="n"/>
+      <c r="B49" s="61" t="n"/>
+      <c r="C49" s="61" t="n"/>
+      <c r="D49" s="61" t="n"/>
+      <c r="E49" s="61" t="n"/>
       <c r="F49" s="1" t="n"/>
       <c r="G49" s="1" t="n"/>
       <c r="H49" s="1" t="n"/>
@@ -4266,10 +4456,23 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
-      <c r="B50" s="1" t="n"/>
-      <c r="C50" s="1" t="n"/>
-      <c r="D50" s="1" t="n"/>
-      <c r="E50" s="1" t="n"/>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C50" s="64">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D50" s="62">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E50" s="62">
+        <f>C50-D50</f>
+        <v/>
+      </c>
       <c r="F50" s="1" t="n"/>
       <c r="G50" s="1" t="n"/>
       <c r="H50" s="1" t="n"/>
@@ -4280,10 +4483,17 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
-      <c r="B51" s="1" t="n"/>
-      <c r="C51" s="1" t="n"/>
-      <c r="D51" s="1" t="n"/>
-      <c r="E51" s="1" t="n"/>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C51" s="64">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="D51" s="61" t="n"/>
+      <c r="E51" s="61" t="n"/>
       <c r="F51" s="1" t="n"/>
       <c r="G51" s="1" t="n"/>
       <c r="H51" s="1" t="n"/>
@@ -4294,10 +4504,17 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
-      <c r="B52" s="1" t="n"/>
-      <c r="C52" s="1" t="n"/>
-      <c r="D52" s="1" t="n"/>
-      <c r="E52" s="1" t="n"/>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>Net Margin</t>
+        </is>
+      </c>
+      <c r="C52" s="64">
+        <f>IFERROR(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D52" s="61" t="n"/>
+      <c r="E52" s="61" t="n"/>
       <c r="F52" s="1" t="n"/>
       <c r="G52" s="1" t="n"/>
       <c r="H52" s="1" t="n"/>
@@ -4308,15 +4525,11 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="n"/>
-      <c r="C53" s="1" t="n"/>
-      <c r="D53" s="1" t="n"/>
-      <c r="E53" s="1" t="n"/>
-      <c r="F53" s="1" t="n"/>
-      <c r="G53" s="1" t="n"/>
-      <c r="H53" s="1" t="n"/>
-      <c r="I53" s="1" t="n"/>
-      <c r="J53" s="1" t="n"/>
+      <c r="B53" s="53" t="inlineStr">
+        <is>
+          <t>"Group Avg" = that category's total across all 16 entities ÷ group revenue, same fiscal year (a size-weighted benchmark, not an average of each entity's own ratio).</t>
+        </is>
+      </c>
       <c r="K53" s="1" t="n"/>
       <c r="L53" s="1" t="n"/>
     </row>
@@ -4336,70 +4549,168 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
-      <c r="C55" s="1" t="n"/>
-      <c r="D55" s="1" t="n"/>
-      <c r="E55" s="1" t="n"/>
-      <c r="F55" s="1" t="n"/>
-      <c r="G55" s="1" t="n"/>
-      <c r="H55" s="1" t="n"/>
-      <c r="I55" s="1" t="n"/>
-      <c r="J55" s="1" t="n"/>
+      <c r="B55" s="59" t="inlineStr">
+        <is>
+          <t>3-Year Trend — Selected Entity</t>
+        </is>
+      </c>
+      <c r="C55" s="49" t="n"/>
+      <c r="D55" s="49" t="n"/>
+      <c r="E55" s="49" t="n"/>
+      <c r="F55" s="49" t="n"/>
+      <c r="G55" s="49" t="n"/>
+      <c r="H55" s="49" t="n"/>
+      <c r="I55" s="49" t="n"/>
+      <c r="J55" s="49" t="n"/>
       <c r="K55" s="1" t="n"/>
       <c r="L55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n"/>
-      <c r="B56" s="1" t="n"/>
-      <c r="C56" s="1" t="n"/>
-      <c r="D56" s="1" t="n"/>
-      <c r="E56" s="1" t="n"/>
+      <c r="B56" s="60" t="inlineStr">
+        <is>
+          <t>Fiscal Year</t>
+        </is>
+      </c>
+      <c r="C56" s="60" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D56" s="60" t="inlineStr">
+        <is>
+          <t>COGS %</t>
+        </is>
+      </c>
+      <c r="E56" s="60" t="inlineStr">
+        <is>
+          <t>Payroll %</t>
+        </is>
+      </c>
       <c r="F56" s="1" t="n"/>
-      <c r="G56" s="1" t="n"/>
-      <c r="H56" s="1" t="n"/>
-      <c r="I56" s="1" t="n"/>
+      <c r="G56" s="60" t="inlineStr">
+        <is>
+          <t>Occupancy %</t>
+        </is>
+      </c>
+      <c r="H56" s="60" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="I56" s="60" t="inlineStr">
+        <is>
+          <t>Net Margin</t>
+        </is>
+      </c>
       <c r="J56" s="1" t="n"/>
       <c r="K56" s="1" t="n"/>
       <c r="L56" s="1" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="n"/>
-      <c r="C57" s="1" t="n"/>
-      <c r="D57" s="1" t="n"/>
-      <c r="E57" s="1" t="n"/>
+      <c r="B57" s="61" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C57" s="65">
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))</f>
+        <v/>
+      </c>
+      <c r="D57" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
+        <v/>
+      </c>
+      <c r="E57" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
+        <v/>
+      </c>
       <c r="F57" s="1" t="n"/>
-      <c r="G57" s="1" t="n"/>
-      <c r="H57" s="1" t="n"/>
-      <c r="I57" s="1" t="n"/>
+      <c r="G57" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
+        <v/>
+      </c>
+      <c r="H57" s="62">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2023")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2023")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
+        <v/>
+      </c>
+      <c r="I57" s="62">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2023")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
+        <v/>
+      </c>
       <c r="J57" s="1" t="n"/>
       <c r="K57" s="1" t="n"/>
       <c r="L57" s="1" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="n"/>
-      <c r="C58" s="1" t="n"/>
-      <c r="D58" s="1" t="n"/>
-      <c r="E58" s="1" t="n"/>
+      <c r="B58" s="61" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C58" s="65">
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))</f>
+        <v/>
+      </c>
+      <c r="D58" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <v/>
+      </c>
+      <c r="E58" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <v/>
+      </c>
       <c r="F58" s="1" t="n"/>
-      <c r="G58" s="1" t="n"/>
-      <c r="H58" s="1" t="n"/>
-      <c r="I58" s="1" t="n"/>
+      <c r="G58" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <v/>
+      </c>
+      <c r="H58" s="62">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2024")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2024")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <v/>
+      </c>
+      <c r="I58" s="62">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2024")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <v/>
+      </c>
       <c r="J58" s="1" t="n"/>
       <c r="K58" s="1" t="n"/>
       <c r="L58" s="1" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
-      <c r="B59" s="1" t="n"/>
-      <c r="C59" s="1" t="n"/>
-      <c r="D59" s="1" t="n"/>
-      <c r="E59" s="1" t="n"/>
+      <c r="B59" s="61" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C59" s="65">
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))</f>
+        <v/>
+      </c>
+      <c r="D59" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
+      <c r="E59" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
       <c r="F59" s="1" t="n"/>
-      <c r="G59" s="1" t="n"/>
-      <c r="H59" s="1" t="n"/>
-      <c r="I59" s="1" t="n"/>
+      <c r="G59" s="62">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
+      <c r="H59" s="62">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
+      <c r="I59" s="62">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2025")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
       <c r="J59" s="1" t="n"/>
       <c r="K59" s="1" t="n"/>
       <c r="L59" s="1" t="n"/>
@@ -4559,14 +4870,17 @@
       <c r="L70" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="23">
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="G15:H16"/>
     <mergeCell ref="B15:C16"/>
     <mergeCell ref="D15:E16"/>
+    <mergeCell ref="B53:J53"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B55:J55"/>
     <mergeCell ref="B2:J3"/>
+    <mergeCell ref="B36:J36"/>
     <mergeCell ref="I15:J16"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="G11:H12"/>
@@ -4581,15 +4895,29 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="B19:E19"/>
   </mergeCells>
-  <dataValidations count="1">
+  <conditionalFormatting sqref="E38:E48">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>-0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=Dim_Entity!$B$2:$B$17</formula1>
     </dataValidation>
+    <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=Dim_Calendar!$A$2:$A$4</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4629,7 +4957,11 @@
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
+      <c r="L1" s="47" t="inlineStr">
+        <is>
+          <t>← 01 Exec Summary</t>
+        </is>
+      </c>
       <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
@@ -4668,7 +5000,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="66" t="inlineStr">
         <is>
           <t>Tax Position — Restaurant IndiaRosa 2 &amp; Associated Group</t>
         </is>
@@ -4681,7 +5013,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>Every figure on this page was matched against an independently-known number before being trusted (per the handoff doc's validation rule) — nothing here is estimated or assumed.</t>
         </is>
@@ -4835,13 +5167,13 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="68" t="inlineStr">
         <is>
           <t>IndiaRosa 2 — Net income for tax purposes (Federal T2), 3-year</t>
         </is>
       </c>
       <c r="F14" s="1" t="n"/>
-      <c r="G14" s="62" t="inlineStr">
+      <c r="G14" s="69" t="inlineStr">
         <is>
           <t>RDTOH / GRIP-CDA continuity</t>
         </is>
@@ -4868,7 +5200,7 @@
       <c r="D15" s="1" t="n"/>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="n"/>
-      <c r="G15" s="63" t="inlineStr">
+      <c r="G15" s="70" t="inlineStr">
         <is>
           <t>RDTOH balance: NOT FOUND
 CDA balance: NOT FOUND
@@ -4962,7 +5294,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="64" t="inlineStr">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>Not the formal 'Taxable Income' line (loss-carryforward application isn't shown in this export) — this is 'Net income for income tax purposes' per the T2. Genuinely differs from accounting net income; not treated as interchangeable.</t>
         </is>
@@ -5004,7 +5336,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="68" t="inlineStr">
         <is>
           <t>Associated Group — SBD &amp; GRIP (from IndiaRosa 2's Taxprep SLIPA schedule, current year)</t>
         </is>
@@ -5022,28 +5354,28 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="65" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="C25" s="65" t="inlineStr">
+      <c r="C25" s="60" t="inlineStr">
         <is>
           <t>Net Income (tax)</t>
         </is>
       </c>
-      <c r="D25" s="65" t="inlineStr">
+      <c r="D25" s="60" t="inlineStr">
         <is>
           <t>Part I Tax</t>
         </is>
       </c>
-      <c r="E25" s="65" t="inlineStr">
+      <c r="E25" s="60" t="inlineStr">
         <is>
           <t>SBD</t>
         </is>
       </c>
       <c r="F25" s="1" t="n"/>
-      <c r="G25" s="65" t="inlineStr">
+      <c r="G25" s="60" t="inlineStr">
         <is>
           <t>GRIP</t>
         </is>
@@ -5057,22 +5389,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="66" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>9357-7427 Québec Inc.</t>
         </is>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="65" t="n">
         <v>-3147</v>
       </c>
-      <c r="D26" s="67" t="n">
+      <c r="D26" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="67" t="n">
+      <c r="E26" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="n"/>
-      <c r="G26" s="67" t="n">
+      <c r="G26" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="n"/>
@@ -5084,22 +5416,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="66" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>9366-1676 Quebec Inc.</t>
         </is>
       </c>
-      <c r="C27" s="67" t="n">
+      <c r="C27" s="65" t="n">
         <v>-665484</v>
       </c>
-      <c r="D27" s="67" t="n">
+      <c r="D27" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="67" t="n">
+      <c r="E27" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="1" t="n"/>
-      <c r="G27" s="67" t="n">
+      <c r="G27" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="n"/>
@@ -5111,22 +5443,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="66" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>9425-4547 Québec Inc.</t>
         </is>
       </c>
-      <c r="C28" s="67" t="n">
+      <c r="C28" s="65" t="n">
         <v>112788</v>
       </c>
-      <c r="D28" s="67" t="n">
+      <c r="D28" s="65" t="n">
         <v>12155</v>
       </c>
-      <c r="E28" s="67" t="n">
+      <c r="E28" s="65" t="n">
         <v>20146</v>
       </c>
       <c r="F28" s="1" t="n"/>
-      <c r="G28" s="67" t="n">
+      <c r="G28" s="65" t="n">
         <v>29568</v>
       </c>
       <c r="H28" s="1" t="n"/>
@@ -5138,22 +5470,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="66" t="inlineStr">
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>9455-4169 Quebec Inc.</t>
         </is>
       </c>
-      <c r="C29" s="67" t="n">
+      <c r="C29" s="65" t="n">
         <v>-3065</v>
       </c>
-      <c r="D29" s="67" t="n">
+      <c r="D29" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="67" t="n">
+      <c r="E29" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="n"/>
-      <c r="G29" s="67" t="n">
+      <c r="G29" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="n"/>
@@ -5165,22 +5497,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="66" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>9455-4177 Quebec Inc.</t>
         </is>
       </c>
-      <c r="C30" s="67" t="n">
+      <c r="C30" s="65" t="n">
         <v>-3015</v>
       </c>
-      <c r="D30" s="67" t="n">
+      <c r="D30" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="67" t="n">
+      <c r="E30" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="n"/>
-      <c r="G30" s="67" t="n">
+      <c r="G30" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="n"/>
@@ -5192,22 +5524,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="66" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>9455-4201 Quebec inc.</t>
         </is>
       </c>
-      <c r="C31" s="67" t="n">
+      <c r="C31" s="65" t="n">
         <v>577222</v>
       </c>
-      <c r="D31" s="67" t="n">
+      <c r="D31" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="67" t="n">
+      <c r="E31" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="n"/>
-      <c r="G31" s="67" t="n">
+      <c r="G31" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="n"/>
@@ -5219,22 +5551,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="66" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>9108-6876 Quebec Inc.</t>
         </is>
       </c>
-      <c r="C32" s="67" t="n">
+      <c r="C32" s="65" t="n">
         <v>390551</v>
       </c>
-      <c r="D32" s="67" t="n">
+      <c r="D32" s="65" t="n">
         <v>8318</v>
       </c>
-      <c r="E32" s="67" t="n">
+      <c r="E32" s="65" t="n">
         <v>16540</v>
       </c>
       <c r="F32" s="1" t="n"/>
-      <c r="G32" s="67" t="n">
+      <c r="G32" s="65" t="n">
         <v>2325</v>
       </c>
       <c r="H32" s="1" t="n"/>
@@ -5246,22 +5578,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="66" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>Bistro Guru Inc.</t>
         </is>
       </c>
-      <c r="C33" s="67" t="n">
+      <c r="C33" s="65" t="n">
         <v>-32467</v>
       </c>
-      <c r="D33" s="67" t="n">
+      <c r="D33" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="67" t="n">
+      <c r="E33" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="1" t="n"/>
-      <c r="G33" s="67" t="n">
+      <c r="G33" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="1" t="n"/>
@@ -5273,22 +5605,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="66" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>9096-0436 Quebec Inc.</t>
         </is>
       </c>
-      <c r="C34" s="67" t="n">
+      <c r="C34" s="65" t="n">
         <v>-21235</v>
       </c>
-      <c r="D34" s="67" t="n">
+      <c r="D34" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="67" t="n">
+      <c r="E34" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="1" t="n"/>
-      <c r="G34" s="67" t="n">
+      <c r="G34" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="1" t="n"/>
@@ -5300,22 +5632,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="66" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>9366-1049 Québec Inc.</t>
         </is>
       </c>
-      <c r="C35" s="67" t="n">
+      <c r="C35" s="65" t="n">
         <v>312963</v>
       </c>
-      <c r="D35" s="67" t="n">
+      <c r="D35" s="65" t="n">
         <v>35338</v>
       </c>
-      <c r="E35" s="67" t="n">
+      <c r="E35" s="65" t="n">
         <v>36755</v>
       </c>
       <c r="F35" s="1" t="n"/>
-      <c r="G35" s="67" t="n">
+      <c r="G35" s="65" t="n">
         <v>229599</v>
       </c>
       <c r="H35" s="1" t="n"/>
@@ -5327,22 +5659,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="66" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>9098-0558 Quebec Inc.</t>
         </is>
       </c>
-      <c r="C36" s="67" t="n">
+      <c r="C36" s="65" t="n">
         <v>-13045</v>
       </c>
-      <c r="D36" s="67" t="n">
+      <c r="D36" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="67" t="n">
+      <c r="E36" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="1" t="n"/>
-      <c r="G36" s="67" t="n">
+      <c r="G36" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="1" t="n"/>
@@ -5354,22 +5686,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="66" t="inlineStr">
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>2749-8567 Quebec Inc.</t>
         </is>
       </c>
-      <c r="C37" s="67" t="n">
+      <c r="C37" s="65" t="n">
         <v>28760</v>
       </c>
-      <c r="D37" s="67" t="n">
+      <c r="D37" s="65" t="n">
         <v>2864</v>
       </c>
-      <c r="E37" s="67" t="n">
+      <c r="E37" s="65" t="n">
         <v>4594</v>
       </c>
       <c r="F37" s="1" t="n"/>
-      <c r="G37" s="67" t="n">
+      <c r="G37" s="65" t="n">
         <v>3297</v>
       </c>
       <c r="H37" s="1" t="n"/>
@@ -5381,22 +5713,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="66" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>9504-7510 Québec Inc.</t>
         </is>
       </c>
-      <c r="C38" s="67" t="n">
+      <c r="C38" s="65" t="n">
         <v>-465609</v>
       </c>
-      <c r="D38" s="67" t="n">
+      <c r="D38" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="67" t="n">
+      <c r="E38" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="1" t="n"/>
-      <c r="G38" s="67" t="n">
+      <c r="G38" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="1" t="n"/>
@@ -5408,22 +5740,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="66" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>9525-2854 Québec Inc.</t>
         </is>
       </c>
-      <c r="C39" s="67" t="n">
+      <c r="C39" s="65" t="n">
         <v>-55143</v>
       </c>
-      <c r="D39" s="67" t="n">
+      <c r="D39" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="67" t="n">
+      <c r="E39" s="65" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="1" t="n"/>
-      <c r="G39" s="67" t="n">
+      <c r="G39" s="65" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="1" t="n"/>
@@ -5435,25 +5767,25 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="68" t="inlineStr">
+      <c r="B40" s="63" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C40" s="69">
+      <c r="C40" s="72">
         <f>SUM(C26:C39)</f>
         <v/>
       </c>
-      <c r="D40" s="69">
+      <c r="D40" s="72">
         <f>SUM(D26:D39)</f>
         <v/>
       </c>
-      <c r="E40" s="69">
+      <c r="E40" s="72">
         <f>SUM(E26:E39)</f>
         <v/>
       </c>
       <c r="F40" s="1" t="n"/>
-      <c r="G40" s="69">
+      <c r="G40" s="72">
         <f>SUM(G26:G39)</f>
         <v/>
       </c>
@@ -5788,10 +6120,13 @@
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="B2:J2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5819,38 +6154,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
-        <is>
-          <t>Entity Register — driven by 02 Profitability's fiscal-year selector</t>
-        </is>
-      </c>
-      <c r="B1" s="48" t="n"/>
-      <c r="C1" s="48" t="n"/>
-      <c r="D1" s="48" t="n"/>
-      <c r="E1" s="48" t="n"/>
-      <c r="F1" s="48" t="n"/>
-      <c r="G1" s="48" t="n"/>
-      <c r="H1" s="48" t="n"/>
-      <c r="I1" s="48" t="n"/>
-      <c r="J1" s="48" t="n"/>
-      <c r="K1" s="48" t="n"/>
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t>Entity Register — driven by 01 Exec Summary's fiscal-year selector</t>
+        </is>
+      </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+      <c r="F1" s="49" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="49" t="n"/>
+      <c r="I1" s="49" t="n"/>
+      <c r="J1" s="49" t="n"/>
+      <c r="K1" s="49" t="n"/>
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="48" t="n"/>
-      <c r="C2" s="48" t="n"/>
-      <c r="D2" s="48" t="n"/>
-      <c r="E2" s="48" t="n"/>
-      <c r="F2" s="48" t="n"/>
-      <c r="G2" s="48" t="n"/>
-      <c r="H2" s="48" t="n"/>
-      <c r="I2" s="48" t="n"/>
-      <c r="J2" s="48" t="n"/>
-      <c r="K2" s="48" t="n"/>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="47" t="inlineStr">
+        <is>
+          <t>← 01 Exec Summary</t>
+        </is>
+      </c>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
@@ -5933,39 +6272,39 @@
         </is>
       </c>
       <c r="C5" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D5" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E5" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F5" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G5" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H5" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I5" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J5" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9357-7427 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9357-7427 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K5" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9357-7427 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L5" s="1" t="n"/>
@@ -5982,39 +6321,39 @@
         </is>
       </c>
       <c r="C6" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D6" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E6" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F6" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G6" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H6" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I6" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J6" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9366-1676 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9366-1676 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K6" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1676 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L6" s="1" t="n"/>
@@ -6031,39 +6370,39 @@
         </is>
       </c>
       <c r="C7" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D7" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E7" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F7" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G7" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H7" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I7" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J7" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9425-4547 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9425-4547 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K7" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9425-4547 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L7" s="1" t="n"/>
@@ -6080,39 +6419,39 @@
         </is>
       </c>
       <c r="C8" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D8" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F8" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G8" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H8" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I8" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J8" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4169 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4169 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K8" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4169 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L8" s="1" t="n"/>
@@ -6129,39 +6468,39 @@
         </is>
       </c>
       <c r="C9" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D9" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E9" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F9" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G9" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H9" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I9" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J9" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4177 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4177 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K9" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4177 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L9" s="1" t="n"/>
@@ -6178,39 +6517,39 @@
         </is>
       </c>
       <c r="C10" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D10" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F10" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G10" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H10" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I10" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J10" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4201 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-4201 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K10" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-4201 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L10" s="1" t="n"/>
@@ -6227,39 +6566,39 @@
         </is>
       </c>
       <c r="C11" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D11" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E11" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F11" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G11" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H11" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I11" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J11" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9108-6876 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9108-6876 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K11" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9108-6876 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L11" s="1" t="n"/>
@@ -6276,39 +6615,39 @@
         </is>
       </c>
       <c r="C12" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D12" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F12" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G12" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H12" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I12" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J12" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="N/A_BisGur")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="N/A_BisGur")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K12" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_BisGur",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L12" s="1" t="n"/>
@@ -6325,39 +6664,39 @@
         </is>
       </c>
       <c r="C13" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D13" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E13" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G13" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H13" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I13" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J13" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9096-0436 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9096-0436 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K13" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9096-0436 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L13" s="1" t="n"/>
@@ -6374,39 +6713,39 @@
         </is>
       </c>
       <c r="C14" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D14" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F14" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G14" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H14" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I14" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J14" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9504-7510 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9504-7510 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K14" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9504-7510 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L14" s="1" t="n"/>
@@ -6423,39 +6762,39 @@
         </is>
       </c>
       <c r="C15" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D15" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E15" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F15" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G15" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H15" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I15" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J15" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-8236 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9455-8236 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K15" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9455-8236 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L15" s="1" t="n"/>
@@ -6472,39 +6811,39 @@
         </is>
       </c>
       <c r="C16" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D16" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E16" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F16" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G16" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H16" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I16" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J16" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9525-2854 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9525-2854 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K16" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9525-2854 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L16" s="1" t="n"/>
@@ -6521,39 +6860,39 @@
         </is>
       </c>
       <c r="C17" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D17" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E17" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F17" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G17" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H17" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I17" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J17" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9366-1049 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9366-1049 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K17" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9366-1049 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L17" s="1" t="n"/>
@@ -6570,39 +6909,39 @@
         </is>
       </c>
       <c r="C18" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D18" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E18" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F18" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G18" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H18" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I18" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J18" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9098-0558 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="9098-0558 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K18" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"9098-0558 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L18" s="1" t="n"/>
@@ -6619,39 +6958,39 @@
         </is>
       </c>
       <c r="C19" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D19" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E19" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F19" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G19" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H19" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I19" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J19" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="2749-8567 QI")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="2749-8567 QI")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K19" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"2749-8567 QI",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L19" s="1" t="n"/>
@@ -6668,39 +7007,39 @@
         </is>
       </c>
       <c r="C20" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="D20" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="E20" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="F20" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="G20" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="H20" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="I20" s="43">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="J20" s="43">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)-SUMPRODUCT((Fact_TrialBalance[EntityId]="N/A_SanSan")*(Fact_TrialBalance[FiscalYear]='02 Profitability'!$H$6)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)-SUMPRODUCT((Fact_TrialBalance[EntityId]="N/A_SanSan")*(Fact_TrialBalance[FiscalYear]='01 Exec Summary'!$K$2)*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount]))</f>
         <v/>
       </c>
       <c r="K20" s="43">
-        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[FiscalYear],'02 Profitability'!$H$6)</f>
+        <f>-SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],"N/A_SanSan",Fact_TrialBalance[FiscalYear],'01 Exec Summary'!$K$2)</f>
         <v/>
       </c>
       <c r="L20" s="1" t="n"/>
@@ -6784,11 +7123,14 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6815,7 +7157,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="47" t="inlineStr">
+        <is>
+          <t>← 01 Exec Summary</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -6827,28 +7173,28 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="58" t="inlineStr">
-        <is>
-          <t>Group Summary — driven by 02 Profitability's fiscal-year selector</t>
-        </is>
-      </c>
-      <c r="C2" s="48" t="n"/>
-      <c r="D2" s="48" t="n"/>
-      <c r="E2" s="48" t="n"/>
-      <c r="F2" s="48" t="n"/>
-      <c r="G2" s="48" t="n"/>
-      <c r="H2" s="48" t="n"/>
+      <c r="B2" s="59" t="inlineStr">
+        <is>
+          <t>Group Summary — driven by 01 Exec Summary's fiscal-year selector</t>
+        </is>
+      </c>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
       <c r="I2" s="1" t="n"/>
       <c r="J2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
-      <c r="C3" s="48" t="n"/>
-      <c r="D3" s="48" t="n"/>
-      <c r="E3" s="48" t="n"/>
-      <c r="F3" s="48" t="n"/>
-      <c r="G3" s="48" t="n"/>
-      <c r="H3" s="48" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
       <c r="I3" s="1" t="n"/>
       <c r="J3" s="1" t="n"/>
     </row>
@@ -6866,7 +7212,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="73" t="inlineStr">
         <is>
           <t>16-entity group total (per Entity Register) — full scope (2 family trusts excluded)</t>
         </is>
@@ -6882,58 +7228,58 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="53" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>GROUP REVENUE</t>
         </is>
       </c>
-      <c r="C6" s="54" t="n"/>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>GROUP EBITDA</t>
         </is>
       </c>
-      <c r="E6" s="54" t="n"/>
+      <c r="E6" s="55" t="n"/>
       <c r="F6" s="1" t="n"/>
-      <c r="G6" s="53" t="inlineStr">
+      <c r="G6" s="54" t="inlineStr">
         <is>
           <t>GROUP NET INCOME</t>
         </is>
       </c>
-      <c r="H6" s="54" t="n"/>
+      <c r="H6" s="55" t="n"/>
       <c r="I6" s="1" t="n"/>
       <c r="J6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="55">
+      <c r="B7" s="56">
         <f>SUM('Entity Register'!C5:C20)</f>
         <v/>
       </c>
-      <c r="C7" s="54" t="n"/>
-      <c r="D7" s="55">
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="56">
         <f>SUM('Entity Register'!J5:J20)</f>
         <v/>
       </c>
-      <c r="E7" s="54" t="n"/>
+      <c r="E7" s="55" t="n"/>
       <c r="F7" s="1" t="n"/>
-      <c r="G7" s="55">
+      <c r="G7" s="56">
         <f>SUM('Entity Register'!K5:K20)</f>
         <v/>
       </c>
-      <c r="H7" s="54" t="n"/>
+      <c r="H7" s="55" t="n"/>
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="54" t="n"/>
-      <c r="C8" s="54" t="n"/>
-      <c r="D8" s="54" t="n"/>
-      <c r="E8" s="54" t="n"/>
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
       <c r="F8" s="1" t="n"/>
-      <c r="G8" s="54" t="n"/>
-      <c r="H8" s="54" t="n"/>
+      <c r="G8" s="55" t="n"/>
+      <c r="H8" s="55" t="n"/>
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="n"/>
     </row>
@@ -6951,58 +7297,58 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="57" t="inlineStr">
         <is>
           <t>GROUP INCOME TAX</t>
         </is>
       </c>
-      <c r="C10" s="54" t="n"/>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>EFFECTIVE TAX RATE</t>
         </is>
       </c>
-      <c r="E10" s="54" t="n"/>
+      <c r="E10" s="55" t="n"/>
       <c r="F10" s="1" t="n"/>
-      <c r="G10" s="56" t="inlineStr">
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>ENTITIES IN MODEL</t>
         </is>
       </c>
-      <c r="H10" s="54" t="n"/>
+      <c r="H10" s="55" t="n"/>
       <c r="I10" s="1" t="n"/>
       <c r="J10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="55">
+      <c r="B11" s="56">
         <f>SUM('Entity Register'!I5:I20)</f>
         <v/>
       </c>
-      <c r="C11" s="54" t="n"/>
-      <c r="D11" s="57">
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="58">
         <f>IFERROR(SUM('Entity Register'!I5:I20)/(SUM('Entity Register'!K5:K20)+SUM('Entity Register'!I5:I20)),0)</f>
         <v/>
       </c>
-      <c r="E11" s="54" t="n"/>
+      <c r="E11" s="55" t="n"/>
       <c r="F11" s="1" t="n"/>
-      <c r="G11" s="71">
+      <c r="G11" s="74">
         <f>COUNTA('Entity Register'!A5:A20)</f>
         <v/>
       </c>
-      <c r="H11" s="54" t="n"/>
+      <c r="H11" s="55" t="n"/>
       <c r="I11" s="1" t="n"/>
       <c r="J11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="54" t="n"/>
-      <c r="C12" s="54" t="n"/>
-      <c r="D12" s="54" t="n"/>
-      <c r="E12" s="54" t="n"/>
+      <c r="B12" s="55" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
       <c r="F12" s="1" t="n"/>
-      <c r="G12" s="54" t="n"/>
-      <c r="H12" s="54" t="n"/>
+      <c r="G12" s="55" t="n"/>
+      <c r="H12" s="55" t="n"/>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
     </row>
@@ -7032,13 +7378,13 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>Revenue &amp; Net Income by Entity</t>
         </is>
       </c>
-      <c r="C15" s="48" t="n"/>
-      <c r="D15" s="48" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="n"/>
       <c r="G15" s="1" t="n"/>
@@ -7264,11 +7610,11 @@
         <f>'Entity Register'!A14</f>
         <v/>
       </c>
-      <c r="C26" s="72">
+      <c r="C26" s="75">
         <f>'Entity Register'!C14</f>
         <v/>
       </c>
-      <c r="D26" s="72">
+      <c r="D26" s="75">
         <f>'Entity Register'!K14</f>
         <v/>
       </c>
@@ -7278,11 +7624,11 @@
         <f>'Entity Register'!A15</f>
         <v/>
       </c>
-      <c r="C27" s="72">
+      <c r="C27" s="75">
         <f>'Entity Register'!C15</f>
         <v/>
       </c>
-      <c r="D27" s="72">
+      <c r="D27" s="75">
         <f>'Entity Register'!K15</f>
         <v/>
       </c>
@@ -7292,11 +7638,11 @@
         <f>'Entity Register'!A16</f>
         <v/>
       </c>
-      <c r="C28" s="72">
+      <c r="C28" s="75">
         <f>'Entity Register'!C16</f>
         <v/>
       </c>
-      <c r="D28" s="72">
+      <c r="D28" s="75">
         <f>'Entity Register'!K16</f>
         <v/>
       </c>
@@ -7306,11 +7652,11 @@
         <f>'Entity Register'!A17</f>
         <v/>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="75">
         <f>'Entity Register'!C17</f>
         <v/>
       </c>
-      <c r="D29" s="72">
+      <c r="D29" s="75">
         <f>'Entity Register'!K17</f>
         <v/>
       </c>
@@ -7320,11 +7666,11 @@
         <f>'Entity Register'!A18</f>
         <v/>
       </c>
-      <c r="C30" s="72">
+      <c r="C30" s="75">
         <f>'Entity Register'!C18</f>
         <v/>
       </c>
-      <c r="D30" s="72">
+      <c r="D30" s="75">
         <f>'Entity Register'!K18</f>
         <v/>
       </c>
@@ -7334,11 +7680,11 @@
         <f>'Entity Register'!A19</f>
         <v/>
       </c>
-      <c r="C31" s="72">
+      <c r="C31" s="75">
         <f>'Entity Register'!C19</f>
         <v/>
       </c>
-      <c r="D31" s="72">
+      <c r="D31" s="75">
         <f>'Entity Register'!K19</f>
         <v/>
       </c>
@@ -7348,11 +7694,11 @@
         <f>'Entity Register'!A20</f>
         <v/>
       </c>
-      <c r="C32" s="72">
+      <c r="C32" s="75">
         <f>'Entity Register'!C20</f>
         <v/>
       </c>
-      <c r="D32" s="72">
+      <c r="D32" s="75">
         <f>'Entity Register'!K20</f>
         <v/>
       </c>
@@ -7374,10 +7720,13 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B15:D15"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7388,261 +7737,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>SANDHU GROUP INTERACTIVE DASHBOARD — Build Notes</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
+      <c r="C1" s="47" t="inlineStr">
+        <is>
+          <t>← 01 Exec Summary</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="74" t="inlineStr"/>
+      <c r="A2" s="77" t="inlineStr"/>
       <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="74" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>Scope: all 16 entities (both family trusts — Gurpreet Sandhu Trust, Harpreet Sandhu Trust — excluded from scope per instruction; ~$4-$10/yr activity per the handoff, immaterial). Every one of these was rebuilt fresh from its raw CaseWare WTB export in this session (not carried over from any prior file) and covers 3 fiscal years: FY2023, FY2024, FY2025.</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="74" t="inlineStr"/>
+      <c r="A4" s="77" t="inlineStr"/>
       <c r="B4" s="1" t="n"/>
+      <c r="C4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="74" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>Missing: Sandhu &amp; Sandhu Enr.'s Corporate Taxprep export (its WTB was supplied and is included).</t>
         </is>
       </c>
       <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="74" t="inlineStr"/>
+      <c r="A6" s="77" t="inlineStr"/>
       <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="74" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>Dim_Entity updated to the user-supplied reference table: CompanyName (incl. owner suffix, e.g. '- Sandhu H.'), LegalName, and Industry (Construction/Real estate/Investments/Hotel/Restaurant/Rental) replace the earlier EntityName/Segment (HoldCo/RealCo/OpCo) scheme everywhere in this workbook. 'Rres_Ind' in that table was treated as a typo for 'Res_Ind' (same LegalName, 9366-1049 Québec Inc.) — same entity, not a new one. Sandhu &amp; Sandhu Enr. isn't in that table at all; its Industry ('Rental') is inferred from its sibling entity Sandhu Leasing, not given data.</t>
         </is>
       </c>
       <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="74" t="inlineStr"/>
+      <c r="A8" s="77" t="inlineStr"/>
       <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="78" t="inlineStr">
         <is>
           <t>UNEXPECTED FILE: 947_338_2025_Tax.csv identifies its filer as '9475-3381 Québec Inc.' — an entity not in the Section 4 entity list at all. No WTB was supplied for it, so it is NOT included in this workbook. Flagged for you to confirm whether it belongs in the group.</t>
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="74" t="inlineStr"/>
+      <c r="A10" s="77" t="inlineStr"/>
       <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="76" t="inlineStr">
+      <c r="A11" s="79" t="inlineStr">
         <is>
           <t>VALIDATION — every entity's FY2025 Net Income matches an independent benchmark exactly:</t>
         </is>
       </c>
       <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  Restaurant IndiaRosa 2 matches every Section 6 category benchmark to the penny (Net Income FY2025 $462,894.92, FY2024 $736,959.45) — see the account-level exceptions below.</t>
         </is>
       </c>
       <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  All other 15 entities match the Validation Log tab in GIFI_Master_Mapping_v2.xlsx exactly, including Bistro Guru Inc. ($-30,118.89), which RESOLVES the discrepancy flagged in an earlier version of this workbook (the old starter kit's $-45,954.06 figure for Bistro Guru was wrong; the fresh WTB rebuild confirms the Validation Log was correct).</t>
         </is>
       </c>
       <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="74" t="inlineStr"/>
+      <c r="A14" s="77" t="inlineStr"/>
       <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="74" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>Restaurant IndiaRosa 2 — three accounts in its WTB carry a GIFI code that contradicts the account name; treated as account-level overrides, not changes to the master GIFI mapping:</t>
         </is>
       </c>
       <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 45130 'Valet service' + 45125 'Musical entertainment' — tagged GIFI 9270 (Amortization) -&gt; reclassified to Marketing &amp; Entertainment.</t>
         </is>
       </c>
       <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="77" t="inlineStr">
+      <c r="A17" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 44215 'Rent - Ford' + 33455 'Equipment rental' + 45250 'Travelling - gas &amp; repairs' — tagged GIFI 8461 (COGS) -&gt; reclassified to Other Operating.</t>
         </is>
       </c>
       <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="77" t="inlineStr">
+      <c r="A18" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 45150 'Consulting fees' — tagged GIFI 8863 (Administrative) -&gt; reclassified to Other Operating per user confirmation (matches Section 6 Admin $99,729 / Other Operating $79,976 exactly).</t>
         </is>
       </c>
       <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="74" t="inlineStr"/>
+      <c r="A19" s="77" t="inlineStr"/>
       <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="74" t="inlineStr">
+      <c r="A20" s="77" t="inlineStr">
         <is>
           <t>Sandhu &amp; Sandhu Enr. — two Map No formatting variants ('40.1' vs '40. 1') were causing 3 accounts to fall through the fallback table uncategorized; fixed by normalizing whitespace in the Map No match, plus adding one missing fallback row (Map No '40. 3' -&gt; Administrative, Insurance). After the fix, FY2025 Net Income matches the Validation Log exactly ($-15,821.17).</t>
         </is>
       </c>
       <c r="B20" s="1" t="n"/>
+      <c r="C20" s="1" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="74" t="inlineStr"/>
+      <c r="A21" s="77" t="inlineStr"/>
       <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="75" t="inlineStr">
+      <c r="A22" s="78" t="inlineStr">
         <is>
           <t>UNRESOLVED: group-level FY2025 Revenue ($14,945,731) and EBITDA ($2,734,142) are within ~0.5% and ~1.8% of the Section 6 16-entity benchmark ($14,873,731 / $2,784,496) despite every single entity's own Net Income matching its benchmark exactly. Income Tax and Investment &amp; Other Income match exactly. This means a small amount is sitting in a different category than the original benchmark used, in one or two entities — similar in nature to IndiaRosa 2's account exceptions above, but not yet isolated. Group Net Income is within $5,014 (0.8%) of benchmark.</t>
         </is>
       </c>
       <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="74" t="inlineStr"/>
+      <c r="A23" s="77" t="inlineStr"/>
       <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="74" t="inlineStr">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>NOT YET INCLUDED: RDTOH and CDA (confirmed absent from the Taxprep export tested — see 03 Tax Position). SBD/GRIP/Part I tax figures are real for IndiaRosa 2's 14 associated corporations (from its Taxprep SLIPA schedule) but each entity's OWN SBD claim from its own Taxprep export has not yet been pulled in — only IndiaRosa 2's Tax CSV has been mined for Section 3-style data.</t>
         </is>
       </c>
       <c r="B24" s="1" t="n"/>
+      <c r="C24" s="1" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="74" t="inlineStr"/>
+      <c r="A25" s="77" t="inlineStr"/>
       <c r="B25" s="1" t="n"/>
+      <c r="C25" s="1" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="74" t="inlineStr">
+      <c r="A26" s="77" t="inlineStr">
         <is>
           <t>Interactivity: this workbook uses dropdown selectors ('02 Profitability'!C6 Entity, !H6 Fiscal Year) driving live SUMIFS formulas and charts — no Power Pivot/DAX setup required, works in any version of Excel. Entity Register and raw data sheets are Excel Tables with built-in filter dropdowns per column.</t>
         </is>
       </c>
       <c r="B26" s="1" t="n"/>
+      <c r="C26" s="1" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="74" t="inlineStr"/>
+      <c r="A27" s="77" t="inlineStr"/>
       <c r="B27" s="1" t="n"/>
+      <c r="C27" s="1" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="74" t="inlineStr">
+      <c r="A28" s="77" t="inlineStr">
         <is>
           <t>Recalculated and verified in LibreOffice headless — every KPI card and cross-check in this sheet was confirmed against the actual computed cell values, not just the formula text.</t>
         </is>
       </c>
       <c r="B28" s="1" t="n"/>
+      <c r="C28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="n"/>
+      <c r="C29" s="1" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="n"/>
+      <c r="C30" s="1" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="n"/>
+      <c r="C31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="n"/>
+      <c r="C32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="n"/>
+      <c r="C33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="n"/>
+      <c r="C34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="n"/>
+      <c r="C35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="n"/>
+      <c r="C39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="n"/>
+      <c r="C40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="n"/>
+      <c r="C41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="n"/>
+      <c r="C42" s="1" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="n"/>
+      <c r="C44" s="1" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="n"/>
+      <c r="C45" s="1" t="n"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -7665,22 +8066,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="78" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="B1" s="78" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>CompanyName</t>
         </is>
       </c>
-      <c r="C1" s="78" t="inlineStr">
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>LegalName</t>
         </is>
       </c>
-      <c r="D1" s="78" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -8061,17 +8462,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="78" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="B1" s="78" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>YearEnd</t>
         </is>
       </c>
-      <c r="C1" s="78" t="inlineStr">
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>YearLabel</t>
         </is>
@@ -8153,27 +8554,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="78" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="B1" s="78" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="78" t="inlineStr">
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="D1" s="78" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="78" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -8195,7 +8596,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D2" s="72" t="n">
+      <c r="D2" s="75" t="n">
         <v>-5213628.68</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -8220,7 +8621,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D3" s="72" t="n">
+      <c r="D3" s="75" t="n">
         <v>30000</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -8245,7 +8646,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D4" s="72" t="n">
+      <c r="D4" s="75" t="n">
         <v>146738.3</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -8270,7 +8671,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D5" s="72" t="n">
+      <c r="D5" s="75" t="n">
         <v>474171.72</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -8295,7 +8696,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D6" s="72" t="n">
+      <c r="D6" s="75" t="n">
         <v>79976.25999999999</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -8320,7 +8721,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D7" s="72" t="n">
+      <c r="D7" s="75" t="n">
         <v>99728.72</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -8345,7 +8746,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D8" s="72" t="n">
+      <c r="D8" s="75" t="n">
         <v>141793.12</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -8370,7 +8771,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D9" s="72" t="n">
+      <c r="D9" s="75" t="n">
         <v>199058</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -8395,7 +8796,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D10" s="72" t="n">
+      <c r="D10" s="75" t="n">
         <v>1647558.89</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -8420,7 +8821,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D11" s="72" t="n">
+      <c r="D11" s="75" t="n">
         <v>1780201.39</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -8445,7 +8846,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D12" s="72" t="n">
+      <c r="D12" s="75" t="n">
         <v>88959.36</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -8470,7 +8871,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D13" s="72" t="n">
+      <c r="D13" s="75" t="n">
         <v>62548</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -8495,7 +8896,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D14" s="72" t="n">
+      <c r="D14" s="75" t="n">
         <v>-6233247.68</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -8520,7 +8921,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D15" s="72" t="n">
+      <c r="D15" s="75" t="n">
         <v>105000</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -8545,7 +8946,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D16" s="72" t="n">
+      <c r="D16" s="75" t="n">
         <v>178561.41</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -8570,7 +8971,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D17" s="72" t="n">
+      <c r="D17" s="75" t="n">
         <v>382549.29</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -8595,7 +8996,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D18" s="72" t="n">
+      <c r="D18" s="75" t="n">
         <v>73281.73</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -8620,7 +9021,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D19" s="72" t="n">
+      <c r="D19" s="75" t="n">
         <v>88387.59</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -8645,7 +9046,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D20" s="72" t="n">
+      <c r="D20" s="75" t="n">
         <v>161333.63</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -8670,7 +9071,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D21" s="72" t="n">
+      <c r="D21" s="75" t="n">
         <v>222195</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -8695,7 +9096,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D22" s="72" t="n">
+      <c r="D22" s="75" t="n">
         <v>1888352.46</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -8720,7 +9121,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D23" s="72" t="n">
+      <c r="D23" s="75" t="n">
         <v>2181636.69</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -8745,7 +9146,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D24" s="72" t="n">
+      <c r="D24" s="75" t="n">
         <v>214990.43</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -8770,7 +9171,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D25" s="72" t="n">
+      <c r="D25" s="75" t="n">
         <v>-1331424.61</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -8795,7 +9196,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D26" s="72" t="n">
+      <c r="D26" s="75" t="n">
         <v>26989.26</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -8820,7 +9221,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D27" s="72" t="n">
+      <c r="D27" s="75" t="n">
         <v>47833.69</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -8845,7 +9246,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D28" s="72" t="n">
+      <c r="D28" s="75" t="n">
         <v>19176.77</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -8870,7 +9271,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D29" s="72" t="n">
+      <c r="D29" s="75" t="n">
         <v>69851.5</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -8895,7 +9296,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D30" s="72" t="n">
+      <c r="D30" s="75" t="n">
         <v>24668.14</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -8920,7 +9321,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D31" s="72" t="n">
+      <c r="D31" s="75" t="n">
         <v>126996</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -8945,7 +9346,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D32" s="72" t="n">
+      <c r="D32" s="75" t="n">
         <v>394933.77</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -8970,7 +9371,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D33" s="72" t="n">
+      <c r="D33" s="75" t="n">
         <v>365807.86</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -8995,7 +9396,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D34" s="72" t="n">
+      <c r="D34" s="75" t="n">
         <v>42134.25</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -9020,7 +9421,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D35" s="72" t="n">
+      <c r="D35" s="75" t="n">
         <v>477.24</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -9045,7 +9446,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D36" s="72" t="n">
+      <c r="D36" s="75" t="n">
         <v>2597</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -9070,7 +9471,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D37" s="72" t="n">
+      <c r="D37" s="75" t="n">
         <v>72.58</v>
       </c>
       <c r="E37" t="inlineStr">
@@ -9095,7 +9496,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D38" s="72" t="n">
+      <c r="D38" s="75" t="n">
         <v>358.94</v>
       </c>
       <c r="E38" t="inlineStr">
@@ -9120,7 +9521,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D39" s="72" t="n">
+      <c r="D39" s="75" t="n">
         <v>2329</v>
       </c>
       <c r="E39" t="inlineStr">
@@ -9145,7 +9546,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D40" s="72" t="n">
+      <c r="D40" s="75" t="n">
         <v>47.81</v>
       </c>
       <c r="E40" t="inlineStr">
@@ -9170,7 +9571,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D41" s="72" t="n">
+      <c r="D41" s="75" t="n">
         <v>-31929</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -9195,7 +9596,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D42" s="72" t="n">
+      <c r="D42" s="75" t="n">
         <v>29026.44</v>
       </c>
       <c r="E42" t="inlineStr">
@@ -9220,7 +9621,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D43" s="72" t="n">
+      <c r="D43" s="75" t="n">
         <v>90</v>
       </c>
       <c r="E43" t="inlineStr">
@@ -9245,7 +9646,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D44" s="72" t="n">
+      <c r="D44" s="75" t="n">
         <v>27273.26</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -9270,7 +9671,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D45" s="72" t="n">
+      <c r="D45" s="75" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="E45" t="inlineStr">
@@ -9295,7 +9696,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D46" s="72" t="n">
+      <c r="D46" s="75" t="n">
         <v>-190152.12</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -9320,7 +9721,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D47" s="72" t="n">
+      <c r="D47" s="75" t="n">
         <v>396762.02</v>
       </c>
       <c r="E47" t="inlineStr">
@@ -9345,7 +9746,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D48" s="72" t="n">
+      <c r="D48" s="75" t="n">
         <v>204136</v>
       </c>
       <c r="E48" t="inlineStr">
@@ -9370,7 +9771,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D49" s="72" t="n">
+      <c r="D49" s="75" t="n">
         <v>215463.66</v>
       </c>
       <c r="E49" t="inlineStr">
@@ -9395,7 +9796,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D50" s="72" t="n">
+      <c r="D50" s="75" t="n">
         <v>33717.57</v>
       </c>
       <c r="E50" t="inlineStr">
@@ -9420,7 +9821,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D51" s="72" t="n">
+      <c r="D51" s="75" t="n">
         <v>425</v>
       </c>
       <c r="E51" t="inlineStr">
@@ -9445,7 +9846,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D52" s="72" t="n">
+      <c r="D52" s="75" t="n">
         <v>-188197.75</v>
       </c>
       <c r="E52" t="inlineStr">
@@ -9470,7 +9871,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D53" s="72" t="n">
+      <c r="D53" s="75" t="n">
         <v>219534.62</v>
       </c>
       <c r="E53" t="inlineStr">
@@ -9495,7 +9896,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D54" s="72" t="n">
+      <c r="D54" s="75" t="n">
         <v>94472</v>
       </c>
       <c r="E54" t="inlineStr">
@@ -9520,7 +9921,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D55" s="72" t="n">
+      <c r="D55" s="75" t="n">
         <v>152117.58</v>
       </c>
       <c r="E55" t="inlineStr">
@@ -9545,7 +9946,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D56" s="72" t="n">
+      <c r="D56" s="75" t="n">
         <v>16431.97</v>
       </c>
       <c r="E56" t="inlineStr">
@@ -9570,7 +9971,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D57" s="72" t="n">
+      <c r="D57" s="75" t="n">
         <v>-220172.35</v>
       </c>
       <c r="E57" t="inlineStr">
@@ -9595,7 +9996,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D58" s="72" t="n">
+      <c r="D58" s="75" t="n">
         <v>-12000</v>
       </c>
       <c r="E58" t="inlineStr">
@@ -9620,7 +10021,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D59" s="72" t="n">
+      <c r="D59" s="75" t="n">
         <v>80807.78</v>
       </c>
       <c r="E59" t="inlineStr">
@@ -9645,7 +10046,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D60" s="72" t="n">
+      <c r="D60" s="75" t="n">
         <v>94975</v>
       </c>
       <c r="E60" t="inlineStr">
@@ -9670,7 +10071,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D61" s="72" t="n">
+      <c r="D61" s="75" t="n">
         <v>121093.68</v>
       </c>
       <c r="E61" t="inlineStr">
@@ -9695,7 +10096,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D62" s="72" t="n">
+      <c r="D62" s="75" t="n">
         <v>13011.85</v>
       </c>
       <c r="E62" t="inlineStr">
@@ -9720,7 +10121,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D63" s="72" t="n">
+      <c r="D63" s="75" t="n">
         <v>7000</v>
       </c>
       <c r="E63" t="inlineStr">
@@ -9745,7 +10146,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D64" s="72" t="n">
+      <c r="D64" s="75" t="n">
         <v>-273186</v>
       </c>
       <c r="E64" t="inlineStr">
@@ -9770,7 +10171,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D65" s="72" t="n">
+      <c r="D65" s="75" t="n">
         <v>-84146.62</v>
       </c>
       <c r="E65" t="inlineStr">
@@ -9795,7 +10196,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D66" s="72" t="n">
+      <c r="D66" s="75" t="n">
         <v>147839</v>
       </c>
       <c r="E66" t="inlineStr">
@@ -9820,7 +10221,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D67" s="72" t="n">
+      <c r="D67" s="75" t="n">
         <v>14870</v>
       </c>
       <c r="E67" t="inlineStr">
@@ -9845,7 +10246,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D68" s="72" t="n">
+      <c r="D68" s="75" t="n">
         <v>81647.35000000001</v>
       </c>
       <c r="E68" t="inlineStr">
@@ -9870,7 +10271,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D69" s="72" t="n">
+      <c r="D69" s="75" t="n">
         <v>8110.21</v>
       </c>
       <c r="E69" t="inlineStr">
@@ -9895,7 +10296,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D70" s="72" t="n">
+      <c r="D70" s="75" t="n">
         <v>14359</v>
       </c>
       <c r="E70" t="inlineStr">
@@ -9920,7 +10321,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D71" s="72" t="n">
+      <c r="D71" s="75" t="n">
         <v>-247975</v>
       </c>
       <c r="E71" t="inlineStr">
@@ -9945,7 +10346,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D72" s="72" t="n">
+      <c r="D72" s="75" t="n">
         <v>-62108.84</v>
       </c>
       <c r="E72" t="inlineStr">
@@ -9970,7 +10371,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D73" s="72" t="n">
+      <c r="D73" s="75" t="n">
         <v>108814.51</v>
       </c>
       <c r="E73" t="inlineStr">
@@ -9995,7 +10396,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D74" s="72" t="n">
+      <c r="D74" s="75" t="n">
         <v>15473</v>
       </c>
       <c r="E74" t="inlineStr">
@@ -10020,7 +10421,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D75" s="72" t="n">
+      <c r="D75" s="75" t="n">
         <v>84635.60000000001</v>
       </c>
       <c r="E75" t="inlineStr">
@@ -10045,7 +10446,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D76" s="72" t="n">
+      <c r="D76" s="75" t="n">
         <v>6455.93</v>
       </c>
       <c r="E76" t="inlineStr">
@@ -10070,7 +10471,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D77" s="72" t="n">
+      <c r="D77" s="75" t="n">
         <v>13363</v>
       </c>
       <c r="E77" t="inlineStr">
@@ -10095,7 +10496,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D78" s="72" t="n">
+      <c r="D78" s="75" t="n">
         <v>-234180</v>
       </c>
       <c r="E78" t="inlineStr">
@@ -10120,7 +10521,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D79" s="72" t="n">
+      <c r="D79" s="75" t="n">
         <v>12000</v>
       </c>
       <c r="E79" t="inlineStr">
@@ -10145,7 +10546,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D80" s="72" t="n">
+      <c r="D80" s="75" t="n">
         <v>5374.62</v>
       </c>
       <c r="E80" t="inlineStr">
@@ -10170,7 +10571,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D81" s="72" t="n">
+      <c r="D81" s="75" t="n">
         <v>55542</v>
       </c>
       <c r="E81" t="inlineStr">
@@ -10195,7 +10596,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D82" s="72" t="n">
+      <c r="D82" s="75" t="n">
         <v>15710</v>
       </c>
       <c r="E82" t="inlineStr">
@@ -10220,7 +10621,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D83" s="72" t="n">
+      <c r="D83" s="75" t="n">
         <v>88267.41</v>
       </c>
       <c r="E83" t="inlineStr">
@@ -10245,7 +10646,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D84" s="72" t="n">
+      <c r="D84" s="75" t="n">
         <v>5719.82</v>
       </c>
       <c r="E84" t="inlineStr">
@@ -10270,7 +10671,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D85" s="72" t="n">
+      <c r="D85" s="75" t="n">
         <v>13857</v>
       </c>
       <c r="E85" t="inlineStr">
@@ -10295,7 +10696,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D86" s="72" t="n">
+      <c r="D86" s="75" t="n">
         <v>2994</v>
       </c>
       <c r="E86" t="inlineStr">
@@ -10320,7 +10721,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D87" s="72" t="n">
+      <c r="D87" s="75" t="n">
         <v>71.34999999999999</v>
       </c>
       <c r="E87" t="inlineStr">
@@ -10345,7 +10746,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D88" s="72" t="n">
+      <c r="D88" s="75" t="n">
         <v>3085</v>
       </c>
       <c r="E88" t="inlineStr">
@@ -10370,7 +10771,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D89" s="72" t="n">
+      <c r="D89" s="75" t="n">
         <v>163.14</v>
       </c>
       <c r="E89" t="inlineStr">
@@ -10395,7 +10796,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D90" s="72" t="n">
+      <c r="D90" s="75" t="n">
         <v>4995</v>
       </c>
       <c r="E90" t="inlineStr">
@@ -10420,7 +10821,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D91" s="72" t="n">
+      <c r="D91" s="75" t="n">
         <v>53.55</v>
       </c>
       <c r="E91" t="inlineStr">
@@ -10445,7 +10846,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D92" s="72" t="n">
+      <c r="D92" s="75" t="n">
         <v>2944</v>
       </c>
       <c r="E92" t="inlineStr">
@@ -10470,7 +10871,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D93" s="72" t="n">
+      <c r="D93" s="75" t="n">
         <v>71.31</v>
       </c>
       <c r="E93" t="inlineStr">
@@ -10495,7 +10896,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D94" s="72" t="n">
+      <c r="D94" s="75" t="n">
         <v>2797</v>
       </c>
       <c r="E94" t="inlineStr">
@@ -10520,7 +10921,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D95" s="72" t="n">
+      <c r="D95" s="75" t="n">
         <v>148.11</v>
       </c>
       <c r="E95" t="inlineStr">
@@ -10545,7 +10946,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D96" s="72" t="n">
+      <c r="D96" s="75" t="n">
         <v>5196</v>
       </c>
       <c r="E96" t="inlineStr">
@@ -10570,7 +10971,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D97" s="72" t="n">
+      <c r="D97" s="75" t="n">
         <v>53.55</v>
       </c>
       <c r="E97" t="inlineStr">
@@ -10595,7 +10996,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D98" s="72" t="n">
+      <c r="D98" s="75" t="n">
         <v>-673859.71</v>
       </c>
       <c r="E98" t="inlineStr">
@@ -10620,7 +11021,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D99" s="72" t="n">
+      <c r="D99" s="75" t="n">
         <v>12508.63</v>
       </c>
       <c r="E99" t="inlineStr">
@@ -10645,7 +11046,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D100" s="72" t="n">
+      <c r="D100" s="75" t="n">
         <v>89815.85000000001</v>
       </c>
       <c r="E100" t="inlineStr">
@@ -10670,7 +11071,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D101" s="72" t="n">
+      <c r="D101" s="75" t="n">
         <v>-1569420.99</v>
       </c>
       <c r="E101" t="inlineStr">
@@ -10695,7 +11096,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D102" s="72" t="n">
+      <c r="D102" s="75" t="n">
         <v>2956</v>
       </c>
       <c r="E102" t="inlineStr">
@@ -10720,7 +11121,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D103" s="72" t="n">
+      <c r="D103" s="75" t="n">
         <v>79366.3</v>
       </c>
       <c r="E103" t="inlineStr">
@@ -10745,7 +11146,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D104" s="72" t="n">
+      <c r="D104" s="75" t="n">
         <v>2823</v>
       </c>
       <c r="E104" t="inlineStr">
@@ -10770,7 +11171,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D105" s="72" t="n">
+      <c r="D105" s="75" t="n">
         <v>146.62</v>
       </c>
       <c r="E105" t="inlineStr">
@@ -10795,7 +11196,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D106" s="72" t="n">
+      <c r="D106" s="75" t="n">
         <v>220492.18</v>
       </c>
       <c r="E106" t="inlineStr">
@@ -10820,7 +11221,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D107" s="72" t="n">
+      <c r="D107" s="75" t="n">
         <v>621319.65</v>
       </c>
       <c r="E107" t="inlineStr">
@@ -10845,7 +11246,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D108" s="72" t="n">
+      <c r="D108" s="75" t="n">
         <v>253612.21</v>
       </c>
       <c r="E108" t="inlineStr">
@@ -10870,7 +11271,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D109" s="72" t="n">
+      <c r="D109" s="75" t="n">
         <v>168226.05</v>
       </c>
       <c r="E109" t="inlineStr">
@@ -10895,7 +11296,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D110" s="72" t="n">
+      <c r="D110" s="75" t="n">
         <v>92484.47</v>
       </c>
       <c r="E110" t="inlineStr">
@@ -10920,7 +11321,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D111" s="72" t="n">
+      <c r="D111" s="75" t="n">
         <v>196184</v>
       </c>
       <c r="E111" t="inlineStr">
@@ -10945,7 +11346,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D112" s="72" t="n">
+      <c r="D112" s="75" t="n">
         <v>-1845734.44</v>
       </c>
       <c r="E112" t="inlineStr">
@@ -10970,7 +11371,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D113" s="72" t="n">
+      <c r="D113" s="75" t="n">
         <v>-773623.08</v>
       </c>
       <c r="E113" t="inlineStr">
@@ -10995,7 +11396,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D114" s="72" t="n">
+      <c r="D114" s="75" t="n">
         <v>293846.95</v>
       </c>
       <c r="E114" t="inlineStr">
@@ -11020,7 +11421,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D115" s="72" t="n">
+      <c r="D115" s="75" t="n">
         <v>265493.63</v>
       </c>
       <c r="E115" t="inlineStr">
@@ -11045,7 +11446,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D116" s="72" t="n">
+      <c r="D116" s="75" t="n">
         <v>191530.24</v>
       </c>
       <c r="E116" t="inlineStr">
@@ -11070,7 +11471,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D117" s="72" t="n">
+      <c r="D117" s="75" t="n">
         <v>11587</v>
       </c>
       <c r="E117" t="inlineStr">
@@ -11095,7 +11496,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D118" s="72" t="n">
+      <c r="D118" s="75" t="n">
         <v>93057.11</v>
       </c>
       <c r="E118" t="inlineStr">
@@ -11120,7 +11521,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D119" s="72" t="n">
+      <c r="D119" s="75" t="n">
         <v>528052.08</v>
       </c>
       <c r="E119" t="inlineStr">
@@ -11145,7 +11546,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D120" s="72" t="n">
+      <c r="D120" s="75" t="n">
         <v>116416.16</v>
       </c>
       <c r="E120" t="inlineStr">
@@ -11170,7 +11571,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D121" s="72" t="n">
+      <c r="D121" s="75" t="n">
         <v>146015.91</v>
       </c>
       <c r="E121" t="inlineStr">
@@ -11195,7 +11596,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D122" s="72" t="n">
+      <c r="D122" s="75" t="n">
         <v>95218.77</v>
       </c>
       <c r="E122" t="inlineStr">
@@ -11220,7 +11621,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D123" s="72" t="n">
+      <c r="D123" s="75" t="n">
         <v>195095</v>
       </c>
       <c r="E123" t="inlineStr">
@@ -11245,7 +11646,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D124" s="72" t="n">
+      <c r="D124" s="75" t="n">
         <v>-1846103.64</v>
       </c>
       <c r="E124" t="inlineStr">
@@ -11270,7 +11671,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D125" s="72" t="n">
+      <c r="D125" s="75" t="n">
         <v>-277628.05</v>
       </c>
       <c r="E125" t="inlineStr">
@@ -11295,7 +11696,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D126" s="72" t="n">
+      <c r="D126" s="75" t="n">
         <v>398.98</v>
       </c>
       <c r="E126" t="inlineStr">
@@ -11320,7 +11721,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D127" s="72" t="n">
+      <c r="D127" s="75" t="n">
         <v>262708.89</v>
       </c>
       <c r="E127" t="inlineStr">
@@ -11345,7 +11746,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D128" s="72" t="n">
+      <c r="D128" s="75" t="n">
         <v>263448.71</v>
       </c>
       <c r="E128" t="inlineStr">
@@ -11370,7 +11771,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D129" s="72" t="n">
+      <c r="D129" s="75" t="n">
         <v>259227.76</v>
       </c>
       <c r="E129" t="inlineStr">
@@ -11395,7 +11796,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D130" s="72" t="n">
+      <c r="D130" s="75" t="n">
         <v>406354.65</v>
       </c>
       <c r="E130" t="inlineStr">
@@ -11420,7 +11821,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D131" s="72" t="n">
+      <c r="D131" s="75" t="n">
         <v>77648.91</v>
       </c>
       <c r="E131" t="inlineStr">
@@ -11445,7 +11846,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D132" s="72" t="n">
+      <c r="D132" s="75" t="n">
         <v>102761.37</v>
       </c>
       <c r="E132" t="inlineStr">
@@ -11470,7 +11871,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D133" s="72" t="n">
+      <c r="D133" s="75" t="n">
         <v>78647.42999999999</v>
       </c>
       <c r="E133" t="inlineStr">
@@ -11495,7 +11896,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D134" s="72" t="n">
+      <c r="D134" s="75" t="n">
         <v>144978</v>
       </c>
       <c r="E134" t="inlineStr">
@@ -11520,7 +11921,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D135" s="72" t="n">
+      <c r="D135" s="75" t="n">
         <v>-1787344.57</v>
       </c>
       <c r="E135" t="inlineStr">
@@ -11545,7 +11946,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D136" s="72" t="n">
+      <c r="D136" s="75" t="n">
         <v>246909.77</v>
       </c>
       <c r="E136" t="inlineStr">
@@ -11570,7 +11971,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D137" s="72" t="n">
+      <c r="D137" s="75" t="n">
         <v>199861.29</v>
       </c>
       <c r="E137" t="inlineStr">
@@ -11595,7 +11996,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D138" s="72" t="n">
+      <c r="D138" s="75" t="n">
         <v>338592.34</v>
       </c>
       <c r="E138" t="inlineStr">
@@ -11620,7 +12021,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D139" s="72" t="n">
+      <c r="D139" s="75" t="n">
         <v>-95567.31</v>
       </c>
       <c r="E139" t="inlineStr">
@@ -11645,7 +12046,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D140" s="72" t="n">
+      <c r="D140" s="75" t="n">
         <v>-4000</v>
       </c>
       <c r="E140" t="inlineStr">
@@ -11670,7 +12071,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D141" s="72" t="n">
+      <c r="D141" s="75" t="n">
         <v>49571.73</v>
       </c>
       <c r="E141" t="inlineStr">
@@ -11695,7 +12096,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D142" s="72" t="n">
+      <c r="D142" s="75" t="n">
         <v>9462.879999999999</v>
       </c>
       <c r="E142" t="inlineStr">
@@ -11720,7 +12121,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D143" s="72" t="n">
+      <c r="D143" s="75" t="n">
         <v>2968.54</v>
       </c>
       <c r="E143" t="inlineStr">
@@ -11745,7 +12146,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D144" s="72" t="n">
+      <c r="D144" s="75" t="n">
         <v>11858</v>
       </c>
       <c r="E144" t="inlineStr">
@@ -11770,7 +12171,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D145" s="72" t="n">
+      <c r="D145" s="75" t="n">
         <v>26947.11</v>
       </c>
       <c r="E145" t="inlineStr">
@@ -11795,7 +12196,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D146" s="72" t="n">
+      <c r="D146" s="75" t="n">
         <v>4362.05</v>
       </c>
       <c r="E146" t="inlineStr">
@@ -11820,7 +12221,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D147" s="72" t="n">
+      <c r="D147" s="75" t="n">
         <v>9729.889999999999</v>
       </c>
       <c r="E147" t="inlineStr">
@@ -11845,7 +12246,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D148" s="72" t="n">
+      <c r="D148" s="75" t="n">
         <v>14786</v>
       </c>
       <c r="E148" t="inlineStr">
@@ -11870,7 +12271,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D149" s="72" t="n">
+      <c r="D149" s="75" t="n">
         <v>-25000</v>
       </c>
       <c r="E149" t="inlineStr">
@@ -11895,7 +12296,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D150" s="72" t="n">
+      <c r="D150" s="75" t="n">
         <v>11691.11</v>
       </c>
       <c r="E150" t="inlineStr">
@@ -11920,7 +12321,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D151" s="72" t="n">
+      <c r="D151" s="75" t="n">
         <v>353.66</v>
       </c>
       <c r="E151" t="inlineStr">
@@ -11945,7 +12346,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D152" s="72" t="n">
+      <c r="D152" s="75" t="n">
         <v>2978.98</v>
       </c>
       <c r="E152" t="inlineStr">
@@ -11970,7 +12371,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D153" s="72" t="n">
+      <c r="D153" s="75" t="n">
         <v>1405.28</v>
       </c>
       <c r="E153" t="inlineStr">
@@ -11995,7 +12396,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D154" s="72" t="n">
+      <c r="D154" s="75" t="n">
         <v>31.2</v>
       </c>
       <c r="E154" t="inlineStr">
@@ -12020,7 +12421,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D155" s="72" t="n">
+      <c r="D155" s="75" t="n">
         <v>-120000</v>
       </c>
       <c r="E155" t="inlineStr">
@@ -12045,7 +12446,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D156" s="72" t="n">
+      <c r="D156" s="75" t="n">
         <v>9970.26</v>
       </c>
       <c r="E156" t="inlineStr">
@@ -12070,7 +12471,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D157" s="72" t="n">
+      <c r="D157" s="75" t="n">
         <v>80.48999999999999</v>
       </c>
       <c r="E157" t="inlineStr">
@@ -12095,7 +12496,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D158" s="72" t="n">
+      <c r="D158" s="75" t="n">
         <v>3536.61</v>
       </c>
       <c r="E158" t="inlineStr">
@@ -12120,7 +12521,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D159" s="72" t="n">
+      <c r="D159" s="75" t="n">
         <v>659.65</v>
       </c>
       <c r="E159" t="inlineStr">
@@ -12145,7 +12546,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D160" s="72" t="n">
+      <c r="D160" s="75" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="E160" t="inlineStr">
@@ -12170,7 +12571,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D161" s="72" t="n">
+      <c r="D161" s="75" t="n">
         <v>-182159.16</v>
       </c>
       <c r="E161" t="inlineStr">
@@ -12195,7 +12596,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D162" s="72" t="n">
+      <c r="D162" s="75" t="n">
         <v>27832.1</v>
       </c>
       <c r="E162" t="inlineStr">
@@ -12220,7 +12621,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D163" s="72" t="n">
+      <c r="D163" s="75" t="n">
         <v>69042.92999999999</v>
       </c>
       <c r="E163" t="inlineStr">
@@ -12245,7 +12646,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D164" s="72" t="n">
+      <c r="D164" s="75" t="n">
         <v>-63372</v>
       </c>
       <c r="E164" t="inlineStr">
@@ -12270,7 +12671,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D165" s="72" t="n">
+      <c r="D165" s="75" t="n">
         <v>21629.4</v>
       </c>
       <c r="E165" t="inlineStr">
@@ -12295,7 +12696,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D166" s="72" t="n">
+      <c r="D166" s="75" t="n">
         <v>3911.77</v>
       </c>
       <c r="E166" t="inlineStr">
@@ -12320,7 +12721,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D167" s="72" t="n">
+      <c r="D167" s="75" t="n">
         <v>84249.49000000001</v>
       </c>
       <c r="E167" t="inlineStr">
@@ -12345,7 +12746,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D168" s="72" t="n">
+      <c r="D168" s="75" t="n">
         <v>31662.59</v>
       </c>
       <c r="E168" t="inlineStr">
@@ -12370,7 +12771,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D169" s="72" t="n">
+      <c r="D169" s="75" t="n">
         <v>3035.5</v>
       </c>
       <c r="E169" t="inlineStr">
@@ -12395,7 +12796,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D170" s="72" t="n">
+      <c r="D170" s="75" t="n">
         <v>16179</v>
       </c>
       <c r="E170" t="inlineStr">
@@ -12420,7 +12821,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D171" s="72" t="n">
+      <c r="D171" s="75" t="n">
         <v>7029.13</v>
       </c>
       <c r="E171" t="inlineStr">
@@ -12445,7 +12846,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D172" s="72" t="n">
+      <c r="D172" s="75" t="n">
         <v>-252814.41</v>
       </c>
       <c r="E172" t="inlineStr">
@@ -12470,7 +12871,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D173" s="72" t="n">
+      <c r="D173" s="75" t="n">
         <v>25803.7</v>
       </c>
       <c r="E173" t="inlineStr">
@@ -12495,7 +12896,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D174" s="72" t="n">
+      <c r="D174" s="75" t="n">
         <v>94213.14999999999</v>
       </c>
       <c r="E174" t="inlineStr">
@@ -12520,7 +12921,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D175" s="72" t="n">
+      <c r="D175" s="75" t="n">
         <v>-105000</v>
       </c>
       <c r="E175" t="inlineStr">
@@ -12545,7 +12946,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D176" s="72" t="n">
+      <c r="D176" s="75" t="n">
         <v>42360.83</v>
       </c>
       <c r="E176" t="inlineStr">
@@ -12570,7 +12971,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D177" s="72" t="n">
+      <c r="D177" s="75" t="n">
         <v>15237.12</v>
       </c>
       <c r="E177" t="inlineStr">
@@ -12595,7 +12996,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D178" s="72" t="n">
+      <c r="D178" s="75" t="n">
         <v>84280.23</v>
       </c>
       <c r="E178" t="inlineStr">
@@ -12620,7 +13021,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D179" s="72" t="n">
+      <c r="D179" s="75" t="n">
         <v>39485.9</v>
       </c>
       <c r="E179" t="inlineStr">
@@ -12645,7 +13046,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D180" s="72" t="n">
+      <c r="D180" s="75" t="n">
         <v>30521.91</v>
       </c>
       <c r="E180" t="inlineStr">
@@ -12670,7 +13071,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D181" s="72" t="n">
+      <c r="D181" s="75" t="n">
         <v>7464</v>
       </c>
       <c r="E181" t="inlineStr">
@@ -12695,7 +13096,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D182" s="72" t="n">
+      <c r="D182" s="75" t="n">
         <v>7661.21</v>
       </c>
       <c r="E182" t="inlineStr">
@@ -12720,7 +13121,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D183" s="72" t="n">
+      <c r="D183" s="75" t="n">
         <v>1145</v>
       </c>
       <c r="E183" t="inlineStr">
@@ -12745,7 +13146,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D184" s="72" t="n">
+      <c r="D184" s="75" t="n">
         <v>-1040169.25</v>
       </c>
       <c r="E184" t="inlineStr">
@@ -12770,7 +13171,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D185" s="72" t="n">
+      <c r="D185" s="75" t="n">
         <v>24267.6</v>
       </c>
       <c r="E185" t="inlineStr">
@@ -12795,7 +13196,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D186" s="72" t="n">
+      <c r="D186" s="75" t="n">
         <v>335260.06</v>
       </c>
       <c r="E186" t="inlineStr">
@@ -12820,7 +13221,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D187" s="72" t="n">
+      <c r="D187" s="75" t="n">
         <v>12000</v>
       </c>
       <c r="E187" t="inlineStr">
@@ -12845,7 +13246,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D188" s="72" t="n">
+      <c r="D188" s="75" t="n">
         <v>306127.7</v>
       </c>
       <c r="E188" t="inlineStr">
@@ -12870,7 +13271,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D189" s="72" t="n">
+      <c r="D189" s="75" t="n">
         <v>28545.56</v>
       </c>
       <c r="E189" t="inlineStr">
@@ -12895,7 +13296,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D190" s="72" t="n">
+      <c r="D190" s="75" t="n">
         <v>84158.63</v>
       </c>
       <c r="E190" t="inlineStr">
@@ -12920,7 +13321,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D191" s="72" t="n">
+      <c r="D191" s="75" t="n">
         <v>40897.33</v>
       </c>
       <c r="E191" t="inlineStr">
@@ -12945,7 +13346,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D192" s="72" t="n">
+      <c r="D192" s="75" t="n">
         <v>155731.54</v>
       </c>
       <c r="E192" t="inlineStr">
@@ -12970,7 +13371,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D193" s="72" t="n">
+      <c r="D193" s="75" t="n">
         <v>6720</v>
       </c>
       <c r="E193" t="inlineStr">
@@ -12995,7 +13396,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D194" s="72" t="n">
+      <c r="D194" s="75" t="n">
         <v>11168.8</v>
       </c>
       <c r="E194" t="inlineStr">
@@ -13020,7 +13421,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D195" s="72" t="n">
+      <c r="D195" s="75" t="n">
         <v>4347</v>
       </c>
       <c r="E195" t="inlineStr">
@@ -13045,7 +13446,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D196" s="72" t="n">
+      <c r="D196" s="75" t="n">
         <v>-36500</v>
       </c>
       <c r="E196" t="inlineStr">
@@ -13070,7 +13471,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D197" s="72" t="n">
+      <c r="D197" s="75" t="n">
         <v>682935.3</v>
       </c>
       <c r="E197" t="inlineStr">
@@ -13095,7 +13496,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D198" s="72" t="n">
+      <c r="D198" s="75" t="n">
         <v>89528.25</v>
       </c>
       <c r="E198" t="inlineStr">
@@ -13120,7 +13521,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D199" s="72" t="n">
+      <c r="D199" s="75" t="n">
         <v>34311.46</v>
       </c>
       <c r="E199" t="inlineStr">
@@ -13145,7 +13546,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D200" s="72" t="n">
+      <c r="D200" s="75" t="n">
         <v>-1276087.3</v>
       </c>
       <c r="E200" t="inlineStr">
@@ -13170,7 +13571,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D201" s="72" t="n">
+      <c r="D201" s="75" t="n">
         <v>119684.05</v>
       </c>
       <c r="E201" t="inlineStr">
@@ -13195,7 +13596,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D202" s="72" t="n">
+      <c r="D202" s="75" t="n">
         <v>461523.69</v>
       </c>
       <c r="E202" t="inlineStr">
@@ -13220,7 +13621,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D203" s="72" t="n">
+      <c r="D203" s="75" t="n">
         <v>70350.57000000001</v>
       </c>
       <c r="E203" t="inlineStr">
@@ -13245,7 +13646,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D204" s="72" t="n">
+      <c r="D204" s="75" t="n">
         <v>85236.12</v>
       </c>
       <c r="E204" t="inlineStr">
@@ -13270,7 +13671,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D205" s="72" t="n">
+      <c r="D205" s="75" t="n">
         <v>25179.13</v>
       </c>
       <c r="E205" t="inlineStr">
@@ -13295,7 +13696,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D206" s="72" t="n">
+      <c r="D206" s="75" t="n">
         <v>74422.25999999999</v>
       </c>
       <c r="E206" t="inlineStr">
@@ -13320,7 +13721,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D207" s="72" t="n">
+      <c r="D207" s="75" t="n">
         <v>47.32</v>
       </c>
       <c r="E207" t="inlineStr">
@@ -13345,7 +13746,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D208" s="72" t="n">
+      <c r="D208" s="75" t="n">
         <v>6971.72</v>
       </c>
       <c r="E208" t="inlineStr">
@@ -13370,7 +13771,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D209" s="72" t="n">
+      <c r="D209" s="75" t="n">
         <v>1030.5</v>
       </c>
       <c r="E209" t="inlineStr">
@@ -13395,7 +13796,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D210" s="72" t="n">
+      <c r="D210" s="75" t="n">
         <v>-60617.22</v>
       </c>
       <c r="E210" t="inlineStr">
@@ -13420,7 +13821,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D211" s="72" t="n">
+      <c r="D211" s="75" t="n">
         <v>7827.94</v>
       </c>
       <c r="E211" t="inlineStr">
@@ -13445,7 +13846,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D212" s="72" t="n">
+      <c r="D212" s="75" t="n">
         <v>28798.6</v>
       </c>
       <c r="E212" t="inlineStr">
@@ -13470,7 +13871,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D213" s="72" t="n">
+      <c r="D213" s="75" t="n">
         <v>160</v>
       </c>
       <c r="E213" t="inlineStr">
@@ -13495,7 +13896,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D214" s="72" t="n">
+      <c r="D214" s="75" t="n">
         <v>17017.8</v>
       </c>
       <c r="E214" t="inlineStr">
@@ -13520,7 +13921,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D215" s="72" t="n">
+      <c r="D215" s="75" t="n">
         <v>8.15</v>
       </c>
       <c r="E215" t="inlineStr">
@@ -13545,7 +13946,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D216" s="72" t="n">
+      <c r="D216" s="75" t="n">
         <v>5393.52</v>
       </c>
       <c r="E216" t="inlineStr">
@@ -13570,7 +13971,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D217" s="72" t="n">
+      <c r="D217" s="75" t="n">
         <v>1690.87</v>
       </c>
       <c r="E217" t="inlineStr">
@@ -13595,7 +13996,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D218" s="72" t="n">
+      <c r="D218" s="75" t="n">
         <v>3819</v>
       </c>
       <c r="E218" t="inlineStr">
@@ -13620,7 +14021,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D219" s="72" t="n">
+      <c r="D219" s="75" t="n">
         <v>1623</v>
       </c>
       <c r="E219" t="inlineStr">
@@ -13645,7 +14046,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D220" s="72" t="n">
+      <c r="D220" s="75" t="n">
         <v>-4020097.09</v>
       </c>
       <c r="E220" t="inlineStr">
@@ -13670,7 +14071,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D221" s="72" t="n">
+      <c r="D221" s="75" t="n">
         <v>36589.58</v>
       </c>
       <c r="E221" t="inlineStr">
@@ -13695,7 +14096,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D222" s="72" t="n">
+      <c r="D222" s="75" t="n">
         <v>-21238.18</v>
       </c>
       <c r="E222" t="inlineStr">
@@ -13720,7 +14121,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D223" s="72" t="n">
+      <c r="D223" s="75" t="n">
         <v>1134014.92</v>
       </c>
       <c r="E223" t="inlineStr">
@@ -13745,7 +14146,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D224" s="72" t="n">
+      <c r="D224" s="75" t="n">
         <v>128437.63</v>
       </c>
       <c r="E224" t="inlineStr">
@@ -13770,7 +14171,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D225" s="72" t="n">
+      <c r="D225" s="75" t="n">
         <v>1648002.47</v>
       </c>
       <c r="E225" t="inlineStr">
@@ -13795,7 +14196,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D226" s="72" t="n">
+      <c r="D226" s="75" t="n">
         <v>285429.57</v>
       </c>
       <c r="E226" t="inlineStr">
@@ -13820,7 +14221,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D227" s="72" t="n">
+      <c r="D227" s="75" t="n">
         <v>112954.41</v>
       </c>
       <c r="E227" t="inlineStr">
@@ -13845,7 +14246,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D228" s="72" t="n">
+      <c r="D228" s="75" t="n">
         <v>152125.33</v>
       </c>
       <c r="E228" t="inlineStr">
@@ -13870,7 +14271,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D229" s="72" t="n">
+      <c r="D229" s="75" t="n">
         <v>119756.18</v>
       </c>
       <c r="E229" t="inlineStr">
@@ -13895,7 +14296,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D230" s="72" t="n">
+      <c r="D230" s="75" t="n">
         <v>115151</v>
       </c>
       <c r="E230" t="inlineStr">
@@ -13920,7 +14321,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D231" s="72" t="n">
+      <c r="D231" s="75" t="n">
         <v>55522</v>
       </c>
       <c r="E231" t="inlineStr">
@@ -13945,7 +14346,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D232" s="72" t="n">
+      <c r="D232" s="75" t="n">
         <v>-3945668.63</v>
       </c>
       <c r="E232" t="inlineStr">
@@ -13970,7 +14371,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D233" s="72" t="n">
+      <c r="D233" s="75" t="n">
         <v>51950.17</v>
       </c>
       <c r="E233" t="inlineStr">
@@ -13995,7 +14396,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D234" s="72" t="n">
+      <c r="D234" s="75" t="n">
         <v>1336954</v>
       </c>
       <c r="E234" t="inlineStr">
@@ -14020,7 +14421,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D235" s="72" t="n">
+      <c r="D235" s="75" t="n">
         <v>104164.1</v>
       </c>
       <c r="E235" t="inlineStr">
@@ -14045,7 +14446,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D236" s="72" t="n">
+      <c r="D236" s="75" t="n">
         <v>1410408.29</v>
       </c>
       <c r="E236" t="inlineStr">
@@ -14070,7 +14471,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D237" s="72" t="n">
+      <c r="D237" s="75" t="n">
         <v>204074.66</v>
       </c>
       <c r="E237" t="inlineStr">
@@ -14095,7 +14496,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D238" s="72" t="n">
+      <c r="D238" s="75" t="n">
         <v>162786.02</v>
       </c>
       <c r="E238" t="inlineStr">
@@ -14120,7 +14521,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D239" s="72" t="n">
+      <c r="D239" s="75" t="n">
         <v>74927.98</v>
       </c>
       <c r="E239" t="inlineStr">
@@ -14145,7 +14546,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D240" s="72" t="n">
+      <c r="D240" s="75" t="n">
         <v>102454.37</v>
       </c>
       <c r="E240" t="inlineStr">
@@ -14170,7 +14571,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D241" s="72" t="n">
+      <c r="D241" s="75" t="n">
         <v>75441</v>
       </c>
       <c r="E241" t="inlineStr">
@@ -14195,7 +14596,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D242" s="72" t="n">
+      <c r="D242" s="75" t="n">
         <v>12250</v>
       </c>
       <c r="E242" t="inlineStr">
@@ -14220,7 +14621,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D243" s="72" t="n">
+      <c r="D243" s="75" t="n">
         <v>-4192108.18</v>
       </c>
       <c r="E243" t="inlineStr">
@@ -14245,7 +14646,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D244" s="72" t="n">
+      <c r="D244" s="75" t="n">
         <v>47186.32</v>
       </c>
       <c r="E244" t="inlineStr">
@@ -14270,7 +14671,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D245" s="72" t="n">
+      <c r="D245" s="75" t="n">
         <v>1435652.25</v>
       </c>
       <c r="E245" t="inlineStr">
@@ -14295,7 +14696,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D246" s="72" t="n">
+      <c r="D246" s="75" t="n">
         <v>89534.44</v>
       </c>
       <c r="E246" t="inlineStr">
@@ -14320,7 +14721,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D247" s="72" t="n">
+      <c r="D247" s="75" t="n">
         <v>28000</v>
       </c>
       <c r="E247" t="inlineStr">
@@ -14345,7 +14746,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D248" s="72" t="n">
+      <c r="D248" s="75" t="n">
         <v>1565414.79</v>
       </c>
       <c r="E248" t="inlineStr">
@@ -14370,7 +14771,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D249" s="72" t="n">
+      <c r="D249" s="75" t="n">
         <v>159546.21</v>
       </c>
       <c r="E249" t="inlineStr">
@@ -14395,7 +14796,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D250" s="72" t="n">
+      <c r="D250" s="75" t="n">
         <v>110590.5</v>
       </c>
       <c r="E250" t="inlineStr">
@@ -14420,7 +14821,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D251" s="72" t="n">
+      <c r="D251" s="75" t="n">
         <v>102861.78</v>
       </c>
       <c r="E251" t="inlineStr">
@@ -14445,7 +14846,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D252" s="72" t="n">
+      <c r="D252" s="75" t="n">
         <v>95846.64999999999</v>
       </c>
       <c r="E252" t="inlineStr">
@@ -14470,7 +14871,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D253" s="72" t="n">
+      <c r="D253" s="75" t="n">
         <v>45876</v>
       </c>
       <c r="E253" t="inlineStr">
@@ -14495,7 +14896,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D254" s="72" t="n">
+      <c r="D254" s="75" t="n">
         <v>83963</v>
       </c>
       <c r="E254" t="inlineStr">
@@ -14520,7 +14921,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D255" s="72" t="n">
+      <c r="D255" s="75" t="n">
         <v>-1606736.08</v>
       </c>
       <c r="E255" t="inlineStr">
@@ -14545,7 +14946,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D256" s="72" t="n">
+      <c r="D256" s="75" t="n">
         <v>11810.27</v>
       </c>
       <c r="E256" t="inlineStr">
@@ -14570,7 +14971,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D257" s="72" t="n">
+      <c r="D257" s="75" t="n">
         <v>83140.49000000001</v>
       </c>
       <c r="E257" t="inlineStr">
@@ -14595,7 +14996,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D258" s="72" t="n">
+      <c r="D258" s="75" t="n">
         <v>35063.04</v>
       </c>
       <c r="E258" t="inlineStr">
@@ -14620,7 +15021,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D259" s="72" t="n">
+      <c r="D259" s="75" t="n">
         <v>51872</v>
       </c>
       <c r="E259" t="inlineStr">
@@ -14645,7 +15046,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D260" s="72" t="n">
+      <c r="D260" s="75" t="n">
         <v>712190.6899999999</v>
       </c>
       <c r="E260" t="inlineStr">
@@ -14670,7 +15071,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D261" s="72" t="n">
+      <c r="D261" s="75" t="n">
         <v>371058.72</v>
       </c>
       <c r="E261" t="inlineStr">
@@ -14695,7 +15096,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D262" s="72" t="n">
+      <c r="D262" s="75" t="n">
         <v>63879.98</v>
       </c>
       <c r="E262" t="inlineStr">
@@ -14720,7 +15121,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D263" s="72" t="n">
+      <c r="D263" s="75" t="n">
         <v>14521.69</v>
       </c>
       <c r="E263" t="inlineStr">
@@ -14745,7 +15146,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D264" s="72" t="n">
+      <c r="D264" s="75" t="n">
         <v>267190.19</v>
       </c>
       <c r="E264" t="inlineStr">
@@ -14770,7 +15171,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D265" s="72" t="n">
+      <c r="D265" s="75" t="n">
         <v>15416</v>
       </c>
       <c r="E265" t="inlineStr">
@@ -14795,7 +15196,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D266" s="72" t="n">
+      <c r="D266" s="75" t="n">
         <v>-1854065.71</v>
       </c>
       <c r="E266" t="inlineStr">
@@ -14820,7 +15221,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D267" s="72" t="n">
+      <c r="D267" s="75" t="n">
         <v>14821.35</v>
       </c>
       <c r="E267" t="inlineStr">
@@ -14845,7 +15246,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D268" s="72" t="n">
+      <c r="D268" s="75" t="n">
         <v>54056.48</v>
       </c>
       <c r="E268" t="inlineStr">
@@ -14870,7 +15271,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D269" s="72" t="n">
+      <c r="D269" s="75" t="n">
         <v>30851.77</v>
       </c>
       <c r="E269" t="inlineStr">
@@ -14895,7 +15296,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D270" s="72" t="n">
+      <c r="D270" s="75" t="n">
         <v>862520.42</v>
       </c>
       <c r="E270" t="inlineStr">
@@ -14920,7 +15321,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D271" s="72" t="n">
+      <c r="D271" s="75" t="n">
         <v>360373.72</v>
       </c>
       <c r="E271" t="inlineStr">
@@ -14945,7 +15346,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D272" s="72" t="n">
+      <c r="D272" s="75" t="n">
         <v>84572.03</v>
       </c>
       <c r="E272" t="inlineStr">
@@ -14970,7 +15371,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D273" s="72" t="n">
+      <c r="D273" s="75" t="n">
         <v>27503.48</v>
       </c>
       <c r="E273" t="inlineStr">
@@ -14995,7 +15396,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D274" s="72" t="n">
+      <c r="D274" s="75" t="n">
         <v>371929.89</v>
       </c>
       <c r="E274" t="inlineStr">
@@ -15020,7 +15421,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D275" s="72" t="n">
+      <c r="D275" s="75" t="n">
         <v>11293</v>
       </c>
       <c r="E275" t="inlineStr">
@@ -15045,7 +15446,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D276" s="72" t="n">
+      <c r="D276" s="75" t="n">
         <v>4426</v>
       </c>
       <c r="E276" t="inlineStr">
@@ -15070,7 +15471,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D277" s="72" t="n">
+      <c r="D277" s="75" t="n">
         <v>-1793621.56</v>
       </c>
       <c r="E277" t="inlineStr">
@@ -15095,7 +15496,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D278" s="72" t="n">
+      <c r="D278" s="75" t="n">
         <v>14534.84</v>
       </c>
       <c r="E278" t="inlineStr">
@@ -15120,7 +15521,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D279" s="72" t="n">
+      <c r="D279" s="75" t="n">
         <v>65906.69</v>
       </c>
       <c r="E279" t="inlineStr">
@@ -15145,7 +15546,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D280" s="72" t="n">
+      <c r="D280" s="75" t="n">
         <v>31042.81</v>
       </c>
       <c r="E280" t="inlineStr">
@@ -15170,7 +15571,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D281" s="72" t="n">
+      <c r="D281" s="75" t="n">
         <v>96000</v>
       </c>
       <c r="E281" t="inlineStr">
@@ -15195,7 +15596,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D282" s="72" t="n">
+      <c r="D282" s="75" t="n">
         <v>745956.71</v>
       </c>
       <c r="E282" t="inlineStr">
@@ -15220,7 +15621,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D283" s="72" t="n">
+      <c r="D283" s="75" t="n">
         <v>430360.81</v>
       </c>
       <c r="E283" t="inlineStr">
@@ -15245,7 +15646,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D284" s="72" t="n">
+      <c r="D284" s="75" t="n">
         <v>63947.25</v>
       </c>
       <c r="E284" t="inlineStr">
@@ -15270,7 +15671,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D285" s="72" t="n">
+      <c r="D285" s="75" t="n">
         <v>20527.86</v>
       </c>
       <c r="E285" t="inlineStr">
@@ -15295,7 +15696,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D286" s="72" t="n">
+      <c r="D286" s="75" t="n">
         <v>230794.19</v>
       </c>
       <c r="E286" t="inlineStr">
@@ -15320,7 +15721,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D287" s="72" t="n">
+      <c r="D287" s="75" t="n">
         <v>7171</v>
       </c>
       <c r="E287" t="inlineStr">
@@ -15345,7 +15746,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D288" s="72" t="n">
+      <c r="D288" s="75" t="n">
         <v>11162</v>
       </c>
       <c r="E288" t="inlineStr">
@@ -15370,7 +15771,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D289" s="72" t="n">
+      <c r="D289" s="75" t="n">
         <v>19007.52</v>
       </c>
       <c r="E289" t="inlineStr">
@@ -15395,7 +15796,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D290" s="72" t="n">
+      <c r="D290" s="75" t="n">
         <v>-109765.32</v>
       </c>
       <c r="E290" t="inlineStr">
@@ -15420,7 +15821,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D291" s="72" t="n">
+      <c r="D291" s="75" t="n">
         <v>194.47</v>
       </c>
       <c r="E291" t="inlineStr">
@@ -15445,7 +15846,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D292" s="72" t="n">
+      <c r="D292" s="75" t="n">
         <v>36000</v>
       </c>
       <c r="E292" t="inlineStr">
@@ -15470,7 +15871,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D293" s="72" t="n">
+      <c r="D293" s="75" t="n">
         <v>7991.46</v>
       </c>
       <c r="E293" t="inlineStr">
@@ -15495,7 +15896,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D294" s="72" t="n">
+      <c r="D294" s="75" t="n">
         <v>20030</v>
       </c>
       <c r="E294" t="inlineStr">
@@ -15520,7 +15921,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D295" s="72" t="n">
+      <c r="D295" s="75" t="n">
         <v>461.73</v>
       </c>
       <c r="E295" t="inlineStr">
@@ -15545,7 +15946,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D296" s="72" t="n">
+      <c r="D296" s="75" t="n">
         <v>4196</v>
       </c>
       <c r="E296" t="inlineStr">
@@ -15570,7 +15971,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D297" s="72" t="n">
+      <c r="D297" s="75" t="n">
         <v>19007.52</v>
       </c>
       <c r="E297" t="inlineStr">
@@ -15595,7 +15996,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D298" s="72" t="n">
+      <c r="D298" s="75" t="n">
         <v>-109765.32</v>
       </c>
       <c r="E298" t="inlineStr">
@@ -15620,7 +16021,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D299" s="72" t="n">
+      <c r="D299" s="75" t="n">
         <v>4960.18</v>
       </c>
       <c r="E299" t="inlineStr">
@@ -15645,7 +16046,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D300" s="72" t="n">
+      <c r="D300" s="75" t="n">
         <v>25000</v>
       </c>
       <c r="E300" t="inlineStr">
@@ -15670,7 +16071,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D301" s="72" t="n">
+      <c r="D301" s="75" t="n">
         <v>12837.77</v>
       </c>
       <c r="E301" t="inlineStr">
@@ -15695,7 +16096,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D302" s="72" t="n">
+      <c r="D302" s="75" t="n">
         <v>22645</v>
       </c>
       <c r="E302" t="inlineStr">
@@ -15720,7 +16121,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D303" s="72" t="n">
+      <c r="D303" s="75" t="n">
         <v>153.5</v>
       </c>
       <c r="E303" t="inlineStr">
@@ -15745,7 +16146,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D304" s="72" t="n">
+      <c r="D304" s="75" t="n">
         <v>3126</v>
       </c>
       <c r="E304" t="inlineStr">
@@ -15770,7 +16171,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D305" s="72" t="n">
+      <c r="D305" s="75" t="n">
         <v>829.6</v>
       </c>
       <c r="E305" t="inlineStr">
@@ -15795,7 +16196,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D306" s="72" t="n">
+      <c r="D306" s="75" t="n">
         <v>-84565.2</v>
       </c>
       <c r="E306" t="inlineStr">
@@ -15820,7 +16221,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D307" s="72" t="n">
+      <c r="D307" s="75" t="n">
         <v>24000</v>
       </c>
       <c r="E307" t="inlineStr">
@@ -15845,7 +16246,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D308" s="72" t="n">
+      <c r="D308" s="75" t="n">
         <v>8780.15</v>
       </c>
       <c r="E308" t="inlineStr">
@@ -15870,7 +16271,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D309" s="72" t="n">
+      <c r="D309" s="75" t="n">
         <v>25230</v>
       </c>
       <c r="E309" t="inlineStr">
@@ -15895,7 +16296,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D310" s="72" t="n">
+      <c r="D310" s="75" t="n">
         <v>123.98</v>
       </c>
       <c r="E310" t="inlineStr">
@@ -15920,7 +16321,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D311" s="72" t="n">
+      <c r="D311" s="75" t="n">
         <v>3017</v>
       </c>
       <c r="E311" t="inlineStr">
@@ -15945,7 +16346,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D312" s="72" t="n">
+      <c r="D312" s="75" t="n">
         <v>-72000</v>
       </c>
       <c r="E312" t="inlineStr">
@@ -15970,7 +16371,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D313" s="72" t="n">
+      <c r="D313" s="75" t="n">
         <v>3002.35</v>
       </c>
       <c r="E313" t="inlineStr">
@@ -15995,7 +16396,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D314" s="72" t="n">
+      <c r="D314" s="75" t="n">
         <v>10807</v>
       </c>
       <c r="E314" t="inlineStr">
@@ -16020,7 +16421,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D315" s="72" t="n">
+      <c r="D315" s="75" t="n">
         <v>69715.82000000001</v>
       </c>
       <c r="E315" t="inlineStr">
@@ -16045,7 +16446,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D316" s="72" t="n">
+      <c r="D316" s="75" t="n">
         <v>4296</v>
       </c>
       <c r="E316" t="inlineStr">
@@ -16070,7 +16471,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D317" s="72" t="n">
+      <c r="D317" s="75" t="n">
         <v>-72001</v>
       </c>
       <c r="E317" t="inlineStr">
@@ -16095,7 +16496,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D318" s="72" t="n">
+      <c r="D318" s="75" t="n">
         <v>340.62</v>
       </c>
       <c r="E318" t="inlineStr">
@@ -16120,7 +16521,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D319" s="72" t="n">
+      <c r="D319" s="75" t="n">
         <v>11257</v>
       </c>
       <c r="E319" t="inlineStr">
@@ -16145,7 +16546,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D320" s="72" t="n">
+      <c r="D320" s="75" t="n">
         <v>69340.75999999999</v>
       </c>
       <c r="E320" t="inlineStr">
@@ -16170,7 +16571,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D321" s="72" t="n">
+      <c r="D321" s="75" t="n">
         <v>2203.93</v>
       </c>
       <c r="E321" t="inlineStr">
@@ -16195,7 +16596,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D322" s="72" t="n">
+      <c r="D322" s="75" t="n">
         <v>-72000</v>
       </c>
       <c r="E322" t="inlineStr">
@@ -16220,7 +16621,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D323" s="72" t="n">
+      <c r="D323" s="75" t="n">
         <v>2422.9</v>
       </c>
       <c r="E323" t="inlineStr">
@@ -16245,7 +16646,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D324" s="72" t="n">
+      <c r="D324" s="75" t="n">
         <v>11458</v>
       </c>
       <c r="E324" t="inlineStr">
@@ -16270,7 +16671,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D325" s="72" t="n">
+      <c r="D325" s="75" t="n">
         <v>67298.08</v>
       </c>
       <c r="E325" t="inlineStr">
@@ -16295,7 +16696,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D326" s="72" t="n">
+      <c r="D326" s="75" t="n">
         <v>24671.28</v>
       </c>
       <c r="E326" t="inlineStr">

--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -208,9 +208,10 @@
       <sz val="9.5"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001C2B45"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -358,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,11 +495,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -515,6 +529,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -977,7 +992,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue vs Net Income by Entity</a:t>
+              <a:t>Revenue vs Net Income by Entity (ranked)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -992,7 +1007,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Group Summary'!C16</f>
+              <f>'Group Summary'!E22</f>
             </strRef>
           </tx>
           <spPr>
@@ -1002,12 +1017,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Group Summary'!$B$17:$B$32</f>
+              <f>'Group Summary'!$C$23:$C$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Group Summary'!$C$17:$C$32</f>
+              <f>'Group Summary'!$E$23:$E$38</f>
             </numRef>
           </val>
         </ser>
@@ -1016,7 +1031,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Group Summary'!D16</f>
+              <f>'Group Summary'!H22</f>
             </strRef>
           </tx>
           <spPr>
@@ -1026,12 +1041,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Group Summary'!$B$17:$B$32</f>
+              <f>'Group Summary'!$C$23:$C$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Group Summary'!$D$17:$D$32</f>
+              <f>'Group Summary'!$H$23:$H$38</f>
             </numRef>
           </val>
         </ser>
@@ -1178,12 +1193,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3960000"/>
+    <ext cx="10800000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1222,7 +1237,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Dim_Entity" displayName="Dim_Entity" ref="A1:D17" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GroupLeaderboard" displayName="GroupLeaderboard" ref="B22:H38" headerRowCount="1">
+  <autoFilter ref="B22:H38"/>
+  <tableColumns count="7">
+    <tableColumn id="2" name="Rank"/>
+    <tableColumn id="3" name="Entity"/>
+    <tableColumn id="4" name="Industry"/>
+    <tableColumn id="5" name="Revenue"/>
+    <tableColumn id="6" name="EBITDA"/>
+    <tableColumn id="7" name="EBITDA Margin"/>
+    <tableColumn id="8" name="Net Income"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Dim_Entity" displayName="Dim_Entity" ref="A1:D17" headerRowCount="1">
   <autoFilter ref="A1:D17"/>
   <tableColumns count="4">
     <tableColumn id="1" name="EntityId"/>
@@ -1234,8 +1265,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Dim_Calendar" displayName="Dim_Calendar" ref="A1:C4" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Dim_Calendar" displayName="Dim_Calendar" ref="A1:C4" headerRowCount="1">
   <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="1" name="FiscalYear"/>
@@ -1246,8 +1277,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Fact_TrialBalance" displayName="Fact_TrialBalance" ref="A1:E326" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Fact_TrialBalance" displayName="Fact_TrialBalance" ref="A1:E326" headerRowCount="1">
   <autoFilter ref="A1:E326"/>
   <tableColumns count="5">
     <tableColumn id="1" name="EntityId"/>
@@ -7142,17 +7173,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7170,187 +7205,197 @@
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="59" t="inlineStr">
-        <is>
-          <t>Group Summary — driven by 01 Exec Summary's fiscal-year selector</t>
-        </is>
-      </c>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="49" t="n"/>
-      <c r="F2" s="49" t="n"/>
-      <c r="G2" s="49" t="n"/>
-      <c r="H2" s="49" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GROUP SUMMARY — ALL ENTITIES, ONE FISCAL YEAR</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Showing</t>
+        </is>
+      </c>
+      <c r="K2" s="5">
+        <f>'01 Exec Summary'!$K$2</f>
+        <v/>
+      </c>
+      <c r="M2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
-      <c r="F3" s="49" t="n"/>
-      <c r="G3" s="49" t="n"/>
-      <c r="H3" s="49" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
       <c r="I3" s="1" t="n"/>
       <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+      <c r="M3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
+      <c r="B4" s="73" t="inlineStr">
+        <is>
+          <t>Sandhu Group — Group Summary</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="73" t="inlineStr">
-        <is>
-          <t>16-entity group total (per Entity Register) — full scope (2 family trusts excluded)</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="n"/>
+      <c r="M5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="54" t="inlineStr">
-        <is>
-          <t>GROUP REVENUE</t>
-        </is>
-      </c>
-      <c r="C6" s="55" t="n"/>
-      <c r="D6" s="57" t="inlineStr">
-        <is>
-          <t>GROUP EBITDA</t>
-        </is>
-      </c>
-      <c r="E6" s="55" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="54" t="inlineStr">
-        <is>
-          <t>GROUP NET INCOME</t>
-        </is>
-      </c>
-      <c r="H6" s="55" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
+      <c r="B6" s="74">
+        <f>"16-entity group total (per Entity Register), fiscal year "&amp;'01 Exec Summary'!$K$2&amp;" — full scope, 2 family trusts excluded. Change the year on 01 Exec Summary."</f>
+        <v/>
+      </c>
+      <c r="M6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="56">
-        <f>SUM('Entity Register'!C5:C20)</f>
-        <v/>
-      </c>
-      <c r="C7" s="55" t="n"/>
-      <c r="D7" s="56">
-        <f>SUM('Entity Register'!J5:J20)</f>
-        <v/>
-      </c>
-      <c r="E7" s="55" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
       <c r="F7" s="1" t="n"/>
-      <c r="G7" s="56">
-        <f>SUM('Entity Register'!K5:K20)</f>
-        <v/>
-      </c>
-      <c r="H7" s="55" t="n"/>
+      <c r="G7" s="1" t="n"/>
+      <c r="H7" s="1" t="n"/>
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
+      <c r="K7" s="1" t="n"/>
+      <c r="L7" s="1" t="n"/>
+      <c r="M7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="55" t="n"/>
-      <c r="C8" s="55" t="n"/>
-      <c r="D8" s="55" t="n"/>
-      <c r="E8" s="55" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
       <c r="F8" s="1" t="n"/>
-      <c r="G8" s="55" t="n"/>
-      <c r="H8" s="55" t="n"/>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="1" t="n"/>
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="n"/>
+      <c r="K8" s="1" t="n"/>
+      <c r="L8" s="1" t="n"/>
+      <c r="M8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="n"/>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>GROUP REVENUE</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>GROUP EBITDA</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>GROUP NET INCOME</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>GROUP INCOME TAX</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>EFFECTIVE TAX RATE</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="1" t="n"/>
+      <c r="M9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="57" t="inlineStr">
-        <is>
-          <t>GROUP INCOME TAX</t>
-        </is>
-      </c>
-      <c r="C10" s="55" t="n"/>
-      <c r="D10" s="57" t="inlineStr">
-        <is>
-          <t>EFFECTIVE TAX RATE</t>
-        </is>
-      </c>
-      <c r="E10" s="55" t="n"/>
-      <c r="F10" s="1" t="n"/>
-      <c r="G10" s="57" t="inlineStr">
-        <is>
-          <t>ENTITIES IN MODEL</t>
-        </is>
-      </c>
-      <c r="H10" s="55" t="n"/>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="n"/>
+      <c r="B10" s="15">
+        <f>SUM('Entity Register'!C5:C20)</f>
+        <v/>
+      </c>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="15">
+        <f>SUM('Entity Register'!J5:J20)</f>
+        <v/>
+      </c>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="15">
+        <f>SUM('Entity Register'!K5:K20)</f>
+        <v/>
+      </c>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="15">
+        <f>SUM('Entity Register'!I5:I20)</f>
+        <v/>
+      </c>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="16">
+        <f>IFERROR(SUM('Entity Register'!I5:I20)/(SUM('Entity Register'!K5:K20)+SUM('Entity Register'!I5:I20)),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="1" t="n"/>
+      <c r="M10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="56">
-        <f>SUM('Entity Register'!I5:I20)</f>
-        <v/>
-      </c>
-      <c r="C11" s="55" t="n"/>
-      <c r="D11" s="58">
-        <f>IFERROR(SUM('Entity Register'!I5:I20)/(SUM('Entity Register'!K5:K20)+SUM('Entity Register'!I5:I20)),0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="55" t="n"/>
-      <c r="F11" s="1" t="n"/>
-      <c r="G11" s="74">
-        <f>COUNTA('Entity Register'!A5:A20)</f>
-        <v/>
-      </c>
-      <c r="H11" s="55" t="n"/>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="1" t="n"/>
+      <c r="M11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="55" t="n"/>
-      <c r="C12" s="55" t="n"/>
-      <c r="D12" s="55" t="n"/>
-      <c r="E12" s="55" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="18">
+        <f>TEXT(SUM('Entity Register'!J5:J20)/SUM('Entity Register'!C5:C20),"0.0%")&amp;" margin"</f>
+        <v/>
+      </c>
       <c r="F12" s="1" t="n"/>
-      <c r="G12" s="55" t="n"/>
-      <c r="H12" s="55" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -7363,6 +7408,9 @@
       <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
       <c r="J13" s="1" t="n"/>
+      <c r="K13" s="1" t="n"/>
+      <c r="L13" s="1" t="n"/>
+      <c r="M13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -7375,351 +7423,904 @@
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
       <c r="J14" s="1" t="n"/>
+      <c r="K14" s="1" t="n"/>
+      <c r="L14" s="1" t="n"/>
+      <c r="M14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="59" t="inlineStr">
-        <is>
-          <t>Revenue &amp; Net Income by Entity</t>
-        </is>
-      </c>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="n"/>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="n"/>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>ENTITIES IN MODEL</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>ENTITIES IN LOSS POSITION</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>TOP PERFORMER</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>BIGGEST LOSS</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="1" t="n"/>
+      <c r="M15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>EntityName</t>
-        </is>
-      </c>
-      <c r="C16" s="44" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D16" s="44" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
-      <c r="G16" s="1" t="n"/>
-      <c r="H16" s="1" t="n"/>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="n"/>
+      <c r="B16" s="75">
+        <f>COUNTA('Entity Register'!A5:A20)</f>
+        <v/>
+      </c>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="17">
+        <f>COUNTIF('Entity Register'!K5:K20,"&lt;0")&amp;" / "&amp;COUNTA('Entity Register'!A5:A20)</f>
+        <v/>
+      </c>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="76">
+        <f>INDEX('Entity Register'!A5:A20,MATCH(MAX('Entity Register'!K5:K20),'Entity Register'!K5:K20,0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="76">
+        <f>INDEX('Entity Register'!A5:A20,MATCH(MIN('Entity Register'!K5:K20),'Entity Register'!K5:K20,0))</f>
+        <v/>
+      </c>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="1" t="n"/>
+      <c r="M16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1">
-        <f>'Entity Register'!A5</f>
-        <v/>
-      </c>
-      <c r="C17" s="43">
-        <f>'Entity Register'!C5</f>
-        <v/>
-      </c>
-      <c r="D17" s="43">
-        <f>'Entity Register'!K5</f>
-        <v/>
-      </c>
-      <c r="E17" s="1" t="n"/>
-      <c r="F17" s="1" t="n"/>
-      <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="1" t="n"/>
+      <c r="M17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1">
-        <f>'Entity Register'!A6</f>
-        <v/>
-      </c>
-      <c r="C18" s="43">
-        <f>'Entity Register'!C6</f>
-        <v/>
-      </c>
-      <c r="D18" s="43">
-        <f>'Entity Register'!K6</f>
-        <v/>
-      </c>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
       <c r="E18" s="1" t="n"/>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="1" t="n"/>
       <c r="I18" s="1" t="n"/>
       <c r="J18" s="1" t="n"/>
+      <c r="K18" s="1" t="n"/>
+      <c r="L18" s="1" t="n"/>
+      <c r="M18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1">
-        <f>'Entity Register'!A7</f>
-        <v/>
-      </c>
-      <c r="C19" s="43">
-        <f>'Entity Register'!C7</f>
-        <v/>
-      </c>
-      <c r="D19" s="43">
-        <f>'Entity Register'!K7</f>
-        <v/>
-      </c>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="1" t="n"/>
       <c r="E19" s="1" t="n"/>
       <c r="F19" s="1" t="n"/>
       <c r="G19" s="1" t="n"/>
       <c r="H19" s="1" t="n"/>
       <c r="I19" s="1" t="n"/>
       <c r="J19" s="1" t="n"/>
+      <c r="K19" s="1" t="n"/>
+      <c r="L19" s="1" t="n"/>
+      <c r="M19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1">
-        <f>'Entity Register'!A8</f>
-        <v/>
-      </c>
-      <c r="C20" s="43">
-        <f>'Entity Register'!C8</f>
-        <v/>
-      </c>
-      <c r="D20" s="43">
-        <f>'Entity Register'!K8</f>
-        <v/>
-      </c>
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="1" t="n"/>
+      <c r="D20" s="1" t="n"/>
       <c r="E20" s="1" t="n"/>
       <c r="F20" s="1" t="n"/>
       <c r="G20" s="1" t="n"/>
       <c r="H20" s="1" t="n"/>
       <c r="I20" s="1" t="n"/>
       <c r="J20" s="1" t="n"/>
+      <c r="K20" s="1" t="n"/>
+      <c r="L20" s="1" t="n"/>
+      <c r="M20" s="1" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1">
-        <f>'Entity Register'!A9</f>
-        <v/>
-      </c>
-      <c r="C21" s="43">
-        <f>'Entity Register'!C9</f>
-        <v/>
-      </c>
-      <c r="D21" s="43">
-        <f>'Entity Register'!K9</f>
-        <v/>
-      </c>
-      <c r="E21" s="1" t="n"/>
-      <c r="F21" s="1" t="n"/>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="1" t="n"/>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Entity Leaderboard — ranked by Net Income</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1">
-        <f>'Entity Register'!A10</f>
-        <v/>
-      </c>
-      <c r="C22" s="43">
-        <f>'Entity Register'!C10</f>
-        <v/>
-      </c>
-      <c r="D22" s="43">
-        <f>'Entity Register'!K10</f>
-        <v/>
-      </c>
-      <c r="E22" s="1" t="n"/>
-      <c r="F22" s="1" t="n"/>
-      <c r="G22" s="1" t="n"/>
-      <c r="H22" s="1" t="n"/>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="F22" s="44" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="G22" s="44" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
       <c r="I22" s="1" t="n"/>
       <c r="J22" s="1" t="n"/>
+      <c r="K22" s="1" t="n"/>
+      <c r="L22" s="1" t="n"/>
+      <c r="M22" s="1" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1">
-        <f>'Entity Register'!A11</f>
-        <v/>
-      </c>
-      <c r="C23" s="43">
-        <f>'Entity Register'!C11</f>
-        <v/>
-      </c>
-      <c r="D23" s="43">
-        <f>'Entity Register'!K11</f>
-        <v/>
-      </c>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
+      <c r="B23" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="78">
+        <f>'Entity Register'!A10</f>
+        <v/>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="E23" s="43">
+        <f>'Entity Register'!C10</f>
+        <v/>
+      </c>
+      <c r="F23" s="43">
+        <f>'Entity Register'!J10</f>
+        <v/>
+      </c>
+      <c r="G23" s="45">
+        <f>IF(E23=0,"n/m",F23/E23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="43">
+        <f>'Entity Register'!K10</f>
+        <v/>
+      </c>
       <c r="I23" s="1" t="n"/>
       <c r="J23" s="1" t="n"/>
+      <c r="K23" s="1" t="n"/>
+      <c r="L23" s="1" t="n"/>
+      <c r="M23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1">
-        <f>'Entity Register'!A12</f>
-        <v/>
-      </c>
-      <c r="C24" s="43">
-        <f>'Entity Register'!C12</f>
-        <v/>
-      </c>
-      <c r="D24" s="43">
-        <f>'Entity Register'!K12</f>
-        <v/>
-      </c>
-      <c r="E24" s="1" t="n"/>
-      <c r="F24" s="1" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="1" t="n"/>
+      <c r="B24" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="78">
+        <f>'Entity Register'!A15</f>
+        <v/>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E24" s="43">
+        <f>'Entity Register'!C15</f>
+        <v/>
+      </c>
+      <c r="F24" s="43">
+        <f>'Entity Register'!J15</f>
+        <v/>
+      </c>
+      <c r="G24" s="45">
+        <f>IF(E24=0,"n/m",F24/E24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="43">
+        <f>'Entity Register'!K15</f>
+        <v/>
+      </c>
       <c r="I24" s="1" t="n"/>
       <c r="J24" s="1" t="n"/>
+      <c r="K24" s="1" t="n"/>
+      <c r="L24" s="1" t="n"/>
+      <c r="M24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="1">
-        <f>'Entity Register'!A13</f>
-        <v/>
-      </c>
-      <c r="C25" s="43">
-        <f>'Entity Register'!C13</f>
-        <v/>
-      </c>
-      <c r="D25" s="43">
-        <f>'Entity Register'!K13</f>
-        <v/>
-      </c>
-      <c r="E25" s="1" t="n"/>
-      <c r="F25" s="1" t="n"/>
-      <c r="G25" s="1" t="n"/>
-      <c r="H25" s="1" t="n"/>
+      <c r="B25" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="78">
+        <f>'Entity Register'!A11</f>
+        <v/>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="E25" s="43">
+        <f>'Entity Register'!C11</f>
+        <v/>
+      </c>
+      <c r="F25" s="43">
+        <f>'Entity Register'!J11</f>
+        <v/>
+      </c>
+      <c r="G25" s="45">
+        <f>IF(E25=0,"n/m",F25/E25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="43">
+        <f>'Entity Register'!K11</f>
+        <v/>
+      </c>
       <c r="I25" s="1" t="n"/>
       <c r="J25" s="1" t="n"/>
+      <c r="K25" s="1" t="n"/>
+      <c r="L25" s="1" t="n"/>
+      <c r="M25" s="1" t="n"/>
     </row>
     <row r="26">
-      <c r="B26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="78">
+        <f>'Entity Register'!A17</f>
+        <v/>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E26" s="43">
+        <f>'Entity Register'!C17</f>
+        <v/>
+      </c>
+      <c r="F26" s="43">
+        <f>'Entity Register'!J17</f>
+        <v/>
+      </c>
+      <c r="G26" s="45">
+        <f>IF(E26=0,"n/m",F26/E26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="43">
+        <f>'Entity Register'!K17</f>
+        <v/>
+      </c>
+      <c r="I26" s="1" t="n"/>
+      <c r="J26" s="1" t="n"/>
+      <c r="K26" s="1" t="n"/>
+      <c r="L26" s="1" t="n"/>
+      <c r="M26" s="1" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="78">
+        <f>'Entity Register'!A7</f>
+        <v/>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+      <c r="E27" s="43">
+        <f>'Entity Register'!C7</f>
+        <v/>
+      </c>
+      <c r="F27" s="43">
+        <f>'Entity Register'!J7</f>
+        <v/>
+      </c>
+      <c r="G27" s="45">
+        <f>IF(E27=0,"n/m",F27/E27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="43">
+        <f>'Entity Register'!K7</f>
+        <v/>
+      </c>
+      <c r="I27" s="1" t="n"/>
+      <c r="J27" s="1" t="n"/>
+      <c r="K27" s="1" t="n"/>
+      <c r="L27" s="1" t="n"/>
+      <c r="M27" s="1" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="78">
+        <f>'Entity Register'!A19</f>
+        <v/>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+      <c r="E28" s="43">
+        <f>'Entity Register'!C19</f>
+        <v/>
+      </c>
+      <c r="F28" s="43">
+        <f>'Entity Register'!J19</f>
+        <v/>
+      </c>
+      <c r="G28" s="45">
+        <f>IF(E28=0,"n/m",F28/E28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="43">
+        <f>'Entity Register'!K19</f>
+        <v/>
+      </c>
+      <c r="I28" s="1" t="n"/>
+      <c r="J28" s="1" t="n"/>
+      <c r="K28" s="1" t="n"/>
+      <c r="L28" s="1" t="n"/>
+      <c r="M28" s="1" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="78">
+        <f>'Entity Register'!A9</f>
+        <v/>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="E29" s="43">
+        <f>'Entity Register'!C9</f>
+        <v/>
+      </c>
+      <c r="F29" s="43">
+        <f>'Entity Register'!J9</f>
+        <v/>
+      </c>
+      <c r="G29" s="45">
+        <f>IF(E29=0,"n/m",F29/E29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="43">
+        <f>'Entity Register'!K9</f>
+        <v/>
+      </c>
+      <c r="I29" s="1" t="n"/>
+      <c r="J29" s="1" t="n"/>
+      <c r="K29" s="1" t="n"/>
+      <c r="L29" s="1" t="n"/>
+      <c r="M29" s="1" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="78">
+        <f>'Entity Register'!A8</f>
+        <v/>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="E30" s="43">
+        <f>'Entity Register'!C8</f>
+        <v/>
+      </c>
+      <c r="F30" s="43">
+        <f>'Entity Register'!J8</f>
+        <v/>
+      </c>
+      <c r="G30" s="45">
+        <f>IF(E30=0,"n/m",F30/E30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="43">
+        <f>'Entity Register'!K8</f>
+        <v/>
+      </c>
+      <c r="I30" s="1" t="n"/>
+      <c r="J30" s="1" t="n"/>
+      <c r="K30" s="1" t="n"/>
+      <c r="L30" s="1" t="n"/>
+      <c r="M30" s="1" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="78">
+        <f>'Entity Register'!A5</f>
+        <v/>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="E31" s="43">
+        <f>'Entity Register'!C5</f>
+        <v/>
+      </c>
+      <c r="F31" s="43">
+        <f>'Entity Register'!J5</f>
+        <v/>
+      </c>
+      <c r="G31" s="45">
+        <f>IF(E31=0,"n/m",F31/E31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="43">
+        <f>'Entity Register'!K5</f>
+        <v/>
+      </c>
+      <c r="I31" s="1" t="n"/>
+      <c r="J31" s="1" t="n"/>
+      <c r="K31" s="1" t="n"/>
+      <c r="L31" s="1" t="n"/>
+      <c r="M31" s="1" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="78">
+        <f>'Entity Register'!A16</f>
+        <v/>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E32" s="43">
+        <f>'Entity Register'!C16</f>
+        <v/>
+      </c>
+      <c r="F32" s="43">
+        <f>'Entity Register'!J16</f>
+        <v/>
+      </c>
+      <c r="G32" s="45">
+        <f>IF(E32=0,"n/m",F32/E32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="43">
+        <f>'Entity Register'!K16</f>
+        <v/>
+      </c>
+      <c r="I32" s="1" t="n"/>
+      <c r="J32" s="1" t="n"/>
+      <c r="K32" s="1" t="n"/>
+      <c r="L32" s="1" t="n"/>
+      <c r="M32" s="1" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="77" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" s="78">
+        <f>'Entity Register'!A20</f>
+        <v/>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+      <c r="E33" s="43">
+        <f>'Entity Register'!C20</f>
+        <v/>
+      </c>
+      <c r="F33" s="43">
+        <f>'Entity Register'!J20</f>
+        <v/>
+      </c>
+      <c r="G33" s="45">
+        <f>IF(E33=0,"n/m",F33/E33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="43">
+        <f>'Entity Register'!K20</f>
+        <v/>
+      </c>
+      <c r="I33" s="1" t="n"/>
+      <c r="J33" s="1" t="n"/>
+      <c r="K33" s="1" t="n"/>
+      <c r="L33" s="1" t="n"/>
+      <c r="M33" s="1" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="C34" s="78">
+        <f>'Entity Register'!A13</f>
+        <v/>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E34" s="43">
+        <f>'Entity Register'!C13</f>
+        <v/>
+      </c>
+      <c r="F34" s="43">
+        <f>'Entity Register'!J13</f>
+        <v/>
+      </c>
+      <c r="G34" s="45">
+        <f>IF(E34=0,"n/m",F34/E34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="43">
+        <f>'Entity Register'!K13</f>
+        <v/>
+      </c>
+      <c r="I34" s="1" t="n"/>
+      <c r="J34" s="1" t="n"/>
+      <c r="K34" s="1" t="n"/>
+      <c r="L34" s="1" t="n"/>
+      <c r="M34" s="1" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="77" t="n">
+        <v>13</v>
+      </c>
+      <c r="C35" s="78">
+        <f>'Entity Register'!A18</f>
+        <v/>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E35" s="43">
+        <f>'Entity Register'!C18</f>
+        <v/>
+      </c>
+      <c r="F35" s="43">
+        <f>'Entity Register'!J18</f>
+        <v/>
+      </c>
+      <c r="G35" s="45">
+        <f>IF(E35=0,"n/m",F35/E35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="43">
+        <f>'Entity Register'!K18</f>
+        <v/>
+      </c>
+      <c r="I35" s="1" t="n"/>
+      <c r="J35" s="1" t="n"/>
+      <c r="K35" s="1" t="n"/>
+      <c r="L35" s="1" t="n"/>
+      <c r="M35" s="1" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="77" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" s="78">
+        <f>'Entity Register'!A12</f>
+        <v/>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E36" s="43">
+        <f>'Entity Register'!C12</f>
+        <v/>
+      </c>
+      <c r="F36" s="43">
+        <f>'Entity Register'!J12</f>
+        <v/>
+      </c>
+      <c r="G36" s="45">
+        <f>IF(E36=0,"n/m",F36/E36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="43">
+        <f>'Entity Register'!K12</f>
+        <v/>
+      </c>
+      <c r="I36" s="1" t="n"/>
+      <c r="J36" s="1" t="n"/>
+      <c r="K36" s="1" t="n"/>
+      <c r="L36" s="1" t="n"/>
+      <c r="M36" s="1" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="77" t="n">
+        <v>15</v>
+      </c>
+      <c r="C37" s="78">
         <f>'Entity Register'!A14</f>
         <v/>
       </c>
-      <c r="C26" s="75">
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E37" s="43">
         <f>'Entity Register'!C14</f>
         <v/>
       </c>
-      <c r="D26" s="75">
+      <c r="F37" s="43">
+        <f>'Entity Register'!J14</f>
+        <v/>
+      </c>
+      <c r="G37" s="45">
+        <f>IF(E37=0,"n/m",F37/E37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="43">
         <f>'Entity Register'!K14</f>
         <v/>
       </c>
-    </row>
-    <row r="27">
-      <c r="B27">
-        <f>'Entity Register'!A15</f>
-        <v/>
-      </c>
-      <c r="C27" s="75">
-        <f>'Entity Register'!C15</f>
-        <v/>
-      </c>
-      <c r="D27" s="75">
-        <f>'Entity Register'!K15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28">
-        <f>'Entity Register'!A16</f>
-        <v/>
-      </c>
-      <c r="C28" s="75">
-        <f>'Entity Register'!C16</f>
-        <v/>
-      </c>
-      <c r="D28" s="75">
-        <f>'Entity Register'!K16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29">
-        <f>'Entity Register'!A17</f>
-        <v/>
-      </c>
-      <c r="C29" s="75">
-        <f>'Entity Register'!C17</f>
-        <v/>
-      </c>
-      <c r="D29" s="75">
-        <f>'Entity Register'!K17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30">
-        <f>'Entity Register'!A18</f>
-        <v/>
-      </c>
-      <c r="C30" s="75">
-        <f>'Entity Register'!C18</f>
-        <v/>
-      </c>
-      <c r="D30" s="75">
-        <f>'Entity Register'!K18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31">
-        <f>'Entity Register'!A19</f>
-        <v/>
-      </c>
-      <c r="C31" s="75">
-        <f>'Entity Register'!C19</f>
-        <v/>
-      </c>
-      <c r="D31" s="75">
-        <f>'Entity Register'!K19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32">
-        <f>'Entity Register'!A20</f>
-        <v/>
-      </c>
-      <c r="C32" s="75">
-        <f>'Entity Register'!C20</f>
-        <v/>
-      </c>
-      <c r="D32" s="75">
-        <f>'Entity Register'!K20</f>
-        <v/>
-      </c>
+      <c r="I37" s="1" t="n"/>
+      <c r="J37" s="1" t="n"/>
+      <c r="K37" s="1" t="n"/>
+      <c r="L37" s="1" t="n"/>
+      <c r="M37" s="1" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="77" t="n">
+        <v>16</v>
+      </c>
+      <c r="C38" s="78">
+        <f>'Entity Register'!A6</f>
+        <v/>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+      <c r="E38" s="43">
+        <f>'Entity Register'!C6</f>
+        <v/>
+      </c>
+      <c r="F38" s="43">
+        <f>'Entity Register'!J6</f>
+        <v/>
+      </c>
+      <c r="G38" s="45">
+        <f>IF(E38=0,"n/m",F38/E38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="43">
+        <f>'Entity Register'!K6</f>
+        <v/>
+      </c>
+      <c r="I38" s="1" t="n"/>
+      <c r="J38" s="1" t="n"/>
+      <c r="K38" s="1" t="n"/>
+      <c r="L38" s="1" t="n"/>
+      <c r="M38" s="1" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>Revenue = Operating Revenue only. A few HoldCos show $0 here but real profit in Net Income — they earn via intercompany dividends/interest (Investment &amp; Other Income), not operating sales; their EBITDA Margin shows "n/m" rather than a misleading 0%.</t>
+        </is>
+      </c>
+      <c r="M39" s="1" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="1" t="n"/>
+      <c r="D40" s="1" t="n"/>
+      <c r="E40" s="1" t="n"/>
+      <c r="F40" s="1" t="n"/>
+      <c r="G40" s="1" t="n"/>
+      <c r="H40" s="1" t="n"/>
+      <c r="I40" s="1" t="n"/>
+      <c r="J40" s="1" t="n"/>
+      <c r="K40" s="1" t="n"/>
+      <c r="L40" s="1" t="n"/>
+      <c r="M40" s="1" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="1" t="n"/>
+      <c r="D41" s="1" t="n"/>
+      <c r="E41" s="1" t="n"/>
+      <c r="F41" s="1" t="n"/>
+      <c r="G41" s="1" t="n"/>
+      <c r="H41" s="1" t="n"/>
+      <c r="I41" s="1" t="n"/>
+      <c r="J41" s="1" t="n"/>
+      <c r="K41" s="1" t="n"/>
+      <c r="L41" s="1" t="n"/>
+      <c r="M41" s="1" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="1" t="n"/>
+      <c r="D42" s="1" t="n"/>
+      <c r="E42" s="1" t="n"/>
+      <c r="F42" s="1" t="n"/>
+      <c r="G42" s="1" t="n"/>
+      <c r="H42" s="1" t="n"/>
+      <c r="I42" s="1" t="n"/>
+      <c r="J42" s="1" t="n"/>
+      <c r="K42" s="1" t="n"/>
+      <c r="L42" s="1" t="n"/>
+      <c r="M42" s="1" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
+      <c r="D43" s="1" t="n"/>
+      <c r="E43" s="1" t="n"/>
+      <c r="F43" s="1" t="n"/>
+      <c r="G43" s="1" t="n"/>
+      <c r="H43" s="1" t="n"/>
+      <c r="I43" s="1" t="n"/>
+      <c r="J43" s="1" t="n"/>
+      <c r="K43" s="1" t="n"/>
+      <c r="L43" s="1" t="n"/>
+      <c r="M43" s="1" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="1" t="n"/>
+      <c r="D44" s="1" t="n"/>
+      <c r="E44" s="1" t="n"/>
+      <c r="F44" s="1" t="n"/>
+      <c r="G44" s="1" t="n"/>
+      <c r="H44" s="1" t="n"/>
+      <c r="I44" s="1" t="n"/>
+      <c r="J44" s="1" t="n"/>
+      <c r="K44" s="1" t="n"/>
+      <c r="L44" s="1" t="n"/>
+      <c r="M44" s="1" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="1" t="n"/>
+      <c r="D45" s="1" t="n"/>
+      <c r="E45" s="1" t="n"/>
+      <c r="F45" s="1" t="n"/>
+      <c r="G45" s="1" t="n"/>
+      <c r="H45" s="1" t="n"/>
+      <c r="I45" s="1" t="n"/>
+      <c r="J45" s="1" t="n"/>
+      <c r="K45" s="1" t="n"/>
+      <c r="L45" s="1" t="n"/>
+      <c r="M45" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="G11:H12"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B15:D15"/>
+  <mergeCells count="25">
+    <mergeCell ref="D16:E17"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F16:H17"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B39:L39"/>
+    <mergeCell ref="D10:E11"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="I16:K17"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="F10:G11"/>
+    <mergeCell ref="H10:I11"/>
+    <mergeCell ref="J10:K11"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
   </mergeCells>
+  <conditionalFormatting sqref="E23:E38">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23:H38">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="0070AD47"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
   </hyperlinks>
@@ -7727,6 +8328,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -7744,7 +8348,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>SANDHU GROUP INTERACTIVE DASHBOARD — Build Notes</t>
         </is>
@@ -7757,12 +8361,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr"/>
+      <c r="A2" s="80" t="inlineStr"/>
       <c r="B2" s="1" t="n"/>
       <c r="C2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="80" t="inlineStr">
         <is>
           <t>Scope: all 16 entities (both family trusts — Gurpreet Sandhu Trust, Harpreet Sandhu Trust — excluded from scope per instruction; ~$4-$10/yr activity per the handoff, immaterial). Every one of these was rebuilt fresh from its raw CaseWare WTB export in this session (not carried over from any prior file) and covers 3 fiscal years: FY2023, FY2024, FY2025.</t>
         </is>
@@ -7771,12 +8375,12 @@
       <c r="C3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr"/>
+      <c r="A4" s="80" t="inlineStr"/>
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="80" t="inlineStr">
         <is>
           <t>Missing: Sandhu &amp; Sandhu Enr.'s Corporate Taxprep export (its WTB was supplied and is included).</t>
         </is>
@@ -7785,12 +8389,12 @@
       <c r="C5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="inlineStr"/>
+      <c r="A6" s="80" t="inlineStr"/>
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="A7" s="80" t="inlineStr">
         <is>
           <t>Dim_Entity updated to the user-supplied reference table: CompanyName (incl. owner suffix, e.g. '- Sandhu H.'), LegalName, and Industry (Construction/Real estate/Investments/Hotel/Restaurant/Rental) replace the earlier EntityName/Segment (HoldCo/RealCo/OpCo) scheme everywhere in this workbook. 'Rres_Ind' in that table was treated as a typo for 'Res_Ind' (same LegalName, 9366-1049 Québec Inc.) — same entity, not a new one. Sandhu &amp; Sandhu Enr. isn't in that table at all; its Industry ('Rental') is inferred from its sibling entity Sandhu Leasing, not given data.</t>
         </is>
@@ -7799,12 +8403,12 @@
       <c r="C7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="inlineStr"/>
+      <c r="A8" s="80" t="inlineStr"/>
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="78" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>UNEXPECTED FILE: 947_338_2025_Tax.csv identifies its filer as '9475-3381 Québec Inc.' — an entity not in the Section 4 entity list at all. No WTB was supplied for it, so it is NOT included in this workbook. Flagged for you to confirm whether it belongs in the group.</t>
         </is>
@@ -7813,12 +8417,12 @@
       <c r="C9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="inlineStr"/>
+      <c r="A10" s="80" t="inlineStr"/>
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="79" t="inlineStr">
+      <c r="A11" s="82" t="inlineStr">
         <is>
           <t>VALIDATION — every entity's FY2025 Net Income matches an independent benchmark exactly:</t>
         </is>
@@ -7827,7 +8431,7 @@
       <c r="C11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="80" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">  Restaurant IndiaRosa 2 matches every Section 6 category benchmark to the penny (Net Income FY2025 $462,894.92, FY2024 $736,959.45) — see the account-level exceptions below.</t>
         </is>
@@ -7836,7 +8440,7 @@
       <c r="C12" s="1" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">  All other 15 entities match the Validation Log tab in GIFI_Master_Mapping_v2.xlsx exactly, including Bistro Guru Inc. ($-30,118.89), which RESOLVES the discrepancy flagged in an earlier version of this workbook (the old starter kit's $-45,954.06 figure for Bistro Guru was wrong; the fresh WTB rebuild confirms the Validation Log was correct).</t>
         </is>
@@ -7845,12 +8449,12 @@
       <c r="C13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="77" t="inlineStr"/>
+      <c r="A14" s="80" t="inlineStr"/>
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="1" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="80" t="inlineStr">
         <is>
           <t>Restaurant IndiaRosa 2 — three accounts in its WTB carry a GIFI code that contradicts the account name; treated as account-level overrides, not changes to the master GIFI mapping:</t>
         </is>
@@ -7859,7 +8463,7 @@
       <c r="C15" s="1" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="80" t="inlineStr">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 45130 'Valet service' + 45125 'Musical entertainment' — tagged GIFI 9270 (Amortization) -&gt; reclassified to Marketing &amp; Entertainment.</t>
         </is>
@@ -7868,7 +8472,7 @@
       <c r="C16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="80" t="inlineStr">
+      <c r="A17" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 44215 'Rent - Ford' + 33455 'Equipment rental' + 45250 'Travelling - gas &amp; repairs' — tagged GIFI 8461 (COGS) -&gt; reclassified to Other Operating.</t>
         </is>
@@ -7877,7 +8481,7 @@
       <c r="C17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="80" t="inlineStr">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">  Acct 45150 'Consulting fees' — tagged GIFI 8863 (Administrative) -&gt; reclassified to Other Operating per user confirmation (matches Section 6 Admin $99,729 / Other Operating $79,976 exactly).</t>
         </is>
@@ -7886,12 +8490,12 @@
       <c r="C18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="inlineStr"/>
+      <c r="A19" s="80" t="inlineStr"/>
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="inlineStr">
+      <c r="A20" s="80" t="inlineStr">
         <is>
           <t>Sandhu &amp; Sandhu Enr. — two Map No formatting variants ('40.1' vs '40. 1') were causing 3 accounts to fall through the fallback table uncategorized; fixed by normalizing whitespace in the Map No match, plus adding one missing fallback row (Map No '40. 3' -&gt; Administrative, Insurance). After the fix, FY2025 Net Income matches the Validation Log exactly ($-15,821.17).</t>
         </is>
@@ -7900,12 +8504,12 @@
       <c r="C20" s="1" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="77" t="inlineStr"/>
+      <c r="A21" s="80" t="inlineStr"/>
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="78" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>UNRESOLVED: group-level FY2025 Revenue ($14,945,731) and EBITDA ($2,734,142) are within ~0.5% and ~1.8% of the Section 6 16-entity benchmark ($14,873,731 / $2,784,496) despite every single entity's own Net Income matching its benchmark exactly. Income Tax and Investment &amp; Other Income match exactly. This means a small amount is sitting in a different category than the original benchmark used, in one or two entities — similar in nature to IndiaRosa 2's account exceptions above, but not yet isolated. Group Net Income is within $5,014 (0.8%) of benchmark.</t>
         </is>
@@ -7914,12 +8518,12 @@
       <c r="C22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="77" t="inlineStr"/>
+      <c r="A23" s="80" t="inlineStr"/>
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="inlineStr">
+      <c r="A24" s="80" t="inlineStr">
         <is>
           <t>NOT YET INCLUDED: RDTOH and CDA (confirmed absent from the Taxprep export tested — see 03 Tax Position). SBD/GRIP/Part I tax figures are real for IndiaRosa 2's 14 associated corporations (from its Taxprep SLIPA schedule) but each entity's OWN SBD claim from its own Taxprep export has not yet been pulled in — only IndiaRosa 2's Tax CSV has been mined for Section 3-style data.</t>
         </is>
@@ -7928,12 +8532,12 @@
       <c r="C24" s="1" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="inlineStr"/>
+      <c r="A25" s="80" t="inlineStr"/>
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="1" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="77" t="inlineStr">
+      <c r="A26" s="80" t="inlineStr">
         <is>
           <t>Interactivity: this workbook uses dropdown selectors ('02 Profitability'!C6 Entity, !H6 Fiscal Year) driving live SUMIFS formulas and charts — no Power Pivot/DAX setup required, works in any version of Excel. Entity Register and raw data sheets are Excel Tables with built-in filter dropdowns per column.</t>
         </is>
@@ -7942,12 +8546,12 @@
       <c r="C26" s="1" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="77" t="inlineStr"/>
+      <c r="A27" s="80" t="inlineStr"/>
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="77" t="inlineStr">
+      <c r="A28" s="80" t="inlineStr">
         <is>
           <t>Recalculated and verified in LibreOffice headless — every KPI card and cross-check in this sheet was confirmed against the actual computed cell values, not just the formula text.</t>
         </is>
@@ -8066,22 +8670,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="B1" s="81" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>CompanyName</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>LegalName</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -8462,17 +9066,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="B1" s="81" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>YearEnd</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>YearLabel</t>
         </is>
@@ -8554,27 +9158,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="B1" s="81" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -8596,7 +9200,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D2" s="75" t="n">
+      <c r="D2" s="85" t="n">
         <v>-5213628.68</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -8621,7 +9225,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D3" s="75" t="n">
+      <c r="D3" s="85" t="n">
         <v>30000</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -8646,7 +9250,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D4" s="75" t="n">
+      <c r="D4" s="85" t="n">
         <v>146738.3</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -8671,7 +9275,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D5" s="75" t="n">
+      <c r="D5" s="85" t="n">
         <v>474171.72</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -8696,7 +9300,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D6" s="75" t="n">
+      <c r="D6" s="85" t="n">
         <v>79976.25999999999</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -8721,7 +9325,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D7" s="75" t="n">
+      <c r="D7" s="85" t="n">
         <v>99728.72</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -8746,7 +9350,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D8" s="75" t="n">
+      <c r="D8" s="85" t="n">
         <v>141793.12</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -8771,7 +9375,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D9" s="75" t="n">
+      <c r="D9" s="85" t="n">
         <v>199058</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -8796,7 +9400,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D10" s="75" t="n">
+      <c r="D10" s="85" t="n">
         <v>1647558.89</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -8821,7 +9425,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D11" s="75" t="n">
+      <c r="D11" s="85" t="n">
         <v>1780201.39</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -8846,7 +9450,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D12" s="75" t="n">
+      <c r="D12" s="85" t="n">
         <v>88959.36</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -8871,7 +9475,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D13" s="75" t="n">
+      <c r="D13" s="85" t="n">
         <v>62548</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -8896,7 +9500,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D14" s="75" t="n">
+      <c r="D14" s="85" t="n">
         <v>-6233247.68</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -8921,7 +9525,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D15" s="75" t="n">
+      <c r="D15" s="85" t="n">
         <v>105000</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -8946,7 +9550,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D16" s="75" t="n">
+      <c r="D16" s="85" t="n">
         <v>178561.41</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -8971,7 +9575,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D17" s="75" t="n">
+      <c r="D17" s="85" t="n">
         <v>382549.29</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -8996,7 +9600,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D18" s="75" t="n">
+      <c r="D18" s="85" t="n">
         <v>73281.73</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -9021,7 +9625,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D19" s="75" t="n">
+      <c r="D19" s="85" t="n">
         <v>88387.59</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -9046,7 +9650,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D20" s="75" t="n">
+      <c r="D20" s="85" t="n">
         <v>161333.63</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -9071,7 +9675,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D21" s="75" t="n">
+      <c r="D21" s="85" t="n">
         <v>222195</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -9096,7 +9700,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D22" s="75" t="n">
+      <c r="D22" s="85" t="n">
         <v>1888352.46</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -9121,7 +9725,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D23" s="75" t="n">
+      <c r="D23" s="85" t="n">
         <v>2181636.69</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -9146,7 +9750,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D24" s="75" t="n">
+      <c r="D24" s="85" t="n">
         <v>214990.43</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -9171,7 +9775,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D25" s="75" t="n">
+      <c r="D25" s="85" t="n">
         <v>-1331424.61</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -9196,7 +9800,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D26" s="75" t="n">
+      <c r="D26" s="85" t="n">
         <v>26989.26</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -9221,7 +9825,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D27" s="75" t="n">
+      <c r="D27" s="85" t="n">
         <v>47833.69</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -9246,7 +9850,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D28" s="75" t="n">
+      <c r="D28" s="85" t="n">
         <v>19176.77</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -9271,7 +9875,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D29" s="75" t="n">
+      <c r="D29" s="85" t="n">
         <v>69851.5</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -9296,7 +9900,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D30" s="75" t="n">
+      <c r="D30" s="85" t="n">
         <v>24668.14</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -9321,7 +9925,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D31" s="75" t="n">
+      <c r="D31" s="85" t="n">
         <v>126996</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -9346,7 +9950,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D32" s="75" t="n">
+      <c r="D32" s="85" t="n">
         <v>394933.77</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -9371,7 +9975,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D33" s="75" t="n">
+      <c r="D33" s="85" t="n">
         <v>365807.86</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -9396,7 +10000,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D34" s="75" t="n">
+      <c r="D34" s="85" t="n">
         <v>42134.25</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -9421,7 +10025,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D35" s="75" t="n">
+      <c r="D35" s="85" t="n">
         <v>477.24</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -9446,7 +10050,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D36" s="75" t="n">
+      <c r="D36" s="85" t="n">
         <v>2597</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -9471,7 +10075,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D37" s="75" t="n">
+      <c r="D37" s="85" t="n">
         <v>72.58</v>
       </c>
       <c r="E37" t="inlineStr">
@@ -9496,7 +10100,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D38" s="75" t="n">
+      <c r="D38" s="85" t="n">
         <v>358.94</v>
       </c>
       <c r="E38" t="inlineStr">
@@ -9521,7 +10125,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D39" s="75" t="n">
+      <c r="D39" s="85" t="n">
         <v>2329</v>
       </c>
       <c r="E39" t="inlineStr">
@@ -9546,7 +10150,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D40" s="75" t="n">
+      <c r="D40" s="85" t="n">
         <v>47.81</v>
       </c>
       <c r="E40" t="inlineStr">
@@ -9571,7 +10175,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D41" s="75" t="n">
+      <c r="D41" s="85" t="n">
         <v>-31929</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -9596,7 +10200,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D42" s="75" t="n">
+      <c r="D42" s="85" t="n">
         <v>29026.44</v>
       </c>
       <c r="E42" t="inlineStr">
@@ -9621,7 +10225,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D43" s="75" t="n">
+      <c r="D43" s="85" t="n">
         <v>90</v>
       </c>
       <c r="E43" t="inlineStr">
@@ -9646,7 +10250,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D44" s="75" t="n">
+      <c r="D44" s="85" t="n">
         <v>27273.26</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -9671,7 +10275,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D45" s="75" t="n">
+      <c r="D45" s="85" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="E45" t="inlineStr">
@@ -9696,7 +10300,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D46" s="75" t="n">
+      <c r="D46" s="85" t="n">
         <v>-190152.12</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -9721,7 +10325,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D47" s="75" t="n">
+      <c r="D47" s="85" t="n">
         <v>396762.02</v>
       </c>
       <c r="E47" t="inlineStr">
@@ -9746,7 +10350,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D48" s="75" t="n">
+      <c r="D48" s="85" t="n">
         <v>204136</v>
       </c>
       <c r="E48" t="inlineStr">
@@ -9771,7 +10375,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D49" s="75" t="n">
+      <c r="D49" s="85" t="n">
         <v>215463.66</v>
       </c>
       <c r="E49" t="inlineStr">
@@ -9796,7 +10400,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D50" s="75" t="n">
+      <c r="D50" s="85" t="n">
         <v>33717.57</v>
       </c>
       <c r="E50" t="inlineStr">
@@ -9821,7 +10425,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D51" s="75" t="n">
+      <c r="D51" s="85" t="n">
         <v>425</v>
       </c>
       <c r="E51" t="inlineStr">
@@ -9846,7 +10450,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D52" s="75" t="n">
+      <c r="D52" s="85" t="n">
         <v>-188197.75</v>
       </c>
       <c r="E52" t="inlineStr">
@@ -9871,7 +10475,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D53" s="75" t="n">
+      <c r="D53" s="85" t="n">
         <v>219534.62</v>
       </c>
       <c r="E53" t="inlineStr">
@@ -9896,7 +10500,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D54" s="75" t="n">
+      <c r="D54" s="85" t="n">
         <v>94472</v>
       </c>
       <c r="E54" t="inlineStr">
@@ -9921,7 +10525,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D55" s="75" t="n">
+      <c r="D55" s="85" t="n">
         <v>152117.58</v>
       </c>
       <c r="E55" t="inlineStr">
@@ -9946,7 +10550,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D56" s="75" t="n">
+      <c r="D56" s="85" t="n">
         <v>16431.97</v>
       </c>
       <c r="E56" t="inlineStr">
@@ -9971,7 +10575,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D57" s="75" t="n">
+      <c r="D57" s="85" t="n">
         <v>-220172.35</v>
       </c>
       <c r="E57" t="inlineStr">
@@ -9996,7 +10600,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D58" s="75" t="n">
+      <c r="D58" s="85" t="n">
         <v>-12000</v>
       </c>
       <c r="E58" t="inlineStr">
@@ -10021,7 +10625,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D59" s="75" t="n">
+      <c r="D59" s="85" t="n">
         <v>80807.78</v>
       </c>
       <c r="E59" t="inlineStr">
@@ -10046,7 +10650,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D60" s="75" t="n">
+      <c r="D60" s="85" t="n">
         <v>94975</v>
       </c>
       <c r="E60" t="inlineStr">
@@ -10071,7 +10675,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D61" s="75" t="n">
+      <c r="D61" s="85" t="n">
         <v>121093.68</v>
       </c>
       <c r="E61" t="inlineStr">
@@ -10096,7 +10700,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D62" s="75" t="n">
+      <c r="D62" s="85" t="n">
         <v>13011.85</v>
       </c>
       <c r="E62" t="inlineStr">
@@ -10121,7 +10725,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D63" s="75" t="n">
+      <c r="D63" s="85" t="n">
         <v>7000</v>
       </c>
       <c r="E63" t="inlineStr">
@@ -10146,7 +10750,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D64" s="75" t="n">
+      <c r="D64" s="85" t="n">
         <v>-273186</v>
       </c>
       <c r="E64" t="inlineStr">
@@ -10171,7 +10775,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D65" s="75" t="n">
+      <c r="D65" s="85" t="n">
         <v>-84146.62</v>
       </c>
       <c r="E65" t="inlineStr">
@@ -10196,7 +10800,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D66" s="75" t="n">
+      <c r="D66" s="85" t="n">
         <v>147839</v>
       </c>
       <c r="E66" t="inlineStr">
@@ -10221,7 +10825,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D67" s="75" t="n">
+      <c r="D67" s="85" t="n">
         <v>14870</v>
       </c>
       <c r="E67" t="inlineStr">
@@ -10246,7 +10850,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D68" s="75" t="n">
+      <c r="D68" s="85" t="n">
         <v>81647.35000000001</v>
       </c>
       <c r="E68" t="inlineStr">
@@ -10271,7 +10875,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D69" s="75" t="n">
+      <c r="D69" s="85" t="n">
         <v>8110.21</v>
       </c>
       <c r="E69" t="inlineStr">
@@ -10296,7 +10900,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D70" s="75" t="n">
+      <c r="D70" s="85" t="n">
         <v>14359</v>
       </c>
       <c r="E70" t="inlineStr">
@@ -10321,7 +10925,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D71" s="75" t="n">
+      <c r="D71" s="85" t="n">
         <v>-247975</v>
       </c>
       <c r="E71" t="inlineStr">
@@ -10346,7 +10950,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D72" s="75" t="n">
+      <c r="D72" s="85" t="n">
         <v>-62108.84</v>
       </c>
       <c r="E72" t="inlineStr">
@@ -10371,7 +10975,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D73" s="75" t="n">
+      <c r="D73" s="85" t="n">
         <v>108814.51</v>
       </c>
       <c r="E73" t="inlineStr">
@@ -10396,7 +11000,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D74" s="75" t="n">
+      <c r="D74" s="85" t="n">
         <v>15473</v>
       </c>
       <c r="E74" t="inlineStr">
@@ -10421,7 +11025,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D75" s="75" t="n">
+      <c r="D75" s="85" t="n">
         <v>84635.60000000001</v>
       </c>
       <c r="E75" t="inlineStr">
@@ -10446,7 +11050,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D76" s="75" t="n">
+      <c r="D76" s="85" t="n">
         <v>6455.93</v>
       </c>
       <c r="E76" t="inlineStr">
@@ -10471,7 +11075,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D77" s="75" t="n">
+      <c r="D77" s="85" t="n">
         <v>13363</v>
       </c>
       <c r="E77" t="inlineStr">
@@ -10496,7 +11100,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D78" s="75" t="n">
+      <c r="D78" s="85" t="n">
         <v>-234180</v>
       </c>
       <c r="E78" t="inlineStr">
@@ -10521,7 +11125,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D79" s="75" t="n">
+      <c r="D79" s="85" t="n">
         <v>12000</v>
       </c>
       <c r="E79" t="inlineStr">
@@ -10546,7 +11150,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D80" s="75" t="n">
+      <c r="D80" s="85" t="n">
         <v>5374.62</v>
       </c>
       <c r="E80" t="inlineStr">
@@ -10571,7 +11175,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D81" s="75" t="n">
+      <c r="D81" s="85" t="n">
         <v>55542</v>
       </c>
       <c r="E81" t="inlineStr">
@@ -10596,7 +11200,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D82" s="75" t="n">
+      <c r="D82" s="85" t="n">
         <v>15710</v>
       </c>
       <c r="E82" t="inlineStr">
@@ -10621,7 +11225,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D83" s="75" t="n">
+      <c r="D83" s="85" t="n">
         <v>88267.41</v>
       </c>
       <c r="E83" t="inlineStr">
@@ -10646,7 +11250,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D84" s="75" t="n">
+      <c r="D84" s="85" t="n">
         <v>5719.82</v>
       </c>
       <c r="E84" t="inlineStr">
@@ -10671,7 +11275,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D85" s="75" t="n">
+      <c r="D85" s="85" t="n">
         <v>13857</v>
       </c>
       <c r="E85" t="inlineStr">
@@ -10696,7 +11300,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D86" s="75" t="n">
+      <c r="D86" s="85" t="n">
         <v>2994</v>
       </c>
       <c r="E86" t="inlineStr">
@@ -10721,7 +11325,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D87" s="75" t="n">
+      <c r="D87" s="85" t="n">
         <v>71.34999999999999</v>
       </c>
       <c r="E87" t="inlineStr">
@@ -10746,7 +11350,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D88" s="75" t="n">
+      <c r="D88" s="85" t="n">
         <v>3085</v>
       </c>
       <c r="E88" t="inlineStr">
@@ -10771,7 +11375,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D89" s="75" t="n">
+      <c r="D89" s="85" t="n">
         <v>163.14</v>
       </c>
       <c r="E89" t="inlineStr">
@@ -10796,7 +11400,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D90" s="75" t="n">
+      <c r="D90" s="85" t="n">
         <v>4995</v>
       </c>
       <c r="E90" t="inlineStr">
@@ -10821,7 +11425,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D91" s="75" t="n">
+      <c r="D91" s="85" t="n">
         <v>53.55</v>
       </c>
       <c r="E91" t="inlineStr">
@@ -10846,7 +11450,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D92" s="75" t="n">
+      <c r="D92" s="85" t="n">
         <v>2944</v>
       </c>
       <c r="E92" t="inlineStr">
@@ -10871,7 +11475,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D93" s="75" t="n">
+      <c r="D93" s="85" t="n">
         <v>71.31</v>
       </c>
       <c r="E93" t="inlineStr">
@@ -10896,7 +11500,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D94" s="75" t="n">
+      <c r="D94" s="85" t="n">
         <v>2797</v>
       </c>
       <c r="E94" t="inlineStr">
@@ -10921,7 +11525,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D95" s="75" t="n">
+      <c r="D95" s="85" t="n">
         <v>148.11</v>
       </c>
       <c r="E95" t="inlineStr">
@@ -10946,7 +11550,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D96" s="75" t="n">
+      <c r="D96" s="85" t="n">
         <v>5196</v>
       </c>
       <c r="E96" t="inlineStr">
@@ -10971,7 +11575,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D97" s="75" t="n">
+      <c r="D97" s="85" t="n">
         <v>53.55</v>
       </c>
       <c r="E97" t="inlineStr">
@@ -10996,7 +11600,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D98" s="75" t="n">
+      <c r="D98" s="85" t="n">
         <v>-673859.71</v>
       </c>
       <c r="E98" t="inlineStr">
@@ -11021,7 +11625,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D99" s="75" t="n">
+      <c r="D99" s="85" t="n">
         <v>12508.63</v>
       </c>
       <c r="E99" t="inlineStr">
@@ -11046,7 +11650,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D100" s="75" t="n">
+      <c r="D100" s="85" t="n">
         <v>89815.85000000001</v>
       </c>
       <c r="E100" t="inlineStr">
@@ -11071,7 +11675,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D101" s="75" t="n">
+      <c r="D101" s="85" t="n">
         <v>-1569420.99</v>
       </c>
       <c r="E101" t="inlineStr">
@@ -11096,7 +11700,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D102" s="75" t="n">
+      <c r="D102" s="85" t="n">
         <v>2956</v>
       </c>
       <c r="E102" t="inlineStr">
@@ -11121,7 +11725,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D103" s="75" t="n">
+      <c r="D103" s="85" t="n">
         <v>79366.3</v>
       </c>
       <c r="E103" t="inlineStr">
@@ -11146,7 +11750,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D104" s="75" t="n">
+      <c r="D104" s="85" t="n">
         <v>2823</v>
       </c>
       <c r="E104" t="inlineStr">
@@ -11171,7 +11775,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D105" s="75" t="n">
+      <c r="D105" s="85" t="n">
         <v>146.62</v>
       </c>
       <c r="E105" t="inlineStr">
@@ -11196,7 +11800,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D106" s="75" t="n">
+      <c r="D106" s="85" t="n">
         <v>220492.18</v>
       </c>
       <c r="E106" t="inlineStr">
@@ -11221,7 +11825,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D107" s="75" t="n">
+      <c r="D107" s="85" t="n">
         <v>621319.65</v>
       </c>
       <c r="E107" t="inlineStr">
@@ -11246,7 +11850,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D108" s="75" t="n">
+      <c r="D108" s="85" t="n">
         <v>253612.21</v>
       </c>
       <c r="E108" t="inlineStr">
@@ -11271,7 +11875,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D109" s="75" t="n">
+      <c r="D109" s="85" t="n">
         <v>168226.05</v>
       </c>
       <c r="E109" t="inlineStr">
@@ -11296,7 +11900,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D110" s="75" t="n">
+      <c r="D110" s="85" t="n">
         <v>92484.47</v>
       </c>
       <c r="E110" t="inlineStr">
@@ -11321,7 +11925,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D111" s="75" t="n">
+      <c r="D111" s="85" t="n">
         <v>196184</v>
       </c>
       <c r="E111" t="inlineStr">
@@ -11346,7 +11950,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D112" s="75" t="n">
+      <c r="D112" s="85" t="n">
         <v>-1845734.44</v>
       </c>
       <c r="E112" t="inlineStr">
@@ -11371,7 +11975,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D113" s="75" t="n">
+      <c r="D113" s="85" t="n">
         <v>-773623.08</v>
       </c>
       <c r="E113" t="inlineStr">
@@ -11396,7 +12000,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D114" s="75" t="n">
+      <c r="D114" s="85" t="n">
         <v>293846.95</v>
       </c>
       <c r="E114" t="inlineStr">
@@ -11421,7 +12025,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D115" s="75" t="n">
+      <c r="D115" s="85" t="n">
         <v>265493.63</v>
       </c>
       <c r="E115" t="inlineStr">
@@ -11446,7 +12050,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D116" s="75" t="n">
+      <c r="D116" s="85" t="n">
         <v>191530.24</v>
       </c>
       <c r="E116" t="inlineStr">
@@ -11471,7 +12075,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D117" s="75" t="n">
+      <c r="D117" s="85" t="n">
         <v>11587</v>
       </c>
       <c r="E117" t="inlineStr">
@@ -11496,7 +12100,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D118" s="75" t="n">
+      <c r="D118" s="85" t="n">
         <v>93057.11</v>
       </c>
       <c r="E118" t="inlineStr">
@@ -11521,7 +12125,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D119" s="75" t="n">
+      <c r="D119" s="85" t="n">
         <v>528052.08</v>
       </c>
       <c r="E119" t="inlineStr">
@@ -11546,7 +12150,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D120" s="75" t="n">
+      <c r="D120" s="85" t="n">
         <v>116416.16</v>
       </c>
       <c r="E120" t="inlineStr">
@@ -11571,7 +12175,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D121" s="75" t="n">
+      <c r="D121" s="85" t="n">
         <v>146015.91</v>
       </c>
       <c r="E121" t="inlineStr">
@@ -11596,7 +12200,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D122" s="75" t="n">
+      <c r="D122" s="85" t="n">
         <v>95218.77</v>
       </c>
       <c r="E122" t="inlineStr">
@@ -11621,7 +12225,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D123" s="75" t="n">
+      <c r="D123" s="85" t="n">
         <v>195095</v>
       </c>
       <c r="E123" t="inlineStr">
@@ -11646,7 +12250,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D124" s="75" t="n">
+      <c r="D124" s="85" t="n">
         <v>-1846103.64</v>
       </c>
       <c r="E124" t="inlineStr">
@@ -11671,7 +12275,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D125" s="75" t="n">
+      <c r="D125" s="85" t="n">
         <v>-277628.05</v>
       </c>
       <c r="E125" t="inlineStr">
@@ -11696,7 +12300,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D126" s="75" t="n">
+      <c r="D126" s="85" t="n">
         <v>398.98</v>
       </c>
       <c r="E126" t="inlineStr">
@@ -11721,7 +12325,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D127" s="75" t="n">
+      <c r="D127" s="85" t="n">
         <v>262708.89</v>
       </c>
       <c r="E127" t="inlineStr">
@@ -11746,7 +12350,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D128" s="75" t="n">
+      <c r="D128" s="85" t="n">
         <v>263448.71</v>
       </c>
       <c r="E128" t="inlineStr">
@@ -11771,7 +12375,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D129" s="75" t="n">
+      <c r="D129" s="85" t="n">
         <v>259227.76</v>
       </c>
       <c r="E129" t="inlineStr">
@@ -11796,7 +12400,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D130" s="75" t="n">
+      <c r="D130" s="85" t="n">
         <v>406354.65</v>
       </c>
       <c r="E130" t="inlineStr">
@@ -11821,7 +12425,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D131" s="75" t="n">
+      <c r="D131" s="85" t="n">
         <v>77648.91</v>
       </c>
       <c r="E131" t="inlineStr">
@@ -11846,7 +12450,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D132" s="75" t="n">
+      <c r="D132" s="85" t="n">
         <v>102761.37</v>
       </c>
       <c r="E132" t="inlineStr">
@@ -11871,7 +12475,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D133" s="75" t="n">
+      <c r="D133" s="85" t="n">
         <v>78647.42999999999</v>
       </c>
       <c r="E133" t="inlineStr">
@@ -11896,7 +12500,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D134" s="75" t="n">
+      <c r="D134" s="85" t="n">
         <v>144978</v>
       </c>
       <c r="E134" t="inlineStr">
@@ -11921,7 +12525,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D135" s="75" t="n">
+      <c r="D135" s="85" t="n">
         <v>-1787344.57</v>
       </c>
       <c r="E135" t="inlineStr">
@@ -11946,7 +12550,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D136" s="75" t="n">
+      <c r="D136" s="85" t="n">
         <v>246909.77</v>
       </c>
       <c r="E136" t="inlineStr">
@@ -11971,7 +12575,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D137" s="75" t="n">
+      <c r="D137" s="85" t="n">
         <v>199861.29</v>
       </c>
       <c r="E137" t="inlineStr">
@@ -11996,7 +12600,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D138" s="75" t="n">
+      <c r="D138" s="85" t="n">
         <v>338592.34</v>
       </c>
       <c r="E138" t="inlineStr">
@@ -12021,7 +12625,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D139" s="75" t="n">
+      <c r="D139" s="85" t="n">
         <v>-95567.31</v>
       </c>
       <c r="E139" t="inlineStr">
@@ -12046,7 +12650,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D140" s="75" t="n">
+      <c r="D140" s="85" t="n">
         <v>-4000</v>
       </c>
       <c r="E140" t="inlineStr">
@@ -12071,7 +12675,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D141" s="75" t="n">
+      <c r="D141" s="85" t="n">
         <v>49571.73</v>
       </c>
       <c r="E141" t="inlineStr">
@@ -12096,7 +12700,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D142" s="75" t="n">
+      <c r="D142" s="85" t="n">
         <v>9462.879999999999</v>
       </c>
       <c r="E142" t="inlineStr">
@@ -12121,7 +12725,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D143" s="75" t="n">
+      <c r="D143" s="85" t="n">
         <v>2968.54</v>
       </c>
       <c r="E143" t="inlineStr">
@@ -12146,7 +12750,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D144" s="75" t="n">
+      <c r="D144" s="85" t="n">
         <v>11858</v>
       </c>
       <c r="E144" t="inlineStr">
@@ -12171,7 +12775,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D145" s="75" t="n">
+      <c r="D145" s="85" t="n">
         <v>26947.11</v>
       </c>
       <c r="E145" t="inlineStr">
@@ -12196,7 +12800,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D146" s="75" t="n">
+      <c r="D146" s="85" t="n">
         <v>4362.05</v>
       </c>
       <c r="E146" t="inlineStr">
@@ -12221,7 +12825,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D147" s="75" t="n">
+      <c r="D147" s="85" t="n">
         <v>9729.889999999999</v>
       </c>
       <c r="E147" t="inlineStr">
@@ -12246,7 +12850,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D148" s="75" t="n">
+      <c r="D148" s="85" t="n">
         <v>14786</v>
       </c>
       <c r="E148" t="inlineStr">
@@ -12271,7 +12875,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D149" s="75" t="n">
+      <c r="D149" s="85" t="n">
         <v>-25000</v>
       </c>
       <c r="E149" t="inlineStr">
@@ -12296,7 +12900,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D150" s="75" t="n">
+      <c r="D150" s="85" t="n">
         <v>11691.11</v>
       </c>
       <c r="E150" t="inlineStr">
@@ -12321,7 +12925,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D151" s="75" t="n">
+      <c r="D151" s="85" t="n">
         <v>353.66</v>
       </c>
       <c r="E151" t="inlineStr">
@@ -12346,7 +12950,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D152" s="75" t="n">
+      <c r="D152" s="85" t="n">
         <v>2978.98</v>
       </c>
       <c r="E152" t="inlineStr">
@@ -12371,7 +12975,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D153" s="75" t="n">
+      <c r="D153" s="85" t="n">
         <v>1405.28</v>
       </c>
       <c r="E153" t="inlineStr">
@@ -12396,7 +13000,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D154" s="75" t="n">
+      <c r="D154" s="85" t="n">
         <v>31.2</v>
       </c>
       <c r="E154" t="inlineStr">
@@ -12421,7 +13025,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D155" s="75" t="n">
+      <c r="D155" s="85" t="n">
         <v>-120000</v>
       </c>
       <c r="E155" t="inlineStr">
@@ -12446,7 +13050,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D156" s="75" t="n">
+      <c r="D156" s="85" t="n">
         <v>9970.26</v>
       </c>
       <c r="E156" t="inlineStr">
@@ -12471,7 +13075,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D157" s="75" t="n">
+      <c r="D157" s="85" t="n">
         <v>80.48999999999999</v>
       </c>
       <c r="E157" t="inlineStr">
@@ -12496,7 +13100,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D158" s="75" t="n">
+      <c r="D158" s="85" t="n">
         <v>3536.61</v>
       </c>
       <c r="E158" t="inlineStr">
@@ -12521,7 +13125,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D159" s="75" t="n">
+      <c r="D159" s="85" t="n">
         <v>659.65</v>
       </c>
       <c r="E159" t="inlineStr">
@@ -12546,7 +13150,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D160" s="75" t="n">
+      <c r="D160" s="85" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="E160" t="inlineStr">
@@ -12571,7 +13175,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D161" s="75" t="n">
+      <c r="D161" s="85" t="n">
         <v>-182159.16</v>
       </c>
       <c r="E161" t="inlineStr">
@@ -12596,7 +13200,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D162" s="75" t="n">
+      <c r="D162" s="85" t="n">
         <v>27832.1</v>
       </c>
       <c r="E162" t="inlineStr">
@@ -12621,7 +13225,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D163" s="75" t="n">
+      <c r="D163" s="85" t="n">
         <v>69042.92999999999</v>
       </c>
       <c r="E163" t="inlineStr">
@@ -12646,7 +13250,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D164" s="75" t="n">
+      <c r="D164" s="85" t="n">
         <v>-63372</v>
       </c>
       <c r="E164" t="inlineStr">
@@ -12671,7 +13275,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D165" s="75" t="n">
+      <c r="D165" s="85" t="n">
         <v>21629.4</v>
       </c>
       <c r="E165" t="inlineStr">
@@ -12696,7 +13300,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D166" s="75" t="n">
+      <c r="D166" s="85" t="n">
         <v>3911.77</v>
       </c>
       <c r="E166" t="inlineStr">
@@ -12721,7 +13325,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D167" s="75" t="n">
+      <c r="D167" s="85" t="n">
         <v>84249.49000000001</v>
       </c>
       <c r="E167" t="inlineStr">
@@ -12746,7 +13350,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D168" s="75" t="n">
+      <c r="D168" s="85" t="n">
         <v>31662.59</v>
       </c>
       <c r="E168" t="inlineStr">
@@ -12771,7 +13375,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D169" s="75" t="n">
+      <c r="D169" s="85" t="n">
         <v>3035.5</v>
       </c>
       <c r="E169" t="inlineStr">
@@ -12796,7 +13400,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D170" s="75" t="n">
+      <c r="D170" s="85" t="n">
         <v>16179</v>
       </c>
       <c r="E170" t="inlineStr">
@@ -12821,7 +13425,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D171" s="75" t="n">
+      <c r="D171" s="85" t="n">
         <v>7029.13</v>
       </c>
       <c r="E171" t="inlineStr">
@@ -12846,7 +13450,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D172" s="75" t="n">
+      <c r="D172" s="85" t="n">
         <v>-252814.41</v>
       </c>
       <c r="E172" t="inlineStr">
@@ -12871,7 +13475,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D173" s="75" t="n">
+      <c r="D173" s="85" t="n">
         <v>25803.7</v>
       </c>
       <c r="E173" t="inlineStr">
@@ -12896,7 +13500,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D174" s="75" t="n">
+      <c r="D174" s="85" t="n">
         <v>94213.14999999999</v>
       </c>
       <c r="E174" t="inlineStr">
@@ -12921,7 +13525,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D175" s="75" t="n">
+      <c r="D175" s="85" t="n">
         <v>-105000</v>
       </c>
       <c r="E175" t="inlineStr">
@@ -12946,7 +13550,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D176" s="75" t="n">
+      <c r="D176" s="85" t="n">
         <v>42360.83</v>
       </c>
       <c r="E176" t="inlineStr">
@@ -12971,7 +13575,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D177" s="75" t="n">
+      <c r="D177" s="85" t="n">
         <v>15237.12</v>
       </c>
       <c r="E177" t="inlineStr">
@@ -12996,7 +13600,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D178" s="75" t="n">
+      <c r="D178" s="85" t="n">
         <v>84280.23</v>
       </c>
       <c r="E178" t="inlineStr">
@@ -13021,7 +13625,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D179" s="75" t="n">
+      <c r="D179" s="85" t="n">
         <v>39485.9</v>
       </c>
       <c r="E179" t="inlineStr">
@@ -13046,7 +13650,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D180" s="75" t="n">
+      <c r="D180" s="85" t="n">
         <v>30521.91</v>
       </c>
       <c r="E180" t="inlineStr">
@@ -13071,7 +13675,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D181" s="75" t="n">
+      <c r="D181" s="85" t="n">
         <v>7464</v>
       </c>
       <c r="E181" t="inlineStr">
@@ -13096,7 +13700,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D182" s="75" t="n">
+      <c r="D182" s="85" t="n">
         <v>7661.21</v>
       </c>
       <c r="E182" t="inlineStr">
@@ -13121,7 +13725,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D183" s="75" t="n">
+      <c r="D183" s="85" t="n">
         <v>1145</v>
       </c>
       <c r="E183" t="inlineStr">
@@ -13146,7 +13750,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D184" s="75" t="n">
+      <c r="D184" s="85" t="n">
         <v>-1040169.25</v>
       </c>
       <c r="E184" t="inlineStr">
@@ -13171,7 +13775,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D185" s="75" t="n">
+      <c r="D185" s="85" t="n">
         <v>24267.6</v>
       </c>
       <c r="E185" t="inlineStr">
@@ -13196,7 +13800,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D186" s="75" t="n">
+      <c r="D186" s="85" t="n">
         <v>335260.06</v>
       </c>
       <c r="E186" t="inlineStr">
@@ -13221,7 +13825,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D187" s="75" t="n">
+      <c r="D187" s="85" t="n">
         <v>12000</v>
       </c>
       <c r="E187" t="inlineStr">
@@ -13246,7 +13850,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D188" s="75" t="n">
+      <c r="D188" s="85" t="n">
         <v>306127.7</v>
       </c>
       <c r="E188" t="inlineStr">
@@ -13271,7 +13875,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D189" s="75" t="n">
+      <c r="D189" s="85" t="n">
         <v>28545.56</v>
       </c>
       <c r="E189" t="inlineStr">
@@ -13296,7 +13900,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D190" s="75" t="n">
+      <c r="D190" s="85" t="n">
         <v>84158.63</v>
       </c>
       <c r="E190" t="inlineStr">
@@ -13321,7 +13925,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D191" s="75" t="n">
+      <c r="D191" s="85" t="n">
         <v>40897.33</v>
       </c>
       <c r="E191" t="inlineStr">
@@ -13346,7 +13950,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D192" s="75" t="n">
+      <c r="D192" s="85" t="n">
         <v>155731.54</v>
       </c>
       <c r="E192" t="inlineStr">
@@ -13371,7 +13975,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D193" s="75" t="n">
+      <c r="D193" s="85" t="n">
         <v>6720</v>
       </c>
       <c r="E193" t="inlineStr">
@@ -13396,7 +14000,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D194" s="75" t="n">
+      <c r="D194" s="85" t="n">
         <v>11168.8</v>
       </c>
       <c r="E194" t="inlineStr">
@@ -13421,7 +14025,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D195" s="75" t="n">
+      <c r="D195" s="85" t="n">
         <v>4347</v>
       </c>
       <c r="E195" t="inlineStr">
@@ -13446,7 +14050,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D196" s="75" t="n">
+      <c r="D196" s="85" t="n">
         <v>-36500</v>
       </c>
       <c r="E196" t="inlineStr">
@@ -13471,7 +14075,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D197" s="75" t="n">
+      <c r="D197" s="85" t="n">
         <v>682935.3</v>
       </c>
       <c r="E197" t="inlineStr">
@@ -13496,7 +14100,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D198" s="75" t="n">
+      <c r="D198" s="85" t="n">
         <v>89528.25</v>
       </c>
       <c r="E198" t="inlineStr">
@@ -13521,7 +14125,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D199" s="75" t="n">
+      <c r="D199" s="85" t="n">
         <v>34311.46</v>
       </c>
       <c r="E199" t="inlineStr">
@@ -13546,7 +14150,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D200" s="75" t="n">
+      <c r="D200" s="85" t="n">
         <v>-1276087.3</v>
       </c>
       <c r="E200" t="inlineStr">
@@ -13571,7 +14175,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D201" s="75" t="n">
+      <c r="D201" s="85" t="n">
         <v>119684.05</v>
       </c>
       <c r="E201" t="inlineStr">
@@ -13596,7 +14200,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D202" s="75" t="n">
+      <c r="D202" s="85" t="n">
         <v>461523.69</v>
       </c>
       <c r="E202" t="inlineStr">
@@ -13621,7 +14225,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D203" s="75" t="n">
+      <c r="D203" s="85" t="n">
         <v>70350.57000000001</v>
       </c>
       <c r="E203" t="inlineStr">
@@ -13646,7 +14250,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D204" s="75" t="n">
+      <c r="D204" s="85" t="n">
         <v>85236.12</v>
       </c>
       <c r="E204" t="inlineStr">
@@ -13671,7 +14275,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D205" s="75" t="n">
+      <c r="D205" s="85" t="n">
         <v>25179.13</v>
       </c>
       <c r="E205" t="inlineStr">
@@ -13696,7 +14300,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D206" s="75" t="n">
+      <c r="D206" s="85" t="n">
         <v>74422.25999999999</v>
       </c>
       <c r="E206" t="inlineStr">
@@ -13721,7 +14325,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D207" s="75" t="n">
+      <c r="D207" s="85" t="n">
         <v>47.32</v>
       </c>
       <c r="E207" t="inlineStr">
@@ -13746,7 +14350,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D208" s="75" t="n">
+      <c r="D208" s="85" t="n">
         <v>6971.72</v>
       </c>
       <c r="E208" t="inlineStr">
@@ -13771,7 +14375,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D209" s="75" t="n">
+      <c r="D209" s="85" t="n">
         <v>1030.5</v>
       </c>
       <c r="E209" t="inlineStr">
@@ -13796,7 +14400,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D210" s="75" t="n">
+      <c r="D210" s="85" t="n">
         <v>-60617.22</v>
       </c>
       <c r="E210" t="inlineStr">
@@ -13821,7 +14425,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D211" s="75" t="n">
+      <c r="D211" s="85" t="n">
         <v>7827.94</v>
       </c>
       <c r="E211" t="inlineStr">
@@ -13846,7 +14450,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D212" s="75" t="n">
+      <c r="D212" s="85" t="n">
         <v>28798.6</v>
       </c>
       <c r="E212" t="inlineStr">
@@ -13871,7 +14475,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D213" s="75" t="n">
+      <c r="D213" s="85" t="n">
         <v>160</v>
       </c>
       <c r="E213" t="inlineStr">
@@ -13896,7 +14500,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D214" s="75" t="n">
+      <c r="D214" s="85" t="n">
         <v>17017.8</v>
       </c>
       <c r="E214" t="inlineStr">
@@ -13921,7 +14525,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D215" s="75" t="n">
+      <c r="D215" s="85" t="n">
         <v>8.15</v>
       </c>
       <c r="E215" t="inlineStr">
@@ -13946,7 +14550,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D216" s="75" t="n">
+      <c r="D216" s="85" t="n">
         <v>5393.52</v>
       </c>
       <c r="E216" t="inlineStr">
@@ -13971,7 +14575,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D217" s="75" t="n">
+      <c r="D217" s="85" t="n">
         <v>1690.87</v>
       </c>
       <c r="E217" t="inlineStr">
@@ -13996,7 +14600,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D218" s="75" t="n">
+      <c r="D218" s="85" t="n">
         <v>3819</v>
       </c>
       <c r="E218" t="inlineStr">
@@ -14021,7 +14625,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D219" s="75" t="n">
+      <c r="D219" s="85" t="n">
         <v>1623</v>
       </c>
       <c r="E219" t="inlineStr">
@@ -14046,7 +14650,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D220" s="75" t="n">
+      <c r="D220" s="85" t="n">
         <v>-4020097.09</v>
       </c>
       <c r="E220" t="inlineStr">
@@ -14071,7 +14675,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D221" s="75" t="n">
+      <c r="D221" s="85" t="n">
         <v>36589.58</v>
       </c>
       <c r="E221" t="inlineStr">
@@ -14096,7 +14700,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D222" s="75" t="n">
+      <c r="D222" s="85" t="n">
         <v>-21238.18</v>
       </c>
       <c r="E222" t="inlineStr">
@@ -14121,7 +14725,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D223" s="75" t="n">
+      <c r="D223" s="85" t="n">
         <v>1134014.92</v>
       </c>
       <c r="E223" t="inlineStr">
@@ -14146,7 +14750,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D224" s="75" t="n">
+      <c r="D224" s="85" t="n">
         <v>128437.63</v>
       </c>
       <c r="E224" t="inlineStr">
@@ -14171,7 +14775,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D225" s="75" t="n">
+      <c r="D225" s="85" t="n">
         <v>1648002.47</v>
       </c>
       <c r="E225" t="inlineStr">
@@ -14196,7 +14800,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D226" s="75" t="n">
+      <c r="D226" s="85" t="n">
         <v>285429.57</v>
       </c>
       <c r="E226" t="inlineStr">
@@ -14221,7 +14825,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D227" s="75" t="n">
+      <c r="D227" s="85" t="n">
         <v>112954.41</v>
       </c>
       <c r="E227" t="inlineStr">
@@ -14246,7 +14850,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D228" s="75" t="n">
+      <c r="D228" s="85" t="n">
         <v>152125.33</v>
       </c>
       <c r="E228" t="inlineStr">
@@ -14271,7 +14875,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D229" s="75" t="n">
+      <c r="D229" s="85" t="n">
         <v>119756.18</v>
       </c>
       <c r="E229" t="inlineStr">
@@ -14296,7 +14900,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D230" s="75" t="n">
+      <c r="D230" s="85" t="n">
         <v>115151</v>
       </c>
       <c r="E230" t="inlineStr">
@@ -14321,7 +14925,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D231" s="75" t="n">
+      <c r="D231" s="85" t="n">
         <v>55522</v>
       </c>
       <c r="E231" t="inlineStr">
@@ -14346,7 +14950,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D232" s="75" t="n">
+      <c r="D232" s="85" t="n">
         <v>-3945668.63</v>
       </c>
       <c r="E232" t="inlineStr">
@@ -14371,7 +14975,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D233" s="75" t="n">
+      <c r="D233" s="85" t="n">
         <v>51950.17</v>
       </c>
       <c r="E233" t="inlineStr">
@@ -14396,7 +15000,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D234" s="75" t="n">
+      <c r="D234" s="85" t="n">
         <v>1336954</v>
       </c>
       <c r="E234" t="inlineStr">
@@ -14421,7 +15025,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D235" s="75" t="n">
+      <c r="D235" s="85" t="n">
         <v>104164.1</v>
       </c>
       <c r="E235" t="inlineStr">
@@ -14446,7 +15050,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D236" s="75" t="n">
+      <c r="D236" s="85" t="n">
         <v>1410408.29</v>
       </c>
       <c r="E236" t="inlineStr">
@@ -14471,7 +15075,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D237" s="75" t="n">
+      <c r="D237" s="85" t="n">
         <v>204074.66</v>
       </c>
       <c r="E237" t="inlineStr">
@@ -14496,7 +15100,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D238" s="75" t="n">
+      <c r="D238" s="85" t="n">
         <v>162786.02</v>
       </c>
       <c r="E238" t="inlineStr">
@@ -14521,7 +15125,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D239" s="75" t="n">
+      <c r="D239" s="85" t="n">
         <v>74927.98</v>
       </c>
       <c r="E239" t="inlineStr">
@@ -14546,7 +15150,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D240" s="75" t="n">
+      <c r="D240" s="85" t="n">
         <v>102454.37</v>
       </c>
       <c r="E240" t="inlineStr">
@@ -14571,7 +15175,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D241" s="75" t="n">
+      <c r="D241" s="85" t="n">
         <v>75441</v>
       </c>
       <c r="E241" t="inlineStr">
@@ -14596,7 +15200,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D242" s="75" t="n">
+      <c r="D242" s="85" t="n">
         <v>12250</v>
       </c>
       <c r="E242" t="inlineStr">
@@ -14621,7 +15225,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D243" s="75" t="n">
+      <c r="D243" s="85" t="n">
         <v>-4192108.18</v>
       </c>
       <c r="E243" t="inlineStr">
@@ -14646,7 +15250,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D244" s="75" t="n">
+      <c r="D244" s="85" t="n">
         <v>47186.32</v>
       </c>
       <c r="E244" t="inlineStr">
@@ -14671,7 +15275,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D245" s="75" t="n">
+      <c r="D245" s="85" t="n">
         <v>1435652.25</v>
       </c>
       <c r="E245" t="inlineStr">
@@ -14696,7 +15300,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D246" s="75" t="n">
+      <c r="D246" s="85" t="n">
         <v>89534.44</v>
       </c>
       <c r="E246" t="inlineStr">
@@ -14721,7 +15325,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D247" s="75" t="n">
+      <c r="D247" s="85" t="n">
         <v>28000</v>
       </c>
       <c r="E247" t="inlineStr">
@@ -14746,7 +15350,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D248" s="75" t="n">
+      <c r="D248" s="85" t="n">
         <v>1565414.79</v>
       </c>
       <c r="E248" t="inlineStr">
@@ -14771,7 +15375,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D249" s="75" t="n">
+      <c r="D249" s="85" t="n">
         <v>159546.21</v>
       </c>
       <c r="E249" t="inlineStr">
@@ -14796,7 +15400,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D250" s="75" t="n">
+      <c r="D250" s="85" t="n">
         <v>110590.5</v>
       </c>
       <c r="E250" t="inlineStr">
@@ -14821,7 +15425,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D251" s="75" t="n">
+      <c r="D251" s="85" t="n">
         <v>102861.78</v>
       </c>
       <c r="E251" t="inlineStr">
@@ -14846,7 +15450,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D252" s="75" t="n">
+      <c r="D252" s="85" t="n">
         <v>95846.64999999999</v>
       </c>
       <c r="E252" t="inlineStr">
@@ -14871,7 +15475,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D253" s="75" t="n">
+      <c r="D253" s="85" t="n">
         <v>45876</v>
       </c>
       <c r="E253" t="inlineStr">
@@ -14896,7 +15500,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D254" s="75" t="n">
+      <c r="D254" s="85" t="n">
         <v>83963</v>
       </c>
       <c r="E254" t="inlineStr">
@@ -14921,7 +15525,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D255" s="75" t="n">
+      <c r="D255" s="85" t="n">
         <v>-1606736.08</v>
       </c>
       <c r="E255" t="inlineStr">
@@ -14946,7 +15550,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D256" s="75" t="n">
+      <c r="D256" s="85" t="n">
         <v>11810.27</v>
       </c>
       <c r="E256" t="inlineStr">
@@ -14971,7 +15575,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D257" s="75" t="n">
+      <c r="D257" s="85" t="n">
         <v>83140.49000000001</v>
       </c>
       <c r="E257" t="inlineStr">
@@ -14996,7 +15600,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D258" s="75" t="n">
+      <c r="D258" s="85" t="n">
         <v>35063.04</v>
       </c>
       <c r="E258" t="inlineStr">
@@ -15021,7 +15625,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D259" s="75" t="n">
+      <c r="D259" s="85" t="n">
         <v>51872</v>
       </c>
       <c r="E259" t="inlineStr">
@@ -15046,7 +15650,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D260" s="75" t="n">
+      <c r="D260" s="85" t="n">
         <v>712190.6899999999</v>
       </c>
       <c r="E260" t="inlineStr">
@@ -15071,7 +15675,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D261" s="75" t="n">
+      <c r="D261" s="85" t="n">
         <v>371058.72</v>
       </c>
       <c r="E261" t="inlineStr">
@@ -15096,7 +15700,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D262" s="75" t="n">
+      <c r="D262" s="85" t="n">
         <v>63879.98</v>
       </c>
       <c r="E262" t="inlineStr">
@@ -15121,7 +15725,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D263" s="75" t="n">
+      <c r="D263" s="85" t="n">
         <v>14521.69</v>
       </c>
       <c r="E263" t="inlineStr">
@@ -15146,7 +15750,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D264" s="75" t="n">
+      <c r="D264" s="85" t="n">
         <v>267190.19</v>
       </c>
       <c r="E264" t="inlineStr">
@@ -15171,7 +15775,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D265" s="75" t="n">
+      <c r="D265" s="85" t="n">
         <v>15416</v>
       </c>
       <c r="E265" t="inlineStr">
@@ -15196,7 +15800,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D266" s="75" t="n">
+      <c r="D266" s="85" t="n">
         <v>-1854065.71</v>
       </c>
       <c r="E266" t="inlineStr">
@@ -15221,7 +15825,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D267" s="75" t="n">
+      <c r="D267" s="85" t="n">
         <v>14821.35</v>
       </c>
       <c r="E267" t="inlineStr">
@@ -15246,7 +15850,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D268" s="75" t="n">
+      <c r="D268" s="85" t="n">
         <v>54056.48</v>
       </c>
       <c r="E268" t="inlineStr">
@@ -15271,7 +15875,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D269" s="75" t="n">
+      <c r="D269" s="85" t="n">
         <v>30851.77</v>
       </c>
       <c r="E269" t="inlineStr">
@@ -15296,7 +15900,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D270" s="75" t="n">
+      <c r="D270" s="85" t="n">
         <v>862520.42</v>
       </c>
       <c r="E270" t="inlineStr">
@@ -15321,7 +15925,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D271" s="75" t="n">
+      <c r="D271" s="85" t="n">
         <v>360373.72</v>
       </c>
       <c r="E271" t="inlineStr">
@@ -15346,7 +15950,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D272" s="75" t="n">
+      <c r="D272" s="85" t="n">
         <v>84572.03</v>
       </c>
       <c r="E272" t="inlineStr">
@@ -15371,7 +15975,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D273" s="75" t="n">
+      <c r="D273" s="85" t="n">
         <v>27503.48</v>
       </c>
       <c r="E273" t="inlineStr">
@@ -15396,7 +16000,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D274" s="75" t="n">
+      <c r="D274" s="85" t="n">
         <v>371929.89</v>
       </c>
       <c r="E274" t="inlineStr">
@@ -15421,7 +16025,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D275" s="75" t="n">
+      <c r="D275" s="85" t="n">
         <v>11293</v>
       </c>
       <c r="E275" t="inlineStr">
@@ -15446,7 +16050,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D276" s="75" t="n">
+      <c r="D276" s="85" t="n">
         <v>4426</v>
       </c>
       <c r="E276" t="inlineStr">
@@ -15471,7 +16075,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D277" s="75" t="n">
+      <c r="D277" s="85" t="n">
         <v>-1793621.56</v>
       </c>
       <c r="E277" t="inlineStr">
@@ -15496,7 +16100,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D278" s="75" t="n">
+      <c r="D278" s="85" t="n">
         <v>14534.84</v>
       </c>
       <c r="E278" t="inlineStr">
@@ -15521,7 +16125,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D279" s="75" t="n">
+      <c r="D279" s="85" t="n">
         <v>65906.69</v>
       </c>
       <c r="E279" t="inlineStr">
@@ -15546,7 +16150,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D280" s="75" t="n">
+      <c r="D280" s="85" t="n">
         <v>31042.81</v>
       </c>
       <c r="E280" t="inlineStr">
@@ -15571,7 +16175,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D281" s="75" t="n">
+      <c r="D281" s="85" t="n">
         <v>96000</v>
       </c>
       <c r="E281" t="inlineStr">
@@ -15596,7 +16200,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D282" s="75" t="n">
+      <c r="D282" s="85" t="n">
         <v>745956.71</v>
       </c>
       <c r="E282" t="inlineStr">
@@ -15621,7 +16225,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D283" s="75" t="n">
+      <c r="D283" s="85" t="n">
         <v>430360.81</v>
       </c>
       <c r="E283" t="inlineStr">
@@ -15646,7 +16250,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D284" s="75" t="n">
+      <c r="D284" s="85" t="n">
         <v>63947.25</v>
       </c>
       <c r="E284" t="inlineStr">
@@ -15671,7 +16275,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D285" s="75" t="n">
+      <c r="D285" s="85" t="n">
         <v>20527.86</v>
       </c>
       <c r="E285" t="inlineStr">
@@ -15696,7 +16300,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D286" s="75" t="n">
+      <c r="D286" s="85" t="n">
         <v>230794.19</v>
       </c>
       <c r="E286" t="inlineStr">
@@ -15721,7 +16325,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D287" s="75" t="n">
+      <c r="D287" s="85" t="n">
         <v>7171</v>
       </c>
       <c r="E287" t="inlineStr">
@@ -15746,7 +16350,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D288" s="75" t="n">
+      <c r="D288" s="85" t="n">
         <v>11162</v>
       </c>
       <c r="E288" t="inlineStr">
@@ -15771,7 +16375,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D289" s="75" t="n">
+      <c r="D289" s="85" t="n">
         <v>19007.52</v>
       </c>
       <c r="E289" t="inlineStr">
@@ -15796,7 +16400,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D290" s="75" t="n">
+      <c r="D290" s="85" t="n">
         <v>-109765.32</v>
       </c>
       <c r="E290" t="inlineStr">
@@ -15821,7 +16425,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D291" s="75" t="n">
+      <c r="D291" s="85" t="n">
         <v>194.47</v>
       </c>
       <c r="E291" t="inlineStr">
@@ -15846,7 +16450,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D292" s="75" t="n">
+      <c r="D292" s="85" t="n">
         <v>36000</v>
       </c>
       <c r="E292" t="inlineStr">
@@ -15871,7 +16475,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D293" s="75" t="n">
+      <c r="D293" s="85" t="n">
         <v>7991.46</v>
       </c>
       <c r="E293" t="inlineStr">
@@ -15896,7 +16500,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D294" s="75" t="n">
+      <c r="D294" s="85" t="n">
         <v>20030</v>
       </c>
       <c r="E294" t="inlineStr">
@@ -15921,7 +16525,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D295" s="75" t="n">
+      <c r="D295" s="85" t="n">
         <v>461.73</v>
       </c>
       <c r="E295" t="inlineStr">
@@ -15946,7 +16550,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D296" s="75" t="n">
+      <c r="D296" s="85" t="n">
         <v>4196</v>
       </c>
       <c r="E296" t="inlineStr">
@@ -15971,7 +16575,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D297" s="75" t="n">
+      <c r="D297" s="85" t="n">
         <v>19007.52</v>
       </c>
       <c r="E297" t="inlineStr">
@@ -15996,7 +16600,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D298" s="75" t="n">
+      <c r="D298" s="85" t="n">
         <v>-109765.32</v>
       </c>
       <c r="E298" t="inlineStr">
@@ -16021,7 +16625,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D299" s="75" t="n">
+      <c r="D299" s="85" t="n">
         <v>4960.18</v>
       </c>
       <c r="E299" t="inlineStr">
@@ -16046,7 +16650,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D300" s="75" t="n">
+      <c r="D300" s="85" t="n">
         <v>25000</v>
       </c>
       <c r="E300" t="inlineStr">
@@ -16071,7 +16675,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D301" s="75" t="n">
+      <c r="D301" s="85" t="n">
         <v>12837.77</v>
       </c>
       <c r="E301" t="inlineStr">
@@ -16096,7 +16700,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D302" s="75" t="n">
+      <c r="D302" s="85" t="n">
         <v>22645</v>
       </c>
       <c r="E302" t="inlineStr">
@@ -16121,7 +16725,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D303" s="75" t="n">
+      <c r="D303" s="85" t="n">
         <v>153.5</v>
       </c>
       <c r="E303" t="inlineStr">
@@ -16146,7 +16750,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D304" s="75" t="n">
+      <c r="D304" s="85" t="n">
         <v>3126</v>
       </c>
       <c r="E304" t="inlineStr">
@@ -16171,7 +16775,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D305" s="75" t="n">
+      <c r="D305" s="85" t="n">
         <v>829.6</v>
       </c>
       <c r="E305" t="inlineStr">
@@ -16196,7 +16800,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D306" s="75" t="n">
+      <c r="D306" s="85" t="n">
         <v>-84565.2</v>
       </c>
       <c r="E306" t="inlineStr">
@@ -16221,7 +16825,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D307" s="75" t="n">
+      <c r="D307" s="85" t="n">
         <v>24000</v>
       </c>
       <c r="E307" t="inlineStr">
@@ -16246,7 +16850,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D308" s="75" t="n">
+      <c r="D308" s="85" t="n">
         <v>8780.15</v>
       </c>
       <c r="E308" t="inlineStr">
@@ -16271,7 +16875,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D309" s="75" t="n">
+      <c r="D309" s="85" t="n">
         <v>25230</v>
       </c>
       <c r="E309" t="inlineStr">
@@ -16296,7 +16900,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D310" s="75" t="n">
+      <c r="D310" s="85" t="n">
         <v>123.98</v>
       </c>
       <c r="E310" t="inlineStr">
@@ -16321,7 +16925,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D311" s="75" t="n">
+      <c r="D311" s="85" t="n">
         <v>3017</v>
       </c>
       <c r="E311" t="inlineStr">
@@ -16346,7 +16950,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D312" s="75" t="n">
+      <c r="D312" s="85" t="n">
         <v>-72000</v>
       </c>
       <c r="E312" t="inlineStr">
@@ -16371,7 +16975,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D313" s="75" t="n">
+      <c r="D313" s="85" t="n">
         <v>3002.35</v>
       </c>
       <c r="E313" t="inlineStr">
@@ -16396,7 +17000,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D314" s="75" t="n">
+      <c r="D314" s="85" t="n">
         <v>10807</v>
       </c>
       <c r="E314" t="inlineStr">
@@ -16421,7 +17025,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D315" s="75" t="n">
+      <c r="D315" s="85" t="n">
         <v>69715.82000000001</v>
       </c>
       <c r="E315" t="inlineStr">
@@ -16446,7 +17050,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D316" s="75" t="n">
+      <c r="D316" s="85" t="n">
         <v>4296</v>
       </c>
       <c r="E316" t="inlineStr">
@@ -16471,7 +17075,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D317" s="75" t="n">
+      <c r="D317" s="85" t="n">
         <v>-72001</v>
       </c>
       <c r="E317" t="inlineStr">
@@ -16496,7 +17100,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D318" s="75" t="n">
+      <c r="D318" s="85" t="n">
         <v>340.62</v>
       </c>
       <c r="E318" t="inlineStr">
@@ -16521,7 +17125,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D319" s="75" t="n">
+      <c r="D319" s="85" t="n">
         <v>11257</v>
       </c>
       <c r="E319" t="inlineStr">
@@ -16546,7 +17150,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D320" s="75" t="n">
+      <c r="D320" s="85" t="n">
         <v>69340.75999999999</v>
       </c>
       <c r="E320" t="inlineStr">
@@ -16571,7 +17175,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D321" s="75" t="n">
+      <c r="D321" s="85" t="n">
         <v>2203.93</v>
       </c>
       <c r="E321" t="inlineStr">
@@ -16596,7 +17200,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D322" s="75" t="n">
+      <c r="D322" s="85" t="n">
         <v>-72000</v>
       </c>
       <c r="E322" t="inlineStr">
@@ -16621,7 +17225,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D323" s="75" t="n">
+      <c r="D323" s="85" t="n">
         <v>2422.9</v>
       </c>
       <c r="E323" t="inlineStr">
@@ -16646,7 +17250,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D324" s="75" t="n">
+      <c r="D324" s="85" t="n">
         <v>11458</v>
       </c>
       <c r="E324" t="inlineStr">
@@ -16671,7 +17275,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D325" s="75" t="n">
+      <c r="D325" s="85" t="n">
         <v>67298.08</v>
       </c>
       <c r="E325" t="inlineStr">
@@ -16696,7 +17300,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D326" s="75" t="n">
+      <c r="D326" s="85" t="n">
         <v>24671.28</v>
       </c>
       <c r="E326" t="inlineStr">

--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -16,6 +16,10 @@
     <sheet name="Dim_Entity" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Dim_Calendar" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Fact_TrialBalance" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PQ_Dim_FilePrefix" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PQ_GIFI_Mapping" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PQ_Fallback_MapNo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="PQ_Exceptions" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1496,6 +1500,52 @@
 </table>
 </file>
 
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="PQ_Dim_FilePrefix" displayName="PQ_Dim_FilePrefix" ref="A1:B17" headerRowCount="1">
+  <autoFilter ref="A1:B17"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="FilePrefix"/>
+    <tableColumn id="2" name="EntityId"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PQ_GIFI_Mapping" displayName="PQ_GIFI_Mapping" ref="A1:B58" headerRowCount="1">
+  <autoFilter ref="A1:B58"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="GIFICode"/>
+    <tableColumn id="2" name="Category"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PQ_Fallback_MapNo" displayName="PQ_Fallback_MapNo" ref="A1:C8" headerRowCount="1">
+  <autoFilter ref="A1:C8"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="FilePrefix"/>
+    <tableColumn id="2" name="MapNoNormalized"/>
+    <tableColumn id="3" name="Category"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="PQ_Exceptions" displayName="PQ_Exceptions" ref="A1:C7" headerRowCount="1">
+  <autoFilter ref="A1:C7"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="FilePrefix"/>
+    <tableColumn id="2" name="AccountNo"/>
+    <tableColumn id="3" name="Category"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3637,6 +3687,1239 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C7C2B8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="94" t="inlineStr">
+        <is>
+          <t>FilePrefix</t>
+        </is>
+      </c>
+      <c r="B1" s="94" t="inlineStr">
+        <is>
+          <t>EntityId</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>935_742</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>9357-7427 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>936_167</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9366-1676 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>942_454</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9425-4547 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>945_416</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9455-4169 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>945_417</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>9455-4177 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>945_420</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9455-4201 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aub_Stl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bis_Gur</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/A_BisGur</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lob_Lou</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Res_Her</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Res_In3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Res_Ind</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Res_Sa2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>San_Lea</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>San_San</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/A_SanSan</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C7C2B8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="94" t="inlineStr">
+        <is>
+          <t>GIFICode</t>
+        </is>
+      </c>
+      <c r="B1" s="94" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>8094</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>8096</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8230</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8239</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8241</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8242</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8248</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8249</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8300</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>8340</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8360</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8450</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8461</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8520</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8522</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8523</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>8670</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>8690</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8691</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>8710</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8711</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8713</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8714</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8760</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>8811</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8860</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8863</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8871</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>8910</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8912</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9060</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9061</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>9066</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>9130</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9133</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>9134</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>9200</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>9221</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>9225</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>9270</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9281</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>9793</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9990</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C7C2B8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="94" t="inlineStr">
+        <is>
+          <t>FilePrefix</t>
+        </is>
+      </c>
+      <c r="B1" s="94" t="inlineStr">
+        <is>
+          <t>MapNoNormalized</t>
+        </is>
+      </c>
+      <c r="C1" s="94" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>San_San</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>San_San</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>San_San</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>San_San</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>40.6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>40.26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San_San</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C7C2B8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="94" t="inlineStr">
+        <is>
+          <t>FilePrefix</t>
+        </is>
+      </c>
+      <c r="B1" s="94" t="inlineStr">
+        <is>
+          <t>AccountNo</t>
+        </is>
+      </c>
+      <c r="C1" s="94" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>45130</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>45125</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>44215</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>33455</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Res_In2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>45150</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/Sandhu_Group_Interactive_Dashboard.xlsx
+++ b/output/Sandhu_Group_Interactive_Dashboard.xlsx
@@ -912,12 +912,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'02 Profitability'!$B$21:$B$33</f>
+              <f>'02 Profitability'!$B$21:$B$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'02 Profitability'!$C$21:$C$33</f>
+              <f>'02 Profitability'!$C$21:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -1475,8 +1475,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Dim_Calendar" displayName="Dim_Calendar" ref="A1:C4" headerRowCount="1">
-  <autoFilter ref="A1:C4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Dim_Calendar" displayName="Dim_Calendar" ref="A1:C5" headerRowCount="1">
+  <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
     <tableColumn id="1" name="FiscalYear"/>
     <tableColumn id="2" name="YearEnd"/>
@@ -1487,8 +1487,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Fact_TrialBalance" displayName="Fact_TrialBalance" ref="A1:E326" headerRowCount="1">
-  <autoFilter ref="A1:E326"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Fact_TrialBalance" displayName="Fact_TrialBalance" ref="A1:E440" headerRowCount="1">
+  <autoFilter ref="A1:E440"/>
   <tableColumns count="5">
     <tableColumn id="1" name="EntityId"/>
     <tableColumn id="2" name="Category"/>
@@ -1512,8 +1512,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PQ_GIFI_Mapping" displayName="PQ_GIFI_Mapping" ref="A1:B58" headerRowCount="1">
-  <autoFilter ref="A1:B58"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PQ_GIFI_Mapping" displayName="PQ_GIFI_Mapping" ref="A1:B59" headerRowCount="1">
+  <autoFilter ref="A1:B59"/>
   <tableColumns count="2">
     <tableColumn id="1" name="GIFICode"/>
     <tableColumn id="2" name="Category"/>
@@ -3672,7 +3672,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="K2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Dim_Calendar!$A$2:$A$4</formula1>
+      <formula1>=Dim_Calendar!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -3920,7 +3920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4620,6 +4620,18 @@
       <c r="B58" t="inlineStr">
         <is>
           <t>Income Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gain on Sale</t>
         </is>
       </c>
     </row>
@@ -5365,11 +5377,11 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Gain on Sale</t>
         </is>
       </c>
       <c r="C23" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Gain on Sale",Fact_TrialBalance[FiscalYear],$H$6))</f>
         <v/>
       </c>
       <c r="D23" s="1" t="n"/>
@@ -5386,11 +5398,11 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C24" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D24" s="1" t="n"/>
@@ -5407,11 +5419,11 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C25" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D25" s="1" t="n"/>
@@ -5428,11 +5440,11 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C26" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D26" s="1" t="n"/>
@@ -5449,11 +5461,11 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C27" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D27" s="1" t="n"/>
@@ -5470,11 +5482,11 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C28" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D28" s="1" t="n"/>
@@ -5491,11 +5503,11 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C29" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D29" s="1" t="n"/>
@@ -5512,11 +5524,11 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C30" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D30" s="1" t="n"/>
@@ -5533,11 +5545,11 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C31" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D31" s="1" t="n"/>
@@ -5554,11 +5566,11 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C32" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D32" s="1" t="n"/>
@@ -5575,11 +5587,11 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C33" s="44">
-        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6)</f>
         <v/>
       </c>
       <c r="D33" s="1" t="n"/>
@@ -5594,8 +5606,15 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="n"/>
-      <c r="C34" s="1" t="n"/>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C34" s="44">
+        <f>SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6)</f>
+        <v/>
+      </c>
       <c r="D34" s="1" t="n"/>
       <c r="E34" s="1" t="n"/>
       <c r="F34" s="1" t="n"/>
@@ -5622,70 +5641,57 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="60" t="inlineStr">
-        <is>
-          <t>Key Ratios — Common-Size P&amp;L (% of Revenue), Selected Entity vs Group, Same Year</t>
-        </is>
-      </c>
-      <c r="C36" s="50" t="n"/>
-      <c r="D36" s="50" t="n"/>
-      <c r="E36" s="50" t="n"/>
-      <c r="F36" s="50" t="n"/>
-      <c r="G36" s="50" t="n"/>
-      <c r="H36" s="50" t="n"/>
-      <c r="I36" s="50" t="n"/>
-      <c r="J36" s="50" t="n"/>
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="n"/>
+      <c r="D36" s="1" t="n"/>
+      <c r="E36" s="1" t="n"/>
+      <c r="F36" s="1" t="n"/>
+      <c r="G36" s="1" t="n"/>
+      <c r="H36" s="1" t="n"/>
+      <c r="I36" s="1" t="n"/>
+      <c r="J36" s="1" t="n"/>
       <c r="K36" s="1" t="n"/>
       <c r="L36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="61" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C37" s="61" t="inlineStr">
-        <is>
-          <t>This Entity</t>
-        </is>
-      </c>
-      <c r="D37" s="61" t="inlineStr">
-        <is>
-          <t>Group Avg</t>
-        </is>
-      </c>
-      <c r="E37" s="61" t="inlineStr">
-        <is>
-          <t>vs Group (pp)</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="n"/>
-      <c r="G37" s="1" t="n"/>
-      <c r="H37" s="1" t="n"/>
-      <c r="I37" s="1" t="n"/>
-      <c r="J37" s="1" t="n"/>
+      <c r="B37" s="60" t="inlineStr">
+        <is>
+          <t>Key Ratios — Common-Size P&amp;L (% of Revenue), Selected Entity vs Group, Same Year</t>
+        </is>
+      </c>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+      <c r="E37" s="50" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="50" t="n"/>
+      <c r="H37" s="50" t="n"/>
+      <c r="I37" s="50" t="n"/>
+      <c r="J37" s="50" t="n"/>
       <c r="K37" s="1" t="n"/>
       <c r="L37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="62" t="inlineStr">
-        <is>
-          <t>COGS</t>
-        </is>
-      </c>
-      <c r="C38" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
-        <v/>
-      </c>
-      <c r="D38" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
-        <v/>
-      </c>
-      <c r="E38" s="63">
-        <f>C38-D38</f>
-        <v/>
+      <c r="B38" s="61" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C38" s="61" t="inlineStr">
+        <is>
+          <t>This Entity</t>
+        </is>
+      </c>
+      <c r="D38" s="61" t="inlineStr">
+        <is>
+          <t>Group Avg</t>
+        </is>
+      </c>
+      <c r="E38" s="61" t="inlineStr">
+        <is>
+          <t>vs Group (pp)</t>
+        </is>
       </c>
       <c r="F38" s="1" t="n"/>
       <c r="G38" s="1" t="n"/>
@@ -5699,15 +5705,15 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="62" t="inlineStr">
         <is>
-          <t>Payroll &amp; Benefits</t>
+          <t>COGS</t>
         </is>
       </c>
       <c r="C39" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D39" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E39" s="63">
@@ -5726,15 +5732,15 @@
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="62" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="C40" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D40" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E40" s="63">
@@ -5753,15 +5759,15 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="62" t="inlineStr">
         <is>
-          <t>Marketing &amp; Entertainment</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C41" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D41" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E41" s="63">
@@ -5780,15 +5786,15 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="62" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Marketing &amp; Entertainment</t>
         </is>
       </c>
       <c r="C42" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D42" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Marketing &amp; Entertainment",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E42" s="63">
@@ -5807,15 +5813,15 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="62" t="inlineStr">
         <is>
-          <t>Management Fees (Interco)</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C43" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D43" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Administrative",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E43" s="63">
@@ -5834,15 +5840,15 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="62" t="inlineStr">
         <is>
-          <t>Interest &amp; Financing</t>
+          <t>Management Fees (Interco)</t>
         </is>
       </c>
       <c r="C44" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D44" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Management Fees (Interco)",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E44" s="63">
@@ -5861,15 +5867,15 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="62" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
+          <t>Interest &amp; Financing</t>
         </is>
       </c>
       <c r="C45" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D45" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Interest &amp; Financing",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E45" s="63">
@@ -5888,15 +5894,15 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="62" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="C46" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D46" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Repairs &amp; Maintenance",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E46" s="63">
@@ -5915,15 +5921,15 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="62" t="inlineStr">
         <is>
-          <t>Other Operating</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="C47" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D47" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Amortization",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E47" s="63">
@@ -5942,15 +5948,15 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="62" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Other Operating</t>
         </is>
       </c>
       <c r="C48" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="D48" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Other Operating",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
         <v/>
       </c>
       <c r="E48" s="63">
@@ -5967,10 +5973,23 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
-      <c r="B49" s="62" t="n"/>
-      <c r="C49" s="62" t="n"/>
-      <c r="D49" s="62" t="n"/>
-      <c r="E49" s="62" t="n"/>
+      <c r="B49" s="62" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C49" s="63">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D49" s="63">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Income Tax",Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E49" s="63">
+        <f>C49-D49</f>
+        <v/>
+      </c>
       <c r="F49" s="1" t="n"/>
       <c r="G49" s="1" t="n"/>
       <c r="H49" s="1" t="n"/>
@@ -5981,23 +6000,10 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
-      <c r="B50" s="64" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C50" s="65">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
-        <v/>
-      </c>
-      <c r="D50" s="63">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
-        <v/>
-      </c>
-      <c r="E50" s="63">
-        <f>C50-D50</f>
-        <v/>
-      </c>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
       <c r="F50" s="1" t="n"/>
       <c r="G50" s="1" t="n"/>
       <c r="H50" s="1" t="n"/>
@@ -6010,15 +6016,21 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="64" t="inlineStr">
         <is>
-          <t>EBITDA Margin</t>
+          <t>Gross Margin</t>
         </is>
       </c>
       <c r="C51" s="65">
-        <f>B15</f>
-        <v/>
-      </c>
-      <c r="D51" s="62" t="n"/>
-      <c r="E51" s="62" t="n"/>
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D51" s="63">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],$H$6)))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="E51" s="63">
+        <f>C51-D51</f>
+        <v/>
+      </c>
       <c r="F51" s="1" t="n"/>
       <c r="G51" s="1" t="n"/>
       <c r="H51" s="1" t="n"/>
@@ -6031,11 +6043,11 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="64" t="inlineStr">
         <is>
-          <t>Net Margin</t>
+          <t>EBITDA Margin</t>
         </is>
       </c>
       <c r="C52" s="65">
-        <f>IFERROR(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <f>B15</f>
         <v/>
       </c>
       <c r="D52" s="62" t="n"/>
@@ -6050,119 +6062,104 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
-      <c r="B53" s="54" t="inlineStr">
-        <is>
-          <t>"Group Avg" = that category's total across all 16 entities ÷ group revenue, same fiscal year (a size-weighted benchmark, not an average of each entity's own ratio).</t>
-        </is>
-      </c>
+      <c r="B53" s="64" t="inlineStr">
+        <is>
+          <t>Net Margin</t>
+        </is>
+      </c>
+      <c r="C53" s="65">
+        <f>IFERROR(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],$H$6))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],$H$6))),0)</f>
+        <v/>
+      </c>
+      <c r="D53" s="62" t="n"/>
+      <c r="E53" s="62" t="n"/>
+      <c r="F53" s="1" t="n"/>
+      <c r="G53" s="1" t="n"/>
+      <c r="H53" s="1" t="n"/>
+      <c r="I53" s="1" t="n"/>
+      <c r="J53" s="1" t="n"/>
       <c r="K53" s="1" t="n"/>
       <c r="L53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
-      <c r="B54" s="1" t="n"/>
-      <c r="C54" s="1" t="n"/>
-      <c r="D54" s="1" t="n"/>
-      <c r="E54" s="1" t="n"/>
-      <c r="F54" s="1" t="n"/>
-      <c r="G54" s="1" t="n"/>
-      <c r="H54" s="1" t="n"/>
-      <c r="I54" s="1" t="n"/>
-      <c r="J54" s="1" t="n"/>
+      <c r="B54" s="54" t="inlineStr">
+        <is>
+          <t>"Group Avg" = that category's total across all 16 entities ÷ group revenue, same fiscal year (a size-weighted benchmark, not an average of each entity's own ratio).</t>
+        </is>
+      </c>
       <c r="K54" s="1" t="n"/>
       <c r="L54" s="1" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
-      <c r="B55" s="60" t="inlineStr">
-        <is>
-          <t>3-Year Trend — Selected Entity</t>
-        </is>
-      </c>
-      <c r="C55" s="50" t="n"/>
-      <c r="D55" s="50" t="n"/>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="50" t="n"/>
-      <c r="G55" s="50" t="n"/>
-      <c r="H55" s="50" t="n"/>
-      <c r="I55" s="50" t="n"/>
-      <c r="J55" s="50" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="n"/>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
+      <c r="I55" s="1" t="n"/>
+      <c r="J55" s="1" t="n"/>
       <c r="K55" s="1" t="n"/>
       <c r="L55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n"/>
-      <c r="B56" s="61" t="inlineStr">
-        <is>
-          <t>Fiscal Year</t>
-        </is>
-      </c>
-      <c r="C56" s="61" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D56" s="61" t="inlineStr">
-        <is>
-          <t>COGS %</t>
-        </is>
-      </c>
-      <c r="E56" s="61" t="inlineStr">
-        <is>
-          <t>Payroll %</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="n"/>
-      <c r="G56" s="61" t="inlineStr">
-        <is>
-          <t>Occupancy %</t>
-        </is>
-      </c>
-      <c r="H56" s="61" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="I56" s="61" t="inlineStr">
-        <is>
-          <t>Net Margin</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="n"/>
+      <c r="B56" s="60" t="inlineStr">
+        <is>
+          <t>3-Year Trend — Selected Entity</t>
+        </is>
+      </c>
+      <c r="C56" s="50" t="n"/>
+      <c r="D56" s="50" t="n"/>
+      <c r="E56" s="50" t="n"/>
+      <c r="F56" s="50" t="n"/>
+      <c r="G56" s="50" t="n"/>
+      <c r="H56" s="50" t="n"/>
+      <c r="I56" s="50" t="n"/>
+      <c r="J56" s="50" t="n"/>
       <c r="K56" s="1" t="n"/>
       <c r="L56" s="1" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="62" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="C57" s="66">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))</f>
-        <v/>
-      </c>
-      <c r="D57" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
-        <v/>
-      </c>
-      <c r="E57" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
-        <v/>
+      <c r="B57" s="61" t="inlineStr">
+        <is>
+          <t>Fiscal Year</t>
+        </is>
+      </c>
+      <c r="C57" s="61" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D57" s="61" t="inlineStr">
+        <is>
+          <t>COGS %</t>
+        </is>
+      </c>
+      <c r="E57" s="61" t="inlineStr">
+        <is>
+          <t>Payroll %</t>
+        </is>
       </c>
       <c r="F57" s="1" t="n"/>
-      <c r="G57" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
-        <v/>
-      </c>
-      <c r="H57" s="63">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2023")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2023")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
-        <v/>
-      </c>
-      <c r="I57" s="63">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2023")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
-        <v/>
+      <c r="G57" s="61" t="inlineStr">
+        <is>
+          <t>Occupancy %</t>
+        </is>
+      </c>
+      <c r="H57" s="61" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="I57" s="61" t="inlineStr">
+        <is>
+          <t>Net Margin</t>
+        </is>
       </c>
       <c r="J57" s="1" t="n"/>
       <c r="K57" s="1" t="n"/>
@@ -6172,32 +6169,32 @@
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="62" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="C58" s="66">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))</f>
         <v/>
       </c>
       <c r="D58" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
         <v/>
       </c>
       <c r="E58" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
         <v/>
       </c>
       <c r="F58" s="1" t="n"/>
       <c r="G58" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2023"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
         <v/>
       </c>
       <c r="H58" s="63">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2024")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2024")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2023")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2023")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
         <v/>
       </c>
       <c r="I58" s="63">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2024")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2023")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2023"))),0)</f>
         <v/>
       </c>
       <c r="J58" s="1" t="n"/>
@@ -6208,32 +6205,32 @@
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="62" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C59" s="66">
-        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))</f>
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))</f>
         <v/>
       </c>
       <c r="D59" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
         <v/>
       </c>
       <c r="E59" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
         <v/>
       </c>
       <c r="F59" s="1" t="n"/>
       <c r="G59" s="63">
-        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2024"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
         <v/>
       </c>
       <c r="H59" s="63">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2024")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2024")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
         <v/>
       </c>
       <c r="I59" s="63">
-        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2025")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2024")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2024"))),0)</f>
         <v/>
       </c>
       <c r="J59" s="1" t="n"/>
@@ -6242,14 +6239,36 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
-      <c r="B60" s="1" t="n"/>
-      <c r="C60" s="1" t="n"/>
-      <c r="D60" s="1" t="n"/>
-      <c r="E60" s="1" t="n"/>
+      <c r="B60" s="62" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C60" s="66">
+        <f>-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))</f>
+        <v/>
+      </c>
+      <c r="D60" s="63">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"COGS",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
+      <c r="E60" s="63">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Payroll &amp; Benefits",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
       <c r="F60" s="1" t="n"/>
-      <c r="G60" s="1" t="n"/>
-      <c r="H60" s="1" t="n"/>
-      <c r="I60" s="1" t="n"/>
+      <c r="G60" s="63">
+        <f>IFERROR((SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Occupancy",Fact_TrialBalance[FiscalYear],"FY2025"))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
+      <c r="H60" s="63">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2025")-SUMPRODUCT((Fact_TrialBalance[EntityId]=$C$8)*(Fact_TrialBalance[FiscalYear]="FY2025")*(ISNUMBER(MATCH(Fact_TrialBalance[Category],{"Interest &amp; Financing","Amortization","Income Tax"},0)))*Fact_TrialBalance[Amount])))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
+      <c r="I60" s="63">
+        <f>IFERROR((-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[FiscalYear],"FY2025")))/(-(SUMIFS(Fact_TrialBalance[Amount],Fact_TrialBalance[EntityId],$C$8,Fact_TrialBalance[Category],"Operating Revenue",Fact_TrialBalance[FiscalYear],"FY2025"))),0)</f>
+        <v/>
+      </c>
       <c r="J60" s="1" t="n"/>
       <c r="K60" s="1" t="n"/>
       <c r="L60" s="1" t="n"/>
@@ -6400,12 +6419,10 @@
     <mergeCell ref="G15:H16"/>
     <mergeCell ref="B15:C16"/>
     <mergeCell ref="D15:E16"/>
-    <mergeCell ref="B53:J53"/>
+    <mergeCell ref="B37:J37"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B55:J55"/>
     <mergeCell ref="B2:J3"/>
-    <mergeCell ref="B36:J36"/>
     <mergeCell ref="I15:J16"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="G11:H12"/>
@@ -6414,13 +6431,15 @@
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="C6:E6"/>
+    <mergeCell ref="B54:J54"/>
     <mergeCell ref="B11:C12"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="D11:E12"/>
     <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B56:J56"/>
     <mergeCell ref="B19:E19"/>
   </mergeCells>
-  <conditionalFormatting sqref="E38:E48">
+  <conditionalFormatting sqref="E39:E49">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.005</formula>
     </cfRule>
@@ -6433,7 +6452,7 @@
       <formula1>=Dim_Entity!$B$2:$B$17</formula1>
     </dataValidation>
     <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Dim_Calendar!$A$2:$A$4</formula1>
+      <formula1>=Dim_Calendar!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -11518,7 +11537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -11545,7 +11564,7 @@
     <row r="3">
       <c r="A3" s="90" t="inlineStr">
         <is>
-          <t>Scope: all 16 entities (both family trusts — Gurpreet Sandhu Trust, Harpreet Sandhu Trust — excluded from scope per instruction; ~$4-$10/yr activity per the handoff, immaterial). Every one of these was rebuilt fresh from its raw CaseWare WTB export in this session (not carried over from any prior file) and covers 3 fiscal years: FY2023, FY2024, FY2025.</t>
+          <t>Scope: all 16 entities (both family trusts — Gurpreet Sandhu Trust, Harpreet Sandhu Trust — excluded from scope per instruction; ~$4-$10/yr activity per the handoff, immaterial). Every one of these was rebuilt fresh from its raw CaseWare WTB export in this session (not carried over from any prior file) and covers FY2023-FY2025 for all 16 entities, plus FY2026 for 15 of them (Sandhu &amp; Sandhu Enr. pending — see below).</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -11559,7 +11578,7 @@
     <row r="5">
       <c r="A5" s="90" t="inlineStr">
         <is>
-          <t>Missing: Sandhu &amp; Sandhu Enr.'s Corporate Taxprep export (its WTB was supplied and is included).</t>
+          <t>FY2026 added from Sandhu_G__2026.xlsx — the single consolidated CaseWare export (16 tabs, one per entity, same column layout as the individual WTB files) your accountant can prepare each year-end instead of 16 separate files. Recommended as the ongoing yearly source: one document, can't miss a company, can't mismatch years across files. As with every other WTB file seen in this project, its column header dates are stale by one year — the column printed 'Final: 2025-03-31' is actually FY2026 (confirmed two ways: 15 of 16 entities' 'Prior' columns match already-validated FY2025 to the cent, and Res_Ind's 'Final' column matches the standalone, independently-confirmed Res_Ind_2026_WTB.xlsx exactly). Column POSITION is trusted, never the header text.</t>
         </is>
       </c>
       <c r="B5" s="1" t="n"/>
@@ -11571,9 +11590,9 @@
       <c r="C6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="90" t="inlineStr">
-        <is>
-          <t>Dim_Entity updated to the user-supplied reference table: CompanyName (incl. owner suffix, e.g. '- Sandhu H.'), LegalName, and Industry (Construction/Real estate/Investments/Hotel/Restaurant/Rental) replace the earlier EntityName/Segment (HoldCo/RealCo/OpCo) scheme everywhere in this workbook. 'Rres_Ind' in that table was treated as a typo for 'Res_Ind' (same LegalName, 9366-1049 Québec Inc.) — same entity, not a new one. Sandhu &amp; Sandhu Enr. isn't in that table at all; its Industry ('Rental') is inferred from its sibling entity Sandhu Leasing, not given data.</t>
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>MISSING FY2026: Sandhu &amp; Sandhu Enr.'s tab in Sandhu_G__2026.xlsx ('Sheet16' — never renamed, unlike the other 15) is a byte-for-byte duplicate of the old standalone San_San_2025_WTB.xlsx, not refreshed data — so there is no genuine FY2026 figure for this entity yet. Its FY2025 figure is unaffected and stays as originally validated ($-15,821.17). A fresh San_San export is needed before FY2026 can be added for it.</t>
         </is>
       </c>
       <c r="B7" s="1" t="n"/>
@@ -11585,9 +11604,9 @@
       <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="91" t="inlineStr">
-        <is>
-          <t>UNEXPECTED FILE: 947_338_2025_Tax.csv identifies its filer as '9475-3381 Québec Inc.' — an entity not in the Section 4 entity list at all. No WTB was supplied for it, so it is NOT included in this workbook. Flagged for you to confirm whether it belongs in the group.</t>
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>New GIFI code: Restaurant Héritaj's FY2026 WTB includes account 45320 'Gain on sale' (GIFI 8211, $300,000) — not seen in any prior year for any entity. Per user decision, mapped to its own 'Gain on Sale' category (kept separate from recurring Other Operating items) rather than folded into the adjacent GIFI 8210 mapping. Added to GIFI_Master_Mapping_v2.xlsx so it categorizes automatically in future years too.</t>
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
@@ -11599,27 +11618,23 @@
       <c r="C10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="92" t="inlineStr">
-        <is>
-          <t>VALIDATION — every entity's FY2025 Net Income matches an independent benchmark exactly:</t>
+      <c r="A11" s="90" t="inlineStr">
+        <is>
+          <t>Missing: Sandhu &amp; Sandhu Enr.'s Corporate Taxprep export (its WTB was supplied and is included).</t>
         </is>
       </c>
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Restaurant IndiaRosa 2 matches every Section 6 category benchmark to the penny (Net Income FY2025 $462,894.92, FY2024 $736,959.45) — see the account-level exceptions below.</t>
-        </is>
-      </c>
+      <c r="A12" s="90" t="inlineStr"/>
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="1" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  All other 15 entities match the Validation Log tab in GIFI_Master_Mapping_v2.xlsx exactly, including Bistro Guru Inc. ($-30,118.89), which RESOLVES the discrepancy flagged in an earlier version of this workbook (the old starter kit's $-45,954.06 figure for Bistro Guru was wrong; the fresh WTB rebuild confirms the Validation Log was correct).</t>
+      <c r="A13" s="90" t="inlineStr">
+        <is>
+          <t>Dim_Entity updated to the user-supplied reference table: CompanyName (incl. owner suffix, e.g. '- Sandhu H.'), LegalName, and Industry (Construction/Real estate/Investments/Hotel/Restaurant/Rental) replace the earlier EntityName/Segment (HoldCo/RealCo/OpCo) scheme everywhere in this workbook. 'Rres_Ind' in that table was treated as a typo for 'Res_Ind' (same LegalName, 9366-1049 Québec Inc.) — same entity, not a new one. Sandhu &amp; Sandhu Enr. isn't in that table at all; its Industry ('Rental') is inferred from its sibling entity Sandhu Leasing, not given data.</t>
         </is>
       </c>
       <c r="B13" s="1" t="n"/>
@@ -11631,27 +11646,23 @@
       <c r="C14" s="1" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="90" t="inlineStr">
-        <is>
-          <t>Restaurant IndiaRosa 2 — three accounts in its WTB carry a GIFI code that contradicts the account name; treated as account-level overrides, not changes to the master GIFI mapping:</t>
+      <c r="A15" s="91" t="inlineStr">
+        <is>
+          <t>UNEXPECTED FILE: 947_338_2025_Tax.csv identifies its filer as '9475-3381 Québec Inc.' — an entity not in the Section 4 entity list at all. No WTB was supplied for it, so it is NOT included in this workbook. Flagged for you to confirm whether it belongs in the group.</t>
         </is>
       </c>
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="1" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Acct 45130 'Valet service' + 45125 'Musical entertainment' — tagged GIFI 9270 (Amortization) -&gt; reclassified to Marketing &amp; Entertainment.</t>
-        </is>
-      </c>
+      <c r="A16" s="90" t="inlineStr"/>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Acct 44215 'Rent - Ford' + 33455 'Equipment rental' + 45250 'Travelling - gas &amp; repairs' — tagged GIFI 8461 (COGS) -&gt; reclassified to Other Operating.</t>
+      <c r="A17" s="92" t="inlineStr">
+        <is>
+          <t>VALIDATION — every entity's FY2025 Net Income matches an independent benchmark exactly:</t>
         </is>
       </c>
       <c r="B17" s="1" t="n"/>
@@ -11660,49 +11671,57 @@
     <row r="18">
       <c r="A18" s="93" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Acct 45150 'Consulting fees' — tagged GIFI 8863 (Administrative) -&gt; reclassified to Other Operating per user confirmation (matches Section 6 Admin $99,729 / Other Operating $79,976 exactly).</t>
+          <t xml:space="preserve">  Restaurant IndiaRosa 2 matches every Section 6 category benchmark to the penny (Net Income FY2025 $462,894.92, FY2024 $736,959.45) — see the account-level exceptions below.</t>
         </is>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="90" t="inlineStr"/>
+      <c r="A19" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  All other 15 entities match the Validation Log tab in GIFI_Master_Mapping_v2.xlsx exactly, including Bistro Guru Inc. ($-30,118.89), which RESOLVES the discrepancy flagged in an earlier version of this workbook (the old starter kit's $-45,954.06 figure for Bistro Guru was wrong; the fresh WTB rebuild confirms the Validation Log was correct).</t>
+        </is>
+      </c>
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="90" t="inlineStr">
-        <is>
-          <t>Sandhu &amp; Sandhu Enr. — two Map No formatting variants ('40.1' vs '40. 1') were causing 3 accounts to fall through the fallback table uncategorized; fixed by normalizing whitespace in the Map No match, plus adding one missing fallback row (Map No '40. 3' -&gt; Administrative, Insurance). After the fix, FY2025 Net Income matches the Validation Log exactly ($-15,821.17).</t>
-        </is>
-      </c>
+      <c r="A20" s="90" t="inlineStr"/>
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="90" t="inlineStr"/>
+      <c r="A21" s="90" t="inlineStr">
+        <is>
+          <t>Restaurant IndiaRosa 2 — three accounts in its WTB carry a GIFI code that contradicts the account name; treated as account-level overrides, not changes to the master GIFI mapping:</t>
+        </is>
+      </c>
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="91" t="inlineStr">
-        <is>
-          <t>UNRESOLVED: group-level FY2025 Revenue ($14,945,731) and EBITDA ($2,734,142) are within ~0.5% and ~1.8% of the Section 6 16-entity benchmark ($14,873,731 / $2,784,496) despite every single entity's own Net Income matching its benchmark exactly. Income Tax and Investment &amp; Other Income match exactly. This means a small amount is sitting in a different category than the original benchmark used, in one or two entities — similar in nature to IndiaRosa 2's account exceptions above, but not yet isolated. Group Net Income is within $5,014 (0.8%) of benchmark.</t>
+      <c r="A22" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Acct 45130 'Valet service' + 45125 'Musical entertainment' — tagged GIFI 9270 (Amortization) -&gt; reclassified to Marketing &amp; Entertainment.</t>
         </is>
       </c>
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="90" t="inlineStr"/>
+      <c r="A23" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Acct 44215 'Rent - Ford' + 33455 'Equipment rental' + 45250 'Travelling - gas &amp; repairs' — tagged GIFI 8461 (COGS) -&gt; reclassified to Other Operating.</t>
+        </is>
+      </c>
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="90" t="inlineStr">
-        <is>
-          <t>NOT YET INCLUDED: RDTOH and CDA (confirmed absent from the Taxprep export tested — see 03 Tax Position). SBD/GRIP/Part I tax figures are real for IndiaRosa 2's 14 associated corporations (from its Taxprep SLIPA schedule) but each entity's OWN SBD claim from its own Taxprep export has not yet been pulled in — only IndiaRosa 2's Tax CSV has been mined for Section 3-style data.</t>
+      <c r="A24" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Acct 45150 'Consulting fees' — tagged GIFI 8863 (Administrative) -&gt; reclassified to Other Operating per user confirmation (matches Section 6 Admin $99,729 / Other Operating $79,976 exactly).</t>
         </is>
       </c>
       <c r="B24" s="1" t="n"/>
@@ -11716,7 +11735,7 @@
     <row r="26">
       <c r="A26" s="90" t="inlineStr">
         <is>
-          <t>Interactivity: this workbook uses dropdown selectors ('02 Profitability'!C6 Entity, !H6 Fiscal Year) driving live SUMIFS formulas and charts — no Power Pivot/DAX setup required, works in any version of Excel. Entity Register and raw data sheets are Excel Tables with built-in filter dropdowns per column.</t>
+          <t>Sandhu &amp; Sandhu Enr. — two Map No formatting variants ('40.1' vs '40. 1') were causing 3 accounts to fall through the fallback table uncategorized; fixed by normalizing whitespace in the Map No match, plus adding one missing fallback row (Map No '40. 3' -&gt; Administrative, Insurance). After the fix, FY2025 Net Income matches the Validation Log exactly ($-15,821.17).</t>
         </is>
       </c>
       <c r="B26" s="1" t="n"/>
@@ -11728,41 +11747,53 @@
       <c r="C27" s="1" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="90" t="inlineStr">
-        <is>
-          <t>Recalculated and verified in LibreOffice headless — every KPI card and cross-check in this sheet was confirmed against the actual computed cell values, not just the formula text.</t>
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>UNRESOLVED: group-level FY2025 Revenue ($14,945,731) and EBITDA ($2,734,142) are within ~0.5% and ~1.8% of the Section 6 16-entity benchmark ($14,873,731 / $2,784,496) despite every single entity's own Net Income matching its benchmark exactly. Income Tax and Investment &amp; Other Income match exactly. This means a small amount is sitting in a different category than the original benchmark used, in one or two entities — similar in nature to IndiaRosa 2's account exceptions above, but not yet isolated. Group Net Income is within $5,014 (0.8%) of benchmark.</t>
         </is>
       </c>
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="1" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n"/>
+      <c r="A29" s="90" t="inlineStr"/>
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n"/>
+      <c r="A30" s="90" t="inlineStr">
+        <is>
+          <t>NOT YET INCLUDED: RDTOH and CDA (confirmed absent from the Taxprep export tested — see 03 Tax Position). SBD/GRIP/Part I tax figures are real for IndiaRosa 2's 14 associated corporations (from its Taxprep SLIPA schedule) but each entity's OWN SBD claim from its own Taxprep export has not yet been pulled in — only IndiaRosa 2's Tax CSV has been mined for Section 3-style data.</t>
+        </is>
+      </c>
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="1" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n"/>
+      <c r="A31" s="90" t="inlineStr"/>
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="1" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n"/>
+      <c r="A32" s="90" t="inlineStr">
+        <is>
+          <t>Interactivity: this workbook uses dropdown selectors ('02 Profitability'!C6 Entity, !H6 Fiscal Year) driving live SUMIFS formulas and charts — no Power Pivot/DAX setup required, works in any version of Excel. Entity Register and raw data sheets are Excel Tables with built-in filter dropdowns per column.</t>
+        </is>
+      </c>
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="1" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n"/>
+      <c r="A33" s="90" t="inlineStr"/>
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="1" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n"/>
+      <c r="A34" s="90" t="inlineStr">
+        <is>
+          <t>Recalculated and verified in LibreOffice headless — every KPI card and cross-check in this sheet was confirmed against the actual computed cell values, not just the formula text.</t>
+        </is>
+      </c>
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="n"/>
     </row>
@@ -11820,6 +11851,81 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="1" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="n"/>
+      <c r="C47" s="1" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="1" t="n"/>
+      <c r="C48" s="1" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="1" t="n"/>
+      <c r="C50" s="1" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="n"/>
+      <c r="C51" s="1" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="1" t="n"/>
+      <c r="C52" s="1" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n"/>
+      <c r="B53" s="1" t="n"/>
+      <c r="C53" s="1" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="1" t="n"/>
+      <c r="C54" s="1" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n"/>
+      <c r="B56" s="1" t="n"/>
+      <c r="C56" s="1" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n"/>
+      <c r="B57" s="1" t="n"/>
+      <c r="C57" s="1" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="1" t="n"/>
+      <c r="C58" s="1" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n"/>
+      <c r="B59" s="1" t="n"/>
+      <c r="C59" s="1" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="1" t="n"/>
+      <c r="C60" s="1" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12234,7 +12340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12307,6 +12413,23 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FY2026</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E326"/>
+  <dimension ref="A1:E440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20486,6 +20609,2856 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D327" s="95" t="n">
+        <v>-3747447.26</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D328" s="95" t="n">
+        <v>45342.25</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D329" s="95" t="n">
+        <v>1093643.32</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D330" s="95" t="n">
+        <v>110347.77</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D331" s="95" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D332" s="95" t="n">
+        <v>1428958.93</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D333" s="95" t="n">
+        <v>297973.66</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D334" s="95" t="n">
+        <v>137080.34</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D335" s="95" t="n">
+        <v>74033</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D336" s="95" t="n">
+        <v>110620.85</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D337" s="95" t="n">
+        <v>121013</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>9366-1049 QI</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D338" s="95" t="n">
+        <v>86779</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D339" s="95" t="n">
+        <v>-4471009.29</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D340" s="95" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D341" s="95" t="n">
+        <v>119143.3</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D342" s="95" t="n">
+        <v>1373196.77</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D343" s="95" t="n">
+        <v>84255.38</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D344" s="95" t="n">
+        <v>1535535.39</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D345" s="95" t="n">
+        <v>517131.55</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D346" s="95" t="n">
+        <v>60321.55</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D347" s="95" t="n">
+        <v>90643.67</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D348" s="95" t="n">
+        <v>122778.53</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D349" s="95" t="n">
+        <v>177785</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>9455-8236 QI</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D350" s="95" t="n">
+        <v>87694</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D351" s="95" t="n">
+        <v>-3435799.94</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D352" s="95" t="n">
+        <v>-263.76</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D353" s="95" t="n">
+        <v>1072421.53</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D354" s="95" t="n">
+        <v>1096801.58</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D355" s="95" t="n">
+        <v>74738.92999999999</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D356" s="95" t="n">
+        <v>315909.85</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D357" s="95" t="n">
+        <v>147386.03</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D358" s="95" t="n">
+        <v>43069.86</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D359" s="95" t="n">
+        <v>111438.41</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D360" s="95" t="n">
+        <v>89541</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D361" s="95" t="n">
+        <v>78023.31</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>9525-2854 QI</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D362" s="95" t="n">
+        <v>85776</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D363" s="95" t="n">
+        <v>-2410355.19</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D364" s="95" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D365" s="95" t="n">
+        <v>962126.53</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D366" s="95" t="n">
+        <v>1146768.51</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D367" s="95" t="n">
+        <v>113670.95</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D368" s="95" t="n">
+        <v>67519.60000000001</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D369" s="95" t="n">
+        <v>3403.31</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D370" s="95" t="n">
+        <v>49520.65</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D371" s="95" t="n">
+        <v>59903.53</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D372" s="95" t="n">
+        <v>173201.79</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D373" s="95" t="n">
+        <v>68739.72</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>9504-7510 QI</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Gain on Sale</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D374" s="95" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D375" s="95" t="n">
+        <v>-1747906.67</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D376" s="95" t="n">
+        <v>14275.14</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D377" s="95" t="n">
+        <v>828828.65</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D378" s="95" t="n">
+        <v>499887.38</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D379" s="95" t="n">
+        <v>102826.18</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D380" s="95" t="n">
+        <v>64151.08</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D381" s="95" t="n">
+        <v>19888.87</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D382" s="95" t="n">
+        <v>179240.18</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D383" s="95" t="n">
+        <v>26866</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>9098-0558 QI</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D384" s="95" t="n">
+        <v>35179.57</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D385" s="95" t="n">
+        <v>-2637339.41</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D386" s="95" t="n">
+        <v>265830.76</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D387" s="95" t="n">
+        <v>55250</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D388" s="95" t="n">
+        <v>282085.63</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D389" s="95" t="n">
+        <v>148741.79</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D390" s="95" t="n">
+        <v>683289.04</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D391" s="95" t="n">
+        <v>142842.42</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D392" s="95" t="n">
+        <v>225566.81</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D393" s="95" t="n">
+        <v>244420.44</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D394" s="95" t="n">
+        <v>182030.5</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D395" s="95" t="n">
+        <v>89641.37</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>9108-6876 QI</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D396" s="95" t="n">
+        <v>101350</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D397" s="95" t="n">
+        <v>-174699.6</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D398" s="95" t="n">
+        <v>28463.6</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Management Fees (Interco)</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D399" s="95" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D400" s="95" t="n">
+        <v>24482.49</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D401" s="95" t="n">
+        <v>1605</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D402" s="95" t="n">
+        <v>69074.72</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D403" s="95" t="n">
+        <v>83143.49000000001</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D404" s="95" t="n">
+        <v>29988.79</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D405" s="95" t="n">
+        <v>1885.23</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D406" s="95" t="n">
+        <v>13378</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>9096-0436 QI</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D407" s="95" t="n">
+        <v>4884.76</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>N/A_BisGur</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D408" s="95" t="n">
+        <v>-439.02</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>N/A_BisGur</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D409" s="95" t="n">
+        <v>4763.69</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>N/A_BisGur</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D410" s="95" t="n">
+        <v>4131.23</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>N/A_BisGur</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D411" s="95" t="n">
+        <v>1758.11</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>N/A_BisGur</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D412" s="95" t="n">
+        <v>1045.3</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>9366-1676 QI</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D413" s="95" t="n">
+        <v>-200981.91</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>9366-1676 QI</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D414" s="95" t="n">
+        <v>297055.39</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>9366-1676 QI</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D415" s="95" t="n">
+        <v>197252</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>9366-1676 QI</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D416" s="95" t="n">
+        <v>226938.85</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>9366-1676 QI</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D417" s="95" t="n">
+        <v>35356.05</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>9425-4547 QI</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D418" s="95" t="n">
+        <v>-264846</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>9425-4547 QI</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D419" s="95" t="n">
+        <v>-82909.61</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>9425-4547 QI</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D420" s="95" t="n">
+        <v>130640.39</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>9425-4547 QI</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D421" s="95" t="n">
+        <v>14292</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>9425-4547 QI</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D422" s="95" t="n">
+        <v>94165.11</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>9425-4547 QI</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D423" s="95" t="n">
+        <v>9129.389999999999</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Real estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>9357-7427 QI</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D424" s="95" t="n">
+        <v>-28350</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>9357-7427 QI</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D425" s="95" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>9357-7427 QI</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D426" s="95" t="n">
+        <v>2489.81</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>9357-7427 QI</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D427" s="95" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>9455-4201 QI</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Investment &amp; Other Income</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D428" s="95" t="n">
+        <v>-282589.41</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>9455-4201 QI</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D429" s="95" t="n">
+        <v>504</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>9455-4201 QI</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D430" s="95" t="n">
+        <v>90969.07000000001</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>9455-4177 QI</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D431" s="95" t="n">
+        <v>1604</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>9455-4177 QI</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D432" s="95" t="n">
+        <v>145.78</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>9455-4169 QI</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D433" s="95" t="n">
+        <v>1604</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>9455-4169 QI</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D434" s="95" t="n">
+        <v>145.79</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D435" s="95" t="n">
+        <v>-109765.32</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D436" s="95" t="n">
+        <v>677.65</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Other Operating</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D437" s="95" t="n">
+        <v>19007.52</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D438" s="95" t="n">
+        <v>6300.69</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D439" s="95" t="n">
+        <v>17021</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2749-8567 QI</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Interest &amp; Financing</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D440" s="95" t="n">
+        <v>866.76</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Rental</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
